--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="777" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F234212-11B4-47E8-99B8-350CD46B3B0C}"/>
+  <xr:revisionPtr revIDLastSave="781" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2861DFB0-9748-4009-AAD5-DD44D47C4BDE}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>DAC</t>
-  </si>
-  <si>
-    <t>RST</t>
   </si>
   <si>
     <t>DSV</t>
@@ -1242,6 +1239,9 @@
   <si>
     <t>%Consumo 
 Prazo</t>
+  </si>
+  <si>
+    <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
   </si>
 </sst>
 </file>
@@ -1723,7 +1723,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="35.6328125" customWidth="1"/>
     <col min="3" max="3" width="55.6328125" customWidth="1"/>
     <col min="4" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1763,19 +1763,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1790,28 +1790,28 @@
         <v>10</v>
       </c>
       <c r="Q1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="S1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R1" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="V1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="V1" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="W1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="X1" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="X1" s="13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="116" x14ac:dyDescent="0.35">
@@ -1822,7 +1822,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>43</v>
@@ -1837,13 +1837,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1864,21 +1864,21 @@
         <v>46283</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1886,13 +1886,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>56</v>
@@ -1904,13 +1904,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1931,20 +1931,20 @@
         <v>46286</v>
       </c>
       <c r="Q3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1955,7 +1955,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>46</v>
@@ -1970,13 +1970,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -1997,24 +1997,24 @@
         <v>46296</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="X4" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="159.5" x14ac:dyDescent="0.35">
@@ -2025,10 +2025,10 @@
         <v>57</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>58</v>
@@ -2040,10 +2040,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="7">
@@ -2063,26 +2063,26 @@
         <v>46287</v>
       </c>
       <c r="Q5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2090,7 +2090,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
@@ -2106,13 +2106,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2133,22 +2133,22 @@
         <v>46286</v>
       </c>
       <c r="Q6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="X6" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2172,13 +2172,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2199,22 +2199,22 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2222,16 +2222,16 @@
         <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2240,13 +2240,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2267,20 +2267,20 @@
         <v>46293</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2288,14 +2288,14 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>305</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>12</v>
@@ -2304,13 +2304,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2329,24 +2329,24 @@
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>64</v>
@@ -2370,13 +2370,13 @@
         <v>33</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2395,24 +2395,24 @@
         <v>46297</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2420,14 +2420,14 @@
         <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>12</v>
@@ -2436,13 +2436,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2463,22 +2463,22 @@
         <v>45915</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2486,14 +2486,14 @@
         <v>55</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>34</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="9">
@@ -2521,21 +2521,21 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
       <c r="W12" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="9">
@@ -2567,25 +2567,25 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>34</v>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="9">
@@ -2613,25 +2613,25 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="9">
@@ -2659,22 +2659,22 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="9">
@@ -2705,18 +2705,18 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
       <c r="W16" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="7"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H17" s="16"/>
       <c r="I17" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="9">
@@ -2749,22 +2749,22 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
       <c r="W17" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>56</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="9">
@@ -2795,21 +2795,21 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="9">
@@ -2841,24 +2841,24 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
       <c r="W19" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="261" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>56</v>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="9">
@@ -2889,25 +2889,25 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
       <c r="W20" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="9">
@@ -2935,25 +2935,25 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
       <c r="W21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>34</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="9">
@@ -2981,25 +2981,25 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>34</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="9">
@@ -3027,18 +3027,18 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="7" t="s">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="9">
@@ -3073,23 +3073,23 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
       <c r="W24" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>34</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H25" s="16"/>
       <c r="I25" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="9">
@@ -3117,25 +3117,25 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>34</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="9">
@@ -3163,25 +3163,25 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
       <c r="W26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>34</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="9">
@@ -3209,25 +3209,25 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
       <c r="W27" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>34</v>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="9">
@@ -3255,22 +3255,22 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>44</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="9">
@@ -3301,21 +3301,21 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
       <c r="W29" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="9">
@@ -3347,25 +3347,25 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
       <c r="W30" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>34</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="9">
@@ -3393,25 +3393,25 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>34</v>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="9">
@@ -3439,24 +3439,24 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>284</v>
-      </c>
       <c r="C33" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>58</v>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="9">
@@ -3487,10 +3487,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="X33" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="781" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2861DFB0-9748-4009-AAD5-DD44D47C4BDE}"/>
+  <xr:revisionPtr revIDLastSave="802" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48525A45-607D-4808-92A3-9674061CCACD}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,9 +265,6 @@
 Analistas revisando todas as jornadas</t>
   </si>
   <si>
-    <t>Homologações com Integradoras e Auditoras em andamento</t>
-  </si>
-  <si>
     <t xml:space="preserve">Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best - sem previsão
 Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
 Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
@@ -285,11 +282,6 @@
   </si>
   <si>
     <t>Artur Giannini</t>
-  </si>
-  <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação.
-Alteralçao do conteúdo durante a etapa de ambientação no AVA
-Alterações normativas durante a produção do conteúdo da capacitação</t>
   </si>
   <si>
     <t>Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP;
@@ -955,26 +947,12 @@
 Material de treinamento em elaboração</t>
   </si>
   <si>
-    <t>Homologação (correção dos 54 itens) - 06/10/2026
-Subida em produção -  07/10/2026
-Correção de demais itens da V3 - 12/10/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Correção de Bugs da V3 -30/09/2026 (54 itens)
 </t>
   </si>
   <si>
-    <t>O módulo Admin será entregue com a V4
-O  ininício da versão V4 está condicionada ao término da V3.
-Refinamento dos requisitos - início previsto 13/10/2026</t>
-  </si>
-  <si>
     <t>Possível revisão de escopo - impacto no cronograma
 Não há previsão para o término do projeto</t>
-  </si>
-  <si>
-    <t>Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas
-A data prevista inicialmente de 25/09/2026 não foi atingida e não há ainda previsão para o fim do projeto</t>
   </si>
   <si>
     <t>Aprovar a Estrutura Organizacional e o Quadro Demonstrativo dos Cargos em Comissão e das Funções de Confiança do Departamento Estadual de Trânsito - DETRAN-SP.</t>
@@ -1016,12 +994,6 @@
   <si>
     <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
 Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 13/10/2026</t>
-  </si>
-  <si>
-    <t>Implantação Classificação de Monta - 01/10/2026
-Implantação Mera identificação - 16/10/2026
-Implantação Compra e Venda de Veículos - 01/11/2026
-Operação Assistida até 23/12/2026</t>
   </si>
   <si>
     <t>Próximos Passos</t>
@@ -1138,12 +1110,6 @@
   </si>
   <si>
     <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be</t>
-  </si>
-  <si>
-    <t>Homologação e implantação da Classificação de Monta -01/10/2026</t>
-  </si>
-  <si>
-    <t>Correção de BUGs da V2 e V3</t>
   </si>
   <si>
     <t>Alinhamento com as áreas de negócio sobre o conteúdo programático</t>
@@ -1242,6 +1208,43 @@
   </si>
   <si>
     <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
+  </si>
+  <si>
+    <t>Implantação MVP-1 que contempla os laudos de vistoria de estrutura e alteração veicular</t>
+  </si>
+  <si>
+    <t>Implantação MVP-1 que contempla os laudos de vistoria de estrutura e alteração veicular
+(Classificação de Monta)</t>
+  </si>
+  <si>
+    <t>Acompanhar funcionamento MVP-1
+Implantação Mera identificação - 16/10/2026
+Implantação Compra e Venda de Veículos - 01/11/2026
+Operação Assistida até 23/12/2026</t>
+  </si>
+  <si>
+    <t>Atraso na revisão e validação do conteúdo da capacitação.
+Alteraçao do conteúdo durante a etapa de ambientação no AVA
+Alterações normativas durante a produção do conteúdo da capacitação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas
+A data prevista inicialmente de 25/09/2026 não foi atingida e não há ainda previsão para o fim do projeto
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção de BUGs da V2 e V3
+</t>
+  </si>
+  <si>
+    <t>Homologação (correção dos 54 itens) - 06/10/2026
+Subida em produção -  07/10/2026
+Correção de demais itens da V3 - 12/10/2026</t>
+  </si>
+  <si>
+    <t>O módulo Admin será entregue com a V4
+O  ininício da versão V4 está condicionada ao término da V3.
+Refinamento dos requisitos - início previsto 13/10/2026</t>
   </si>
 </sst>
 </file>
@@ -1748,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1763,19 +1766,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1793,7 +1796,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1802,16 +1805,16 @@
         <v>73</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V1" s="13" t="s">
         <v>74</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="116" x14ac:dyDescent="0.35">
@@ -1822,7 +1825,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>43</v>
@@ -1837,13 +1840,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1872,13 +1875,13 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1889,10 +1892,10 @@
         <v>68</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>56</v>
@@ -1904,13 +1907,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1931,20 +1934,20 @@
         <v>46286</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1955,7 +1958,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>46</v>
@@ -1970,13 +1973,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -1997,24 +2000,24 @@
         <v>46296</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="159.5" x14ac:dyDescent="0.35">
@@ -2025,10 +2028,10 @@
         <v>57</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>58</v>
@@ -2040,10 +2043,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="7">
@@ -2063,26 +2066,26 @@
         <v>46287</v>
       </c>
       <c r="Q5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2106,13 +2109,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2141,14 +2144,14 @@
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2172,13 +2175,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2199,22 +2202,22 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2225,13 +2228,13 @@
         <v>70</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2240,13 +2243,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2266,21 +2269,21 @@
       <c r="P8" s="8">
         <v>46293</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>79</v>
+      <c r="Q8" s="15" t="s">
+        <v>299</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2288,11 +2291,11 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>67</v>
@@ -2304,13 +2307,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2321,32 +2324,30 @@
       <c r="M9" s="8">
         <v>46042</v>
       </c>
-      <c r="N9" s="8">
-        <v>46185</v>
-      </c>
+      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8">
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2358,7 +2359,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>64</v>
@@ -2370,13 +2371,13 @@
         <v>33</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2395,24 +2396,24 @@
         <v>46297</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2420,7 +2421,7 @@
         <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
@@ -2436,13 +2437,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2463,22 +2464,22 @@
         <v>45915</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2486,14 +2487,14 @@
         <v>55</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>34</v>
@@ -2503,7 +2504,7 @@
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="9">
@@ -2521,21 +2522,21 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
       <c r="W12" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -2549,7 +2550,7 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="9">
@@ -2567,25 +2568,25 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>34</v>
@@ -2595,7 +2596,7 @@
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="9">
@@ -2613,25 +2614,25 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
@@ -2641,7 +2642,7 @@
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="9" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="9">
@@ -2659,22 +2660,22 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
@@ -2687,7 +2688,7 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="9" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="9">
@@ -2705,18 +2706,18 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
       <c r="W16" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="7"/>
@@ -2731,7 +2732,7 @@
       </c>
       <c r="H17" s="16"/>
       <c r="I17" s="9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="9">
@@ -2749,22 +2750,22 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
       <c r="W17" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>56</v>
@@ -2777,7 +2778,7 @@
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="9">
@@ -2795,21 +2796,21 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -2823,7 +2824,7 @@
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="9">
@@ -2841,24 +2842,24 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
       <c r="W19" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="261" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>56</v>
@@ -2871,7 +2872,7 @@
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="9">
@@ -2889,25 +2890,25 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
       <c r="W20" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
@@ -2917,7 +2918,7 @@
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="9">
@@ -2935,25 +2936,25 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
       <c r="W21" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>34</v>
@@ -2963,7 +2964,7 @@
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="9">
@@ -2981,25 +2982,25 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>34</v>
@@ -3009,7 +3010,7 @@
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="9">
@@ -3027,18 +3028,18 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="7" t="s">
@@ -3055,7 +3056,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="9">
@@ -3073,18 +3074,18 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
       <c r="W24" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="7"/>
@@ -3099,7 +3100,7 @@
       </c>
       <c r="H25" s="16"/>
       <c r="I25" s="9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="9">
@@ -3117,25 +3118,25 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>34</v>
@@ -3145,7 +3146,7 @@
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="9" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="9">
@@ -3163,25 +3164,25 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
       <c r="W26" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>34</v>
@@ -3191,7 +3192,7 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="9" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="9">
@@ -3209,25 +3210,25 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
       <c r="W27" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>34</v>
@@ -3237,7 +3238,7 @@
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="9" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="9">
@@ -3255,22 +3256,22 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>44</v>
@@ -3283,7 +3284,7 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="9">
@@ -3301,21 +3302,21 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
       <c r="W29" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
@@ -3329,7 +3330,7 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="9">
@@ -3347,21 +3348,21 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
       <c r="W30" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
@@ -3375,7 +3376,7 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="9" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="9">
@@ -3393,25 +3394,25 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>34</v>
@@ -3421,7 +3422,7 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="9">
@@ -3439,24 +3440,24 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>58</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="9">
@@ -3487,10 +3488,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3721,17 +3722,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3972,6 +3962,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3982,17 +3983,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4011,6 +4001,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="802" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48525A45-607D-4808-92A3-9674061CCACD}"/>
+  <xr:revisionPtr revIDLastSave="803" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB954FC4-9BDF-4A23-8E16-7BD06F1A0A78}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1223,11 +1223,6 @@
 Operação Assistida até 23/12/2026</t>
   </si>
   <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação.
-Alteraçao do conteúdo durante a etapa de ambientação no AVA
-Alterações normativas durante a produção do conteúdo da capacitação</t>
-  </si>
-  <si>
     <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas
 A data prevista inicialmente de 25/09/2026 não foi atingida e não há ainda previsão para o fim do projeto
 </t>
@@ -1245,6 +1240,11 @@
     <t>O módulo Admin será entregue com a V4
 O  ininício da versão V4 está condicionada ao término da V3.
 Refinamento dos requisitos - início previsto 13/10/2026</t>
+  </si>
+  <si>
+    <t>Atraso na revisão e validação do conteúdo da capacitação.
+Alteração do conteúdo durante a etapa de ambientação no AVA
+Alterações normativas durante a produção do conteúdo da capacitação</t>
   </si>
 </sst>
 </file>
@@ -2307,13 +2307,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>246</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2333,10 +2333,10 @@
         <v>223</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
@@ -2473,7 +2473,7 @@
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="W11" s="3" t="s">
         <v>191</v>
@@ -3722,6 +3722,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3962,27 +3982,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4001,25 +4020,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="803" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB954FC4-9BDF-4A23-8E16-7BD06F1A0A78}"/>
+  <xr:revisionPtr revIDLastSave="808" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BC88B3A-108A-46FD-A4CE-967F14771F70}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,11 +730,6 @@
 Transmitir ao cidadão a eficiência e a confiança nos serviços.
 Transmitir o conceito disponibilidade do Detran-SP em atender o cidadão.
 </t>
-  </si>
-  <si>
-    <t>Realizar concurso público para contratação de novos Agentes Estaduais de Transito.
-Promover a recepção dos novos agentes, garantindo que o processo de onboarding seja estruturado e acolhedor.
-A iniciativa contempla a apresentação institucional, incluindo áreas da empresa, benefícios e regras internas, além de reforçar a integração cultural por meio de atividades que transmitam valores, missão e visão da organização, serão ministrados treinamentos operacionais voltados às rotinas e processos específicos de cada função, com suporte de ferramentas digitais que centralizam informações, documentos e conteúdos de capacitação.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1246,12 +1241,42 @@
 Alteração do conteúdo durante a etapa de ambientação no AVA
 Alterações normativas durante a produção do conteúdo da capacitação</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Promover a recepção dos novos agentes, garantindo que o processo de onboarding seja estruturado e acolhedor.
+A iniciativa contempla a apresentação institucional, incluindo áreas da empresa, benefícios e regras internas, além de reforçar a integração cultural por meio de atividades que transmitam valores, missão e visão da organização, serão ministrados treinamentos operacionais voltados às rotinas e processos específicos de cada função, com suporte de ferramentas digitais que centralizam informações, documentos e conteúdos de capacitação.
+Capacitação dos novos ingressantes para o exercício da função.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NÃO ESCOPO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: O Concurso Público em andamento é de responsabilidade unica e exclusivamente da DAL. 
+A data da realização da prova, descrita  nesse projeto, é meramente informativa.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1276,6 +1301,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1769,16 +1802,16 @@
         <v>150</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1796,7 +1829,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1843,10 +1876,10 @@
         <v>151</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1875,13 +1908,13 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>94</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1907,13 +1940,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1944,10 +1977,10 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1973,13 +2006,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -2000,17 +2033,17 @@
         <v>46296</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
@@ -2046,7 +2079,7 @@
         <v>152</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="7">
@@ -2085,7 +2118,7 @@
         <v>97</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2109,13 +2142,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2175,13 +2208,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2202,13 +2235,13 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
@@ -2217,7 +2250,7 @@
         <v>100</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2234,7 +2267,7 @@
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2243,13 +2276,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2270,10 +2303,10 @@
         <v>46293</v>
       </c>
       <c r="Q8" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
@@ -2283,7 +2316,7 @@
         <v>101</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2291,7 +2324,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
@@ -2307,13 +2340,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2330,24 +2363,24 @@
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>102</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2374,10 +2407,10 @@
         <v>153</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2396,10 +2429,10 @@
         <v>46297</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>79</v>
@@ -2410,13 +2443,13 @@
         <v>80</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>54</v>
       </c>
@@ -2437,13 +2470,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2473,13 +2506,13 @@
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="W11" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="W11" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="X11" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2494,7 +2527,7 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>34</v>
@@ -2504,7 +2537,7 @@
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="9">
@@ -2550,7 +2583,7 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="9">
@@ -2568,7 +2601,7 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>169</v>
@@ -2586,7 +2619,7 @@
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>34</v>
@@ -2596,7 +2629,7 @@
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="9">
@@ -2632,7 +2665,7 @@
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
@@ -2642,7 +2675,7 @@
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="9">
@@ -2660,7 +2693,7 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>171</v>
@@ -2675,7 +2708,7 @@
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
@@ -2688,7 +2721,7 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="9">
@@ -2706,7 +2739,7 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
       <c r="W16" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X16" s="3" t="s">
         <v>172</v>
@@ -2732,7 +2765,7 @@
       </c>
       <c r="H17" s="16"/>
       <c r="I17" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="9">
@@ -2750,7 +2783,7 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
       <c r="W17" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>173</v>
@@ -2765,7 +2798,7 @@
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>56</v>
@@ -2778,7 +2811,7 @@
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="9">
@@ -2796,7 +2829,7 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>174</v>
@@ -2824,7 +2857,7 @@
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="9">
@@ -2842,7 +2875,7 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
       <c r="W19" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>175</v>
@@ -2859,7 +2892,7 @@
         <v>161</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>56</v>
@@ -2872,7 +2905,7 @@
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="9">
@@ -2890,7 +2923,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
       <c r="W20" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>176</v>
@@ -2905,10 +2938,10 @@
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
@@ -2918,7 +2951,7 @@
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="9">
@@ -2936,7 +2969,7 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
       <c r="W21" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>177</v>
@@ -2954,7 +2987,7 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>34</v>
@@ -2964,7 +2997,7 @@
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="9">
@@ -2982,7 +3015,7 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>178</v>
@@ -3000,7 +3033,7 @@
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>34</v>
@@ -3010,7 +3043,7 @@
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="9">
@@ -3028,7 +3061,7 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>179</v>
@@ -3056,7 +3089,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="9">
@@ -3074,7 +3107,7 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
       <c r="W24" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>180</v>
@@ -3100,7 +3133,7 @@
       </c>
       <c r="H25" s="16"/>
       <c r="I25" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="9">
@@ -3118,7 +3151,7 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>181</v>
@@ -3136,7 +3169,7 @@
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>34</v>
@@ -3146,7 +3179,7 @@
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="9">
@@ -3164,7 +3197,7 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
       <c r="W26" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>182</v>
@@ -3182,7 +3215,7 @@
         <v>65</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>34</v>
@@ -3192,7 +3225,7 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="9">
@@ -3210,7 +3243,7 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
       <c r="W27" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>183</v>
@@ -3228,7 +3261,7 @@
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>34</v>
@@ -3238,7 +3271,7 @@
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="9">
@@ -3256,7 +3289,7 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X28" s="3" t="s">
         <v>184</v>
@@ -3271,7 +3304,7 @@
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>44</v>
@@ -3284,7 +3317,7 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="9">
@@ -3302,7 +3335,7 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
       <c r="W29" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>185</v>
@@ -3330,7 +3363,7 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="9">
@@ -3348,7 +3381,7 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
       <c r="W30" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X30" s="3" t="s">
         <v>186</v>
@@ -3376,7 +3409,7 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="9">
@@ -3394,7 +3427,7 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X31" s="3" t="s">
         <v>187</v>
@@ -3412,7 +3445,7 @@
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>34</v>
@@ -3422,7 +3455,7 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="9">
@@ -3440,7 +3473,7 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>188</v>
@@ -3448,16 +3481,16 @@
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>275</v>
-      </c>
       <c r="C33" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>58</v>
@@ -3470,7 +3503,7 @@
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="9">
@@ -3488,10 +3521,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="X33" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3722,26 +3755,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3982,26 +3995,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4020,6 +4034,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="808" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BC88B3A-108A-46FD-A4CE-967F14771F70}"/>
+  <xr:revisionPtr revIDLastSave="809" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52D5CD7-4762-4561-A2DD-F1F0C14DFC0E}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -935,11 +935,6 @@
   </si>
   <si>
     <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
-  </si>
-  <si>
-    <t>Projeto segue dentro do prazo, conforme planejado
-Edital  publicado - provas 01/11/2026
-Material de treinamento em elaboração</t>
   </si>
   <si>
     <t xml:space="preserve">Correção de Bugs da V3 -30/09/2026 (54 itens)
@@ -1270,6 +1265,11 @@
       <t>: O Concurso Público em andamento é de responsabilidade unica e exclusivamente da DAL. 
 A data da realização da prova, descrita  nesse projeto, é meramente informativa.</t>
     </r>
+  </si>
+  <si>
+    <t>Projeto segue dentro do prazo, conforme planejado
+Edital  publicado - provas 01/11/2026 (DAL)
+Material de treinamento em elaboração</t>
   </si>
 </sst>
 </file>
@@ -1802,16 +1802,16 @@
         <v>150</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1829,7 +1829,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1876,10 +1876,10 @@
         <v>151</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1908,7 +1908,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>94</v>
@@ -1940,13 +1940,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -2006,13 +2006,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -2033,17 +2033,17 @@
         <v>46296</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
@@ -2079,7 +2079,7 @@
         <v>152</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="7">
@@ -2142,13 +2142,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2208,13 +2208,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2235,13 +2235,13 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
@@ -2276,13 +2276,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2303,10 +2303,10 @@
         <v>46293</v>
       </c>
       <c r="Q8" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
@@ -2324,7 +2324,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
@@ -2340,13 +2340,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>300</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>301</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2363,18 +2363,18 @@
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>102</v>
@@ -2407,10 +2407,10 @@
         <v>153</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2429,10 +2429,10 @@
         <v>46297</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>79</v>
@@ -2470,13 +2470,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2506,10 +2506,10 @@
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="W11" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>201</v>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="9">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="9">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="9">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="9">
@@ -2693,7 +2693,7 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>171</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="9">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="H17" s="16"/>
       <c r="I17" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="9">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>56</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="9">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="9">
@@ -2892,7 +2892,7 @@
         <v>161</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>56</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="9">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>202</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="9">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="9">
@@ -3015,7 +3015,7 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>178</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="9">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="9">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="16"/>
       <c r="I25" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="9">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="9">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="9">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>34</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="9">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>44</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="9">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="9">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="9">
@@ -3427,7 +3427,7 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X31" s="3" t="s">
         <v>187</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="9">
@@ -3473,7 +3473,7 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>188</v>
@@ -3481,16 +3481,16 @@
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>274</v>
-      </c>
       <c r="C33" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>58</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="9">
@@ -3521,10 +3521,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="X33" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3755,6 +3755,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3995,27 +4015,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4034,25 +4053,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="809" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52D5CD7-4762-4561-A2DD-F1F0C14DFC0E}"/>
+  <xr:revisionPtr revIDLastSave="810" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92BC5510-D7FC-417D-825F-931A696F798B}"/>
   <bookViews>
     <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1235,6 +1235,11 @@
     <t>Atraso na revisão e validação do conteúdo da capacitação.
 Alteração do conteúdo durante a etapa de ambientação no AVA
 Alterações normativas durante a produção do conteúdo da capacitação</t>
+  </si>
+  <si>
+    <t>Projeto segue dentro do prazo, conforme planejado
+Edital  publicado - provas 01/11/2026 (DAL)
+Material de treinamento em elaboração</t>
   </si>
   <si>
     <r>
@@ -1262,14 +1267,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: O Concurso Público em andamento é de responsabilidade unica e exclusivamente da DAL. 
+      <t>: O Concurso Público em andamento é de responsabilidade única e exclusivamente da DAL. 
 A data da realização da prova, descrita  nesse projeto, é meramente informativa.</t>
     </r>
-  </si>
-  <si>
-    <t>Projeto segue dentro do prazo, conforme planejado
-Edital  publicado - provas 01/11/2026 (DAL)
-Material de treinamento em elaboração</t>
   </si>
 </sst>
 </file>
@@ -2470,7 +2470,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>246</v>
@@ -2509,7 +2509,7 @@
         <v>303</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>201</v>
@@ -3755,26 +3755,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -4015,26 +3995,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4053,6 +4034,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="810" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92BC5510-D7FC-417D-825F-931A696F798B}"/>
+  <xr:revisionPtr revIDLastSave="861" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D9A9C2-B123-41F5-8680-CB09172E2195}"/>
   <bookViews>
-    <workbookView xWindow="-15615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="276">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -249,20 +249,6 @@
   </si>
   <si>
     <t>Riscos</t>
-  </si>
-  <si>
-    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais</t>
-  </si>
-  <si>
-    <t>Aguardando licitação da PRF
-Implantação dos equipamentros</t>
-  </si>
-  <si>
-    <t>Todas jornadas finalizadas</t>
-  </si>
-  <si>
-    <t>Aguardando validação AME
-Analistas revisando todas as jornadas</t>
   </si>
   <si>
     <t xml:space="preserve">Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best - sem previsão
@@ -523,11 +509,6 @@
   </si>
   <si>
     <t>Justificativa da Situação</t>
-  </si>
-  <si>
-    <t>Mudança de estratégia : 
-Decisão de entrar na licitação da PRF para aquisição das câmeras corporais.
-Dependência de licitação a ser realizada por outro órgão.</t>
   </si>
   <si>
     <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura.
@@ -999,99 +980,6 @@
     <t>Período da última semana</t>
   </si>
   <si>
-    <t>28/09/2026 a 02/10/2026</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2027</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2028</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2029</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2030</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2031</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2032</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2033</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2034</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2035</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2036</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2037</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2038</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2039</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2040</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2041</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2042</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2043</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2044</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2045</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2046</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2047</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2048</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2049</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2050</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2051</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2052</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2053</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2054</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2055</t>
-  </si>
-  <si>
-    <t>28/09/2026 a 02/10/2056</t>
-  </si>
-  <si>
     <t>O que foi feito na última semana</t>
   </si>
   <si>
@@ -1168,15 +1056,6 @@
 Sistema de Atendimento - entregue 14/06/2026 (homologação)
 Base de Conhecimento - correções - entregue 30/09/2026
 </t>
-  </si>
-  <si>
-    <t>Sistema de Atendimento preparação para GMUD em 05/10
-Elaboração e aprovação de comunicado para 05/10</t>
-  </si>
-  <si>
-    <t>Capacitação em prompts - 15/10/2026
-Agente OCR de Documentos de Credenciamento - integração com o portal - 22/10/2026
-Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
   </si>
   <si>
     <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
@@ -1270,6 +1149,40 @@
       <t>: O Concurso Público em andamento é de responsabilidade única e exclusivamente da DAL. 
 A data da realização da prova, descrita  nesse projeto, é meramente informativa.</t>
     </r>
+  </si>
+  <si>
+    <t>05/10/2026 a 09/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
+</t>
+  </si>
+  <si>
+    <t>Capacitação em prompts - 19/10/2026
+Agente OCR de Documentos de Credenciamento - integração com o portal - 27/10/2026
+Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
+  </si>
+  <si>
+    <t>Mudança de estratégia : 
+Decisão de entrar na licitação da PRF para aquisição das câmeras corporais.
+Dependência de licitação a ser realizada por outro órgão.
+Até o momento não temos resposta da PRF sobre a licitação</t>
+  </si>
+  <si>
+    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
+Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
+Não houve resposta da PRF até o momento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação
+</t>
+  </si>
+  <si>
+    <t>Todas jornadas finalizadas
+Todas as jornadas revisadas</t>
+  </si>
+  <si>
+    <t>Aguardando validação AME</t>
   </si>
 </sst>
 </file>
@@ -1784,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1799,19 +1712,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1829,7 +1742,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1838,16 +1751,16 @@
         <v>73</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="V1" s="13" t="s">
         <v>74</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="116" x14ac:dyDescent="0.35">
@@ -1858,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>43</v>
@@ -1873,13 +1786,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1893,28 +1806,27 @@
       <c r="N2" s="10">
         <v>45838</v>
       </c>
-      <c r="O2" s="10">
-        <v>46435</v>
-      </c>
+      <c r="O2" s="10"/>
       <c r="P2" s="10">
-        <v>46283</v>
+        <v>46304</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="R2" s="3"/>
       <c r="S2" s="3" t="s">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1925,10 +1837,10 @@
         <v>68</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>56</v>
@@ -1940,13 +1852,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1967,20 +1879,20 @@
         <v>46286</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1991,7 +1903,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>46</v>
@@ -2006,13 +1918,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>233</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>269</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -2030,27 +1942,27 @@
         <v>46421</v>
       </c>
       <c r="P4" s="10">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="159.5" x14ac:dyDescent="0.35">
@@ -2061,10 +1973,10 @@
         <v>57</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>58</v>
@@ -2076,10 +1988,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="7">
@@ -2099,26 +2011,26 @@
         <v>46287</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2142,13 +2054,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2169,22 +2081,22 @@
         <v>46286</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2208,13 +2120,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2235,22 +2147,22 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2261,13 +2173,13 @@
         <v>70</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2276,13 +2188,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2303,20 +2215,20 @@
         <v>46293</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2324,11 +2236,11 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>67</v>
@@ -2340,13 +2252,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2363,24 +2275,24 @@
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>302</v>
+        <v>264</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2392,7 +2304,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>64</v>
@@ -2404,13 +2316,13 @@
         <v>33</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2426,27 +2338,27 @@
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="8">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
@@ -2454,7 +2366,7 @@
         <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
@@ -2470,13 +2382,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2497,22 +2409,22 @@
         <v>45915</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2520,14 +2432,14 @@
         <v>55</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>34</v>
@@ -2536,9 +2448,7 @@
         <v>34</v>
       </c>
       <c r="H12" s="16"/>
-      <c r="I12" s="9" t="s">
-        <v>247</v>
-      </c>
+      <c r="I12" s="9"/>
       <c r="J12" s="15"/>
       <c r="K12" s="9">
         <v>100</v>
@@ -2555,21 +2465,21 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
       <c r="W12" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -2582,9 +2492,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="16"/>
-      <c r="I13" s="9" t="s">
-        <v>248</v>
-      </c>
+      <c r="I13" s="9"/>
       <c r="J13" s="15"/>
       <c r="K13" s="9">
         <v>100</v>
@@ -2601,25 +2509,25 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>34</v>
@@ -2628,9 +2536,7 @@
         <v>34</v>
       </c>
       <c r="H14" s="16"/>
-      <c r="I14" s="9" t="s">
-        <v>249</v>
-      </c>
+      <c r="I14" s="9"/>
       <c r="J14" s="15"/>
       <c r="K14" s="9">
         <v>100</v>
@@ -2647,25 +2553,25 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
@@ -2674,9 +2580,7 @@
         <v>34</v>
       </c>
       <c r="H15" s="16"/>
-      <c r="I15" s="9" t="s">
-        <v>250</v>
-      </c>
+      <c r="I15" s="9"/>
       <c r="J15" s="15"/>
       <c r="K15" s="9">
         <v>100</v>
@@ -2693,22 +2597,22 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
@@ -2720,9 +2624,7 @@
         <v>34</v>
       </c>
       <c r="H16" s="16"/>
-      <c r="I16" s="9" t="s">
-        <v>251</v>
-      </c>
+      <c r="I16" s="9"/>
       <c r="J16" s="15"/>
       <c r="K16" s="9">
         <v>100</v>
@@ -2739,18 +2641,18 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
       <c r="W16" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="7"/>
@@ -2764,9 +2666,7 @@
         <v>34</v>
       </c>
       <c r="H17" s="16"/>
-      <c r="I17" s="9" t="s">
-        <v>252</v>
-      </c>
+      <c r="I17" s="9"/>
       <c r="J17" s="15"/>
       <c r="K17" s="9">
         <v>100</v>
@@ -2783,22 +2683,22 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
       <c r="W17" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>56</v>
@@ -2810,9 +2710,7 @@
         <v>34</v>
       </c>
       <c r="H18" s="16"/>
-      <c r="I18" s="9" t="s">
-        <v>253</v>
-      </c>
+      <c r="I18" s="9"/>
       <c r="J18" s="15"/>
       <c r="K18" s="9">
         <v>100</v>
@@ -2829,21 +2727,21 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -2856,9 +2754,7 @@
         <v>34</v>
       </c>
       <c r="H19" s="16"/>
-      <c r="I19" s="9" t="s">
-        <v>254</v>
-      </c>
+      <c r="I19" s="9"/>
       <c r="J19" s="15"/>
       <c r="K19" s="9">
         <v>100</v>
@@ -2875,24 +2771,24 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
       <c r="W19" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="261" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>56</v>
@@ -2904,9 +2800,7 @@
         <v>34</v>
       </c>
       <c r="H20" s="16"/>
-      <c r="I20" s="9" t="s">
-        <v>255</v>
-      </c>
+      <c r="I20" s="9"/>
       <c r="J20" s="15"/>
       <c r="K20" s="9">
         <v>100</v>
@@ -2923,25 +2817,25 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
       <c r="W20" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
@@ -2950,9 +2844,7 @@
         <v>34</v>
       </c>
       <c r="H21" s="16"/>
-      <c r="I21" s="9" t="s">
-        <v>256</v>
-      </c>
+      <c r="I21" s="9"/>
       <c r="J21" s="15"/>
       <c r="K21" s="9">
         <v>100</v>
@@ -2969,25 +2861,25 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
       <c r="W21" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>34</v>
@@ -2996,9 +2888,7 @@
         <v>34</v>
       </c>
       <c r="H22" s="16"/>
-      <c r="I22" s="9" t="s">
-        <v>257</v>
-      </c>
+      <c r="I22" s="9"/>
       <c r="J22" s="15"/>
       <c r="K22" s="9">
         <v>100</v>
@@ -3015,25 +2905,25 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>34</v>
@@ -3042,9 +2932,7 @@
         <v>34</v>
       </c>
       <c r="H23" s="16"/>
-      <c r="I23" s="9" t="s">
-        <v>258</v>
-      </c>
+      <c r="I23" s="9"/>
       <c r="J23" s="15"/>
       <c r="K23" s="9">
         <v>100</v>
@@ -3061,18 +2949,18 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="7" t="s">
@@ -3088,9 +2976,7 @@
         <v>34</v>
       </c>
       <c r="H24" s="16"/>
-      <c r="I24" s="9" t="s">
-        <v>259</v>
-      </c>
+      <c r="I24" s="9"/>
       <c r="J24" s="15"/>
       <c r="K24" s="9">
         <v>100</v>
@@ -3107,18 +2993,18 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
       <c r="W24" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="7"/>
@@ -3132,9 +3018,7 @@
         <v>34</v>
       </c>
       <c r="H25" s="16"/>
-      <c r="I25" s="9" t="s">
-        <v>260</v>
-      </c>
+      <c r="I25" s="9"/>
       <c r="J25" s="15"/>
       <c r="K25" s="9">
         <v>100</v>
@@ -3151,25 +3035,25 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>34</v>
@@ -3178,9 +3062,7 @@
         <v>34</v>
       </c>
       <c r="H26" s="16"/>
-      <c r="I26" s="9" t="s">
-        <v>261</v>
-      </c>
+      <c r="I26" s="9"/>
       <c r="J26" s="15"/>
       <c r="K26" s="9">
         <v>100</v>
@@ -3197,25 +3079,25 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
       <c r="W26" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>34</v>
@@ -3224,9 +3106,7 @@
         <v>34</v>
       </c>
       <c r="H27" s="16"/>
-      <c r="I27" s="9" t="s">
-        <v>262</v>
-      </c>
+      <c r="I27" s="9"/>
       <c r="J27" s="15"/>
       <c r="K27" s="9">
         <v>100</v>
@@ -3243,25 +3123,25 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
       <c r="W27" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>34</v>
@@ -3270,9 +3150,7 @@
         <v>34</v>
       </c>
       <c r="H28" s="16"/>
-      <c r="I28" s="9" t="s">
-        <v>263</v>
-      </c>
+      <c r="I28" s="9"/>
       <c r="J28" s="15"/>
       <c r="K28" s="9">
         <v>100</v>
@@ -3289,22 +3167,22 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>44</v>
@@ -3316,9 +3194,7 @@
         <v>34</v>
       </c>
       <c r="H29" s="16"/>
-      <c r="I29" s="9" t="s">
-        <v>264</v>
-      </c>
+      <c r="I29" s="9"/>
       <c r="J29" s="15"/>
       <c r="K29" s="9">
         <v>100</v>
@@ -3335,21 +3211,21 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
       <c r="W29" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
@@ -3362,9 +3238,7 @@
         <v>34</v>
       </c>
       <c r="H30" s="16"/>
-      <c r="I30" s="9" t="s">
-        <v>265</v>
-      </c>
+      <c r="I30" s="9"/>
       <c r="J30" s="15"/>
       <c r="K30" s="9">
         <v>100</v>
@@ -3381,21 +3255,21 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
       <c r="W30" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
@@ -3408,9 +3282,7 @@
         <v>34</v>
       </c>
       <c r="H31" s="16"/>
-      <c r="I31" s="9" t="s">
-        <v>266</v>
-      </c>
+      <c r="I31" s="9"/>
       <c r="J31" s="15"/>
       <c r="K31" s="9">
         <v>100</v>
@@ -3427,25 +3299,25 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>34</v>
@@ -3454,9 +3326,7 @@
         <v>34</v>
       </c>
       <c r="H32" s="16"/>
-      <c r="I32" s="9" t="s">
-        <v>267</v>
-      </c>
+      <c r="I32" s="9"/>
       <c r="J32" s="15"/>
       <c r="K32" s="9">
         <v>100</v>
@@ -3473,24 +3343,24 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>58</v>
@@ -3502,9 +3372,7 @@
         <v>34</v>
       </c>
       <c r="H33" s="16"/>
-      <c r="I33" s="9" t="s">
-        <v>267</v>
-      </c>
+      <c r="I33" s="9"/>
       <c r="J33" s="15"/>
       <c r="K33" s="9">
         <v>100</v>
@@ -3521,10 +3389,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="3" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3600,7 +3468,7 @@
           <x14:formula1>
             <xm:f>Listas!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:I33 J2:J5 J9:J33</xm:sqref>
+          <xm:sqref>J9:J33 J2:J5 G2:I33</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3755,6 +3623,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3995,27 +3883,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4034,25 +3921,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp-my.sharepoint.com/personal/gerson_motta_detran_sp_gov_br/Documents/Area de Trabalho/Documentos/GERSON MOTTA/OBSIDIAN/antigravity-skills/00_Projetos/PAINEL-de-PROJETOS-V2-NETLIFY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerson.motta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="861" documentId="13_ncr:1_{8C8DD3CA-0FB3-47A1-8FFE-7A24820C7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D9A9C2-B123-41F5-8680-CB09172E2195}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42DF245-900F-4B4B-B48B-86252EFB40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,10 +711,6 @@
 Transmitir ao cidadão a eficiência e a confiança nos serviços.
 Transmitir o conceito disponibilidade do Detran-SP em atender o cidadão.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.</t>
   </si>
   <si>
     <t>DCI</t>
@@ -1183,6 +1179,17 @@
   </si>
   <si>
     <t>Aguardando validação AME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
+Primeira Habilitação
+Renovação da CNH
+Live2.0
+Autorização de Transporte Escolar (ATE)
+Gestão de Procuração 2.0
+Emplacar Veículo OKM
+Novo APP DETRAN-SP</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1234,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1237,6 +1244,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF183B56"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1305,7 +1318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1346,24 +1359,42 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1715,16 +1746,16 @@
         <v>146</v>
       </c>
       <c r="I1" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1742,7 +1773,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1770,7 +1801,7 @@
       <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>154</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1785,14 +1816,14 @@
       <c r="G2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>271</v>
+      <c r="H2" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>233</v>
+        <v>267</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>232</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1811,22 +1842,22 @@
         <v>46304</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>90</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1836,7 +1867,7 @@
       <c r="B3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>160</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1851,14 +1882,14 @@
       <c r="G3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>242</v>
+      <c r="H3" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>241</v>
+        <v>267</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>240</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1876,7 +1907,7 @@
         <v>46377</v>
       </c>
       <c r="P3" s="10">
-        <v>46286</v>
+        <v>46303</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>84</v>
@@ -1889,10 +1920,10 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1902,7 +1933,7 @@
       <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="15" t="s">
         <v>157</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1917,14 +1948,14 @@
       <c r="G4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>228</v>
+      <c r="H4" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>233</v>
+        <v>267</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>232</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -1945,17 +1976,17 @@
         <v>46303</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
@@ -1972,7 +2003,7 @@
       <c r="B5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>159</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -1987,13 +2018,13 @@
       <c r="G5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>147</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J5" s="15"/>
+        <v>267</v>
+      </c>
+      <c r="J5" s="14"/>
       <c r="K5" s="7">
         <v>53</v>
       </c>
@@ -2008,7 +2039,7 @@
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8">
-        <v>46287</v>
+        <v>46304</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>80</v>
@@ -2030,7 +2061,7 @@
         <v>93</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2053,14 +2084,14 @@
       <c r="G6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>253</v>
+      <c r="H6" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>234</v>
+        <v>267</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>233</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2081,10 +2112,10 @@
         <v>46286</v>
       </c>
       <c r="Q6" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
@@ -2119,14 +2150,14 @@
       <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>224</v>
+      <c r="H7" s="14" t="s">
+        <v>223</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>249</v>
+        <v>267</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2147,13 +2178,13 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
@@ -2162,7 +2193,7 @@
         <v>96</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2172,14 +2203,14 @@
       <c r="B8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>160</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2187,14 +2218,14 @@
       <c r="G8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="15" t="s">
-        <v>230</v>
+      <c r="H8" s="14" t="s">
+        <v>229</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>258</v>
+        <v>267</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>257</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2214,11 +2245,11 @@
       <c r="P8" s="8">
         <v>46293</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
@@ -2228,7 +2259,7 @@
         <v>97</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2236,7 +2267,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
@@ -2251,14 +2282,14 @@
       <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>261</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>262</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2275,24 +2306,24 @@
         <v>46288</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>98</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2315,14 +2346,14 @@
       <c r="G10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="14" t="s">
         <v>148</v>
       </c>
       <c r="I10" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>269</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2341,10 +2372,10 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>75</v>
@@ -2355,7 +2386,7 @@
         <v>76</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>99</v>
@@ -2381,14 +2412,14 @@
       <c r="G11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>266</v>
+      <c r="H11" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>235</v>
+        <v>267</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>234</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2406,7 +2437,7 @@
         <v>46461</v>
       </c>
       <c r="P11" s="8">
-        <v>45915</v>
+        <v>45939</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>100</v>
@@ -2418,981 +2449,981 @@
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="9">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="21">
         <v>100</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="3" t="s">
+      <c r="L12" s="21"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="X12" s="24" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="9">
+      <c r="F13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="18"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="21">
         <v>100</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="X13" s="3" t="s">
+      <c r="L13" s="21"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="X13" s="24" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="9">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="21">
         <v>100</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="3" t="s">
+      <c r="L14" s="21"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="24" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="9">
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="21">
         <v>100</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="X15" s="3" t="s">
+      <c r="L15" s="21"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="X15" s="24" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="C16" s="23"/>
+      <c r="D16" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="9">
+      <c r="F16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="21">
         <v>100</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="X16" s="3" t="s">
+      <c r="L16" s="21"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="X16" s="24" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7" t="s">
+      <c r="C17" s="23"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="9">
+      <c r="F17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="21">
         <v>100</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="X17" s="3" t="s">
+      <c r="L17" s="21"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="X17" s="24" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="9">
+      <c r="F18" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="21">
         <v>100</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="X18" s="3" t="s">
+      <c r="L18" s="21"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="X18" s="24" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7" t="s">
+      <c r="D19" s="20"/>
+      <c r="E19" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="9">
+      <c r="F19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="21">
         <v>100</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="X19" s="3" t="s">
+      <c r="L19" s="21"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="X19" s="24" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="261" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="D20" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="9">
+      <c r="F20" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="21">
         <v>100</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="X20" s="3" t="s">
+      <c r="L20" s="21"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="23"/>
+      <c r="W20" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="X20" s="24" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="9">
+      <c r="C21" s="23"/>
+      <c r="D21" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="21">
         <v>100</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="X21" s="3" t="s">
+      <c r="L21" s="21"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="X21" s="24" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="9">
+      <c r="D22" s="20"/>
+      <c r="E22" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="21">
         <v>100</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="X22" s="3" t="s">
+      <c r="L22" s="21"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="X22" s="24" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="9">
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="21">
         <v>100</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="X23" s="3" t="s">
+      <c r="L23" s="21"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="X23" s="24" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="7" t="s">
+      <c r="C24" s="23"/>
+      <c r="D24" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="9">
+      <c r="F24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="21">
         <v>100</v>
       </c>
-      <c r="L24" s="9"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="X24" s="3" t="s">
+      <c r="L24" s="21"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="X24" s="24" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7" t="s">
+      <c r="C25" s="23"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="9">
+      <c r="F25" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="21">
         <v>100</v>
       </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="X25" s="3" t="s">
+      <c r="L25" s="21"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="X25" s="24" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="9">
+      <c r="D26" s="20"/>
+      <c r="E26" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="21">
         <v>100</v>
       </c>
-      <c r="L26" s="9"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="X26" s="3" t="s">
+      <c r="L26" s="21"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="X26" s="24" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="23"/>
+      <c r="D27" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27" s="16"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="9">
+      <c r="E27" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="18"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="21">
         <v>100</v>
       </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="X27" s="3" t="s">
+      <c r="L27" s="21"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="X27" s="24" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="16"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="9">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="21">
         <v>100</v>
       </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="X28" s="3" t="s">
+      <c r="L28" s="21"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="X28" s="24" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="C29" s="23"/>
+      <c r="D29" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="9">
+      <c r="F29" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="21">
         <v>100</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="L29" s="21"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="X29" s="24" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7" t="s">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="9">
+      <c r="F30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="21">
         <v>100</v>
       </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="X30" s="3" t="s">
+      <c r="L30" s="21"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="X30" s="24" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7" t="s">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="9">
+      <c r="F31" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="18"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="21">
         <v>100</v>
       </c>
-      <c r="L31" s="9"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X31" s="3" t="s">
+      <c r="L31" s="21"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="X31" s="24" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="9">
+      <c r="D32" s="20"/>
+      <c r="E32" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="21">
         <v>100</v>
       </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="X32" s="3" t="s">
+      <c r="L32" s="21"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="X32" s="24" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="C33" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="21">
+        <v>100</v>
+      </c>
+      <c r="L33" s="21"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="23"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="9">
-        <v>100</v>
-      </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="3" t="s">
+      <c r="X33" s="24" t="s">
         <v>238</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3632,17 +3663,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3883,6 +3903,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
@@ -3892,17 +3923,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3921,6 +3941,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerson.motta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42DF245-900F-4B4B-B48B-86252EFB40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EEA10B-4AE8-40B4-99A0-9D55084ADC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2243,7 +2243,7 @@
         <v>46379</v>
       </c>
       <c r="P8" s="8">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="Q8" s="14" t="s">
         <v>258</v>
@@ -3663,6 +3663,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3903,17 +3914,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
@@ -3923,6 +3923,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3941,17 +3952,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerson.motta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EEA10B-4AE8-40B4-99A0-9D55084ADC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B866C7-CECE-4727-92CE-41CA211F7FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="277">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -1178,9 +1178,6 @@
 Todas as jornadas revisadas</t>
   </si>
   <si>
-    <t>Aguardando validação AME</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
 Primeira Habilitação
@@ -1190,6 +1187,12 @@
 Gestão de Procuração 2.0
 Emplacar Veículo OKM
 Novo APP DETRAN-SP</t>
+  </si>
+  <si>
+    <t>Introduzir os analistas na fase 2 utilizando a ferramenta VSM</t>
+  </si>
+  <si>
+    <t>Aguardando validações e feedback</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1923,7 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>194</v>
@@ -2106,18 +2109,20 @@
         <v>46351</v>
       </c>
       <c r="O6" s="8">
-        <v>46351</v>
+        <v>46373</v>
       </c>
       <c r="P6" s="8">
-        <v>46286</v>
+        <v>46304</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>273</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="S6" s="3"/>
+        <v>275</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="T6" s="6"/>
       <c r="U6" s="3" t="s">
         <v>103</v>
@@ -2303,7 +2308,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8">
-        <v>46288</v>
+        <v>46303</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>215</v>
@@ -3663,17 +3668,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3914,6 +3908,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
@@ -3923,17 +3928,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3952,6 +3946,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerson.motta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B866C7-CECE-4727-92CE-41CA211F7FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -717,14 +717,6 @@
   </si>
   <si>
     <t>DHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de Conhecimento
-Sistema de Atendimento
-Agente OCR de documentos de credenciamento
-Agente Q&amp;A da Wiki ("Isa")
-Agente Revisor de conteúdo da Wiki
-</t>
   </si>
   <si>
     <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
@@ -1193,6 +1185,14 @@
   </si>
   <si>
     <t>Aguardando validações e feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de Conhecimento - Wave 0
+Sistema de Atendimento - Wave 0
+Agente OCR de documentos de credenciamento - Wave 1
+Agente Q&amp;A da Wiki ("Isa") - Wave 2
+Agente Revisor de conteúdo da Wiki - Wave 3
+</t>
   </si>
 </sst>
 </file>
@@ -1749,16 +1749,16 @@
         <v>146</v>
       </c>
       <c r="I1" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>231</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1776,7 +1776,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1820,13 +1820,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K2" s="9">
         <v>79</v>
@@ -1845,22 +1845,22 @@
         <v>46304</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>90</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
@@ -1886,13 +1886,13 @@
         <v>13</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K3" s="9">
         <v>75</v>
@@ -1923,10 +1923,10 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -1952,13 +1952,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K4" s="9">
         <v>92</v>
@@ -1979,17 +1979,17 @@
         <v>46303</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
@@ -2025,7 +2025,7 @@
         <v>147</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="7">
@@ -2064,7 +2064,7 @@
         <v>93</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2088,13 +2088,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K6" s="7">
         <v>90</v>
@@ -2115,13 +2115,13 @@
         <v>46304</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="3" t="s">
@@ -2156,13 +2156,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K7" s="7">
         <v>70</v>
@@ -2183,13 +2183,13 @@
         <v>46300</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="3"/>
@@ -2198,7 +2198,7 @@
         <v>96</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2215,7 +2215,7 @@
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2224,13 +2224,13 @@
         <v>13</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K8" s="7">
         <v>93</v>
@@ -2251,10 +2251,10 @@
         <v>46300</v>
       </c>
       <c r="Q8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="6"/>
@@ -2264,7 +2264,7 @@
         <v>97</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -2272,7 +2272,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
@@ -2288,13 +2288,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>260</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>261</v>
       </c>
       <c r="K9" s="7">
         <v>99</v>
@@ -2311,24 +2311,24 @@
         <v>46303</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>98</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2355,10 +2355,10 @@
         <v>148</v>
       </c>
       <c r="I10" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>268</v>
       </c>
       <c r="K10" s="7">
         <v>50</v>
@@ -2377,10 +2377,10 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>75</v>
@@ -2391,7 +2391,7 @@
         <v>76</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>99</v>
@@ -2418,13 +2418,13 @@
         <v>13</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K11" s="7">
         <v>15</v>
@@ -2454,13 +2454,13 @@
       <c r="T11" s="6"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>34</v>
@@ -2545,7 +2545,7 @@
       <c r="U13" s="23"/>
       <c r="V13" s="23"/>
       <c r="W13" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X13" s="24" t="s">
         <v>164</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>34</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -2633,7 +2633,7 @@
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X15" s="24" t="s">
         <v>166</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>60</v>
@@ -2677,7 +2677,7 @@
       <c r="U16" s="23"/>
       <c r="V16" s="23"/>
       <c r="W16" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X16" s="24" t="s">
         <v>167</v>
@@ -2719,7 +2719,7 @@
       <c r="U17" s="23"/>
       <c r="V17" s="23"/>
       <c r="W17" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X17" s="24" t="s">
         <v>168</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C18" s="23"/>
       <c r="D18" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>56</v>
@@ -2763,7 +2763,7 @@
       <c r="U18" s="23"/>
       <c r="V18" s="23"/>
       <c r="W18" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X18" s="24" t="s">
         <v>169</v>
@@ -2807,7 +2807,7 @@
       <c r="U19" s="23"/>
       <c r="V19" s="23"/>
       <c r="W19" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X19" s="24" t="s">
         <v>170</v>
@@ -2824,7 +2824,7 @@
         <v>156</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>56</v>
@@ -2853,7 +2853,7 @@
       <c r="U20" s="23"/>
       <c r="V20" s="23"/>
       <c r="W20" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X20" s="24" t="s">
         <v>171</v>
@@ -2868,10 +2868,10 @@
       </c>
       <c r="C21" s="23"/>
       <c r="D21" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>34</v>
@@ -2897,7 +2897,7 @@
       <c r="U21" s="23"/>
       <c r="V21" s="23"/>
       <c r="W21" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X21" s="24" t="s">
         <v>172</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>34</v>
@@ -2941,7 +2941,7 @@
       <c r="U22" s="23"/>
       <c r="V22" s="23"/>
       <c r="W22" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X22" s="24" t="s">
         <v>173</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>34</v>
@@ -2985,7 +2985,7 @@
       <c r="U23" s="23"/>
       <c r="V23" s="23"/>
       <c r="W23" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X23" s="24" t="s">
         <v>174</v>
@@ -3029,7 +3029,7 @@
       <c r="U24" s="23"/>
       <c r="V24" s="23"/>
       <c r="W24" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X24" s="24" t="s">
         <v>175</v>
@@ -3071,7 +3071,7 @@
       <c r="U25" s="23"/>
       <c r="V25" s="23"/>
       <c r="W25" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X25" s="24" t="s">
         <v>176</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>34</v>
@@ -3115,7 +3115,7 @@
       <c r="U26" s="23"/>
       <c r="V26" s="23"/>
       <c r="W26" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X26" s="24" t="s">
         <v>177</v>
@@ -3159,7 +3159,7 @@
       <c r="U27" s="23"/>
       <c r="V27" s="23"/>
       <c r="W27" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X27" s="24" t="s">
         <v>178</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>34</v>
@@ -3203,7 +3203,7 @@
       <c r="U28" s="23"/>
       <c r="V28" s="23"/>
       <c r="W28" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X28" s="24" t="s">
         <v>179</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>44</v>
@@ -3247,7 +3247,7 @@
       <c r="U29" s="23"/>
       <c r="V29" s="23"/>
       <c r="W29" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X29" s="24" t="s">
         <v>180</v>
@@ -3291,7 +3291,7 @@
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
       <c r="W30" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X30" s="24" t="s">
         <v>181</v>
@@ -3335,7 +3335,7 @@
       <c r="U31" s="23"/>
       <c r="V31" s="23"/>
       <c r="W31" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X31" s="24" t="s">
         <v>182</v>
@@ -3379,7 +3379,7 @@
       <c r="U32" s="23"/>
       <c r="V32" s="23"/>
       <c r="W32" s="24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X32" s="24" t="s">
         <v>183</v>
@@ -3387,16 +3387,16 @@
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>236</v>
-      </c>
       <c r="C33" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>58</v>
@@ -3425,10 +3425,10 @@
       <c r="U33" s="23"/>
       <c r="V33" s="23"/>
       <c r="W33" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="X33" s="24" t="s">
         <v>237</v>
-      </c>
-      <c r="X33" s="24" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3668,6 +3668,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3908,17 +3919,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
@@ -3928,6 +3928,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3946,17 +3957,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -5,26 +5,39 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerson.motta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B64915A-19CB-4437-BC01-14C6E762B6FB}"/>
   <bookViews>
-    <workbookView xWindow="13185" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
     <sheet name="Listas" sheetId="10" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Projetos!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Projetos!$A$1:$X$33</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="280">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -249,12 +262,6 @@
   </si>
   <si>
     <t>Riscos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best - sem previsão
-Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
-Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
-</t>
   </si>
   <si>
     <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
@@ -285,23 +292,6 @@
   <si>
     <t>Risco de impacto no cronograma de implantação, caso haja prolongamento das etapas de contratação dos projetos, obra e serviços.
 Considerando o caráter piloto da Estaiadinha, eventual atraso também poderá repercutir na validação prática das soluções e na consolidação do padrão para expansão do Habilita SP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Após apresentação do Protótipo Renovação de CNH, ajustando os requisitos funcionais e Protótipo
-Continuando QA e homologação Portal do cidadão
-CSM homologado 27/08
-Desenvolvimento Live 2.0 com previsão de implantação para 03/11
-Entregeue MVP, com os seguintes serviços: Licenciamento, Pesquisa de Peças, Consulta Débitos e Restrições, Pagamento de Vistorias e TDV (todas)
-Plataforma de vistorias em Homologações com Integradoras e Auditoras em andamento
-</t>
-  </si>
-  <si>
-    <t>Disponibilizar nova versão renovação de CNH para validação da área de negócio
-DTI, na entrega Live 2.0, está fazendo a manuntenção do SISPL com previsão de implantação da API para 24/11
-Homologação até 01/09 app Serviços CSM
-Plataforma de vistorias em Homologações com Integradoras e Auditoras seguem em validação
-Portal do Cidadão QA e Homologação
-Programar subida em produção app Serviços CSM</t>
   </si>
   <si>
     <t>Pendências</t>
@@ -514,12 +504,6 @@
     <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura.
 Desenhos técnicos necessários para contratação disponibilizados desde julho/2026.
 </t>
-  </si>
-  <si>
-    <t>Projeto apresenta significativo atraso e não há previsão para o término:
-Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best - sem previsão
-Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
-Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão</t>
   </si>
   <si>
     <t>Portaria</t>
@@ -1002,15 +986,6 @@
   </si>
   <si>
     <t>Portaria DETRAN-SP nº 4.429, de 17 de julho de 2024</t>
-  </si>
-  <si>
-    <t>LIVE 2.0: Foi concluído a obtenção de credenciais e validação de CPF, a assinatura digital, a disponibilização do ofício com o código de liberação e a execução da rotina de expiração de documentos vencidos para garantir a conformidade.
-Serviços CSM no APP: 1° lote de 9 formulários CSM, foram desenvolvidos e validados</t>
-  </si>
-  <si>
-    <t>Live 1.0 - entregue
-Consulta de peças - entregue
-Serviços CSM no app e live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
     <t>Norma Gregório</t>
@@ -1146,11 +1121,6 @@
 </t>
   </si>
   <si>
-    <t>Capacitação em prompts - 19/10/2026
-Agente OCR de Documentos de Credenciamento - integração com o portal - 27/10/2026
-Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
-  </si>
-  <si>
     <t>Mudança de estratégia : 
 Decisão de entrar na licitação da PRF para aquisição das câmeras corporais.
 Dependência de licitação a ser realizada por outro órgão.
@@ -1168,6 +1138,65 @@
   <si>
     <t>Todas jornadas finalizadas
 Todas as jornadas revisadas</t>
+  </si>
+  <si>
+    <t>Introduzir os analistas na fase 2 utilizando a ferramenta VSM</t>
+  </si>
+  <si>
+    <t>Aguardando validações e feedback</t>
+  </si>
+  <si>
+    <t>Projeto apresenta significativo atraso e não há previsão para o término:
+Agente OCR
+Treinamento - 19/10
+Homologação - 20/10
+GMUD - 27/10
+Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best 
+GMUD - 06/11
+Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
+Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão</t>
+  </si>
+  <si>
+    <t>Capacitação em prompts - 19/10/2026
+Agente OCR de Documentos de Credenciamento - integração com o portal -
+Treinamento - 19/10/2026
+Homologação - 20/10/2026
+GMUD - 27/10/2026
+Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
+Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de Conhecimento
+Sistema de Atendimento
+Agente OCR de documentos de credenciamento
+Agente Q&amp;A da Wiki ("Isa")
+Agente Revisor de conteúdo da Wiki
+</t>
+  </si>
+  <si>
+    <t>Live 1.0 - entregue
+Consulta de peças - entregue
+Plataforma estadual de vistorias e Live 2.0 em andamento sem impeditivos</t>
+  </si>
+  <si>
+    <t>13/10/2026 a 16/10/2026</t>
+  </si>
+  <si>
+    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
+Plataforma estadual de vistoria: Implantação assistida.
+Emplacar Veículo 0KM realizado o Kickoff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo app segue em fase de testes.
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
+Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) </t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1177,29 +1206,26 @@
 Live2.0
 Autorização de Transporte Escolar (ATE)
 Gestão de Procuração 2.0
-Emplacar Veículo OKM
+Emplacar Veículo 0Km
 Novo APP DETRAN-SP</t>
   </si>
   <si>
-    <t>Introduzir os analistas na fase 2 utilizando a ferramenta VSM</t>
-  </si>
-  <si>
-    <t>Aguardando validações e feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de Conhecimento - Wave 0
-Sistema de Atendimento - Wave 0
-Agente OCR de documentos de credenciamento - Wave 1
-Agente Q&amp;A da Wiki ("Isa") - Wave 2
-Agente Revisor de conteúdo da Wiki - Wave 3
-</t>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Emplacar Veículo 0Km: Chaintec não forneceu cronograma de desenvolvimento.</t>
+  </si>
+  <si>
+    <t>Não tiveram atualizações:
+Autorização de Transporte Escolar (ATE): Aguardando contratação de fornecedor de desenvolvimento.
+Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1230,6 +1256,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1317,11 +1350,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1368,9 +1402,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1393,16 +1424,23 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1706,21 +1744,21 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="35.6328125" customWidth="1"/>
-    <col min="3" max="3" width="55.6328125" customWidth="1"/>
+    <col min="2" max="2" width="35.54296875" customWidth="1"/>
+    <col min="3" max="3" width="55.54296875" customWidth="1"/>
     <col min="4" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.6328125" customWidth="1"/>
-    <col min="9" max="9" width="25.6328125" customWidth="1"/>
-    <col min="10" max="10" width="40.6328125" customWidth="1"/>
+    <col min="8" max="8" width="40.54296875" customWidth="1"/>
+    <col min="9" max="9" width="25.54296875" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.6328125" customWidth="1"/>
-    <col min="23" max="23" width="50.6328125" customWidth="1"/>
-    <col min="24" max="24" width="120.6328125" customWidth="1"/>
+    <col min="17" max="22" width="40.54296875" customWidth="1"/>
+    <col min="23" max="23" width="50.54296875" customWidth="1"/>
+    <col min="24" max="24" width="120.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1731,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1746,19 +1784,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1776,7 +1814,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1785,301 +1823,234 @@
         <v>73</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="V1" s="13" t="s">
         <v>74</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="116" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K2" s="9">
-        <v>79</v>
-      </c>
-      <c r="L2" s="9">
+    <row r="2" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="20">
         <v>100</v>
       </c>
-      <c r="M2" s="10">
-        <v>45407</v>
-      </c>
-      <c r="N2" s="10">
-        <v>45838</v>
-      </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10">
-        <v>46304</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>188</v>
+      <c r="L2" s="20"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="X2" s="23" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="20">
+        <v>100</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="X3" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="C4" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="K3" s="9">
-        <v>75</v>
-      </c>
-      <c r="L3" s="9">
-        <v>82</v>
-      </c>
-      <c r="M3" s="10">
-        <v>45555</v>
-      </c>
-      <c r="N3" s="10">
-        <v>46370</v>
-      </c>
-      <c r="O3" s="10">
-        <v>46377</v>
-      </c>
-      <c r="P3" s="10">
-        <v>46303</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="145" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="K4" s="9">
-        <v>92</v>
-      </c>
-      <c r="L4" s="9">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="L4" s="27">
+        <f ca="1">(TODAY()-M4)/(N4-M4)</f>
+        <v>0.92638036809815949</v>
       </c>
       <c r="M4" s="10">
-        <v>45511</v>
+        <v>45555</v>
       </c>
       <c r="N4" s="10">
-        <v>45699</v>
+        <v>46370</v>
       </c>
       <c r="O4" s="10">
-        <v>46421</v>
+        <v>46377</v>
       </c>
       <c r="P4" s="10">
         <v>46303</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>91</v>
+        <v>277</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="7">
-        <v>53</v>
-      </c>
-      <c r="L5" s="9">
+    <row r="5" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="20">
         <v>100</v>
       </c>
-      <c r="M5" s="8">
-        <v>45659</v>
-      </c>
-      <c r="N5" s="8">
-        <v>46045</v>
-      </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8">
-        <v>46304</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" s="6"/>
-      <c r="U5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>189</v>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="X5" s="23" t="s">
+        <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>12</v>
@@ -2088,1370 +2059,1447 @@
         <v>13</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K6" s="7">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="L6" s="7">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="M6" s="8">
-        <v>45901</v>
+        <v>46210</v>
       </c>
       <c r="N6" s="8">
-        <v>46351</v>
+        <v>46461</v>
       </c>
       <c r="O6" s="8">
-        <v>46373</v>
+        <v>46461</v>
       </c>
       <c r="P6" s="8">
+        <v>45939</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="261" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="20">
+        <v>100</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="20">
+        <v>100</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="X8" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="20">
+        <v>100</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="9">
+        <v>79</v>
+      </c>
+      <c r="L10" s="9">
+        <v>100</v>
+      </c>
+      <c r="M10" s="10">
+        <v>45407</v>
+      </c>
+      <c r="N10" s="10">
+        <v>45838</v>
+      </c>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10">
         <v>46304</v>
       </c>
-      <c r="Q6" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="145" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="K7" s="7">
-        <v>70</v>
-      </c>
-      <c r="L7" s="7">
-        <v>82</v>
-      </c>
-      <c r="M7" s="8">
-        <v>45938</v>
-      </c>
-      <c r="N7" s="8">
-        <v>46383</v>
-      </c>
-      <c r="O7" s="8">
-        <v>46365</v>
-      </c>
-      <c r="P7" s="8">
-        <v>46300</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="174" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="K8" s="7">
-        <v>93</v>
-      </c>
-      <c r="L8" s="7">
-        <v>100</v>
-      </c>
-      <c r="M8" s="8">
-        <v>45988</v>
-      </c>
-      <c r="N8" s="8">
-        <v>46204</v>
-      </c>
-      <c r="O8" s="8">
-        <v>46379</v>
-      </c>
-      <c r="P8" s="8">
-        <v>46300</v>
-      </c>
-      <c r="Q8" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="S8" s="3"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="203" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K9" s="7">
-        <v>99</v>
-      </c>
-      <c r="L9" s="7">
-        <v>100</v>
-      </c>
-      <c r="M9" s="8">
-        <v>46042</v>
-      </c>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8">
-        <v>46303</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="145" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="K10" s="7">
-        <v>50</v>
-      </c>
-      <c r="L10" s="7">
-        <v>100</v>
-      </c>
-      <c r="M10" s="8">
-        <v>46111</v>
-      </c>
-      <c r="N10" s="8">
-        <v>46187</v>
-      </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="8">
-        <v>46304</v>
-      </c>
       <c r="Q10" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>268</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="T10" s="6"/>
+        <v>264</v>
+      </c>
+      <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="7" t="s">
+    <row r="11" spans="1:24" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="20">
+        <v>100</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="X11" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J11" s="14" t="s">
+      <c r="G12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J12" s="14"/>
+      <c r="K12" s="7">
+        <v>53</v>
+      </c>
+      <c r="L12" s="9">
+        <v>100</v>
+      </c>
+      <c r="M12" s="8">
+        <v>45659</v>
+      </c>
+      <c r="N12" s="8">
+        <v>46045</v>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8">
+        <v>46304</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="T12" s="6"/>
+      <c r="U12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="20">
+        <v>100</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="X13" s="23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="20">
+        <v>100</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="X14" s="23" t="s">
         <v>233</v>
-      </c>
-      <c r="K11" s="7">
-        <v>15</v>
-      </c>
-      <c r="L11" s="7">
-        <v>36</v>
-      </c>
-      <c r="M11" s="8">
-        <v>46210</v>
-      </c>
-      <c r="N11" s="8">
-        <v>46461</v>
-      </c>
-      <c r="O11" s="8">
-        <v>46461</v>
-      </c>
-      <c r="P11" s="8">
-        <v>45939</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="S11" s="3"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="21">
-        <v>100</v>
-      </c>
-      <c r="L12" s="21"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="21">
-        <v>100</v>
-      </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="X13" s="24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="21">
-        <v>100</v>
-      </c>
-      <c r="L14" s="21"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="X14" s="24" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="21">
+      <c r="A15" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="20">
         <v>100</v>
       </c>
-      <c r="L15" s="21"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="X15" s="24" t="s">
-        <v>166</v>
+      <c r="L15" s="20"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="X15" s="23" t="s">
+        <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="E16" s="20" t="s">
+    <row r="16" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="K16" s="7">
+        <v>70</v>
+      </c>
+      <c r="L16" s="7">
+        <v>82</v>
+      </c>
+      <c r="M16" s="8">
+        <v>45938</v>
+      </c>
+      <c r="N16" s="8">
+        <v>46383</v>
+      </c>
+      <c r="O16" s="8">
+        <v>46365</v>
+      </c>
+      <c r="P16" s="8">
+        <v>46300</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="21">
+      <c r="F17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="K17" s="7">
+        <v>90</v>
+      </c>
+      <c r="L17" s="7">
+        <v>89</v>
+      </c>
+      <c r="M17" s="8">
+        <v>45901</v>
+      </c>
+      <c r="N17" s="8">
+        <v>46351</v>
+      </c>
+      <c r="O17" s="8">
+        <v>46373</v>
+      </c>
+      <c r="P17" s="8">
+        <v>46304</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="T17" s="6"/>
+      <c r="U17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L16" s="21"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="X16" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="21">
-        <v>100</v>
-      </c>
-      <c r="L17" s="21"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="X17" s="24" t="s">
-        <v>168</v>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="E18" s="20" t="s">
+      <c r="A18" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="21">
+      <c r="F18" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="20">
         <v>100</v>
       </c>
-      <c r="L18" s="21"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="24" t="s">
+      <c r="L18" s="20"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="X18" s="23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="20">
+        <v>100</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="X19" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="20">
+        <v>100</v>
+      </c>
+      <c r="L20" s="20"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="X20" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="20">
+        <v>100</v>
+      </c>
+      <c r="L21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="X21" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="K22" s="7">
+        <v>93</v>
+      </c>
+      <c r="L22" s="7">
+        <v>100</v>
+      </c>
+      <c r="M22" s="8">
+        <v>45988</v>
+      </c>
+      <c r="N22" s="8">
+        <v>46204</v>
+      </c>
+      <c r="O22" s="8">
+        <v>46379</v>
+      </c>
+      <c r="P22" s="8">
+        <v>46300</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="S22" s="3"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="232" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="K23" s="7">
+        <v>50</v>
+      </c>
+      <c r="L23" s="7">
+        <v>100</v>
+      </c>
+      <c r="M23" s="8">
+        <v>46111</v>
+      </c>
+      <c r="N23" s="8">
+        <v>46187</v>
+      </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="8">
+        <v>46304</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="T23" s="6"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="20">
+        <v>100</v>
+      </c>
+      <c r="L24" s="20"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="X24" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="20">
+        <v>100</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="X25" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="K26" s="7">
+        <v>99</v>
+      </c>
+      <c r="L26" s="7">
+        <v>100</v>
+      </c>
+      <c r="M26" s="8">
+        <v>46042</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8">
+        <v>46303</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="T26" s="6"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="K27" s="9">
+        <v>92</v>
+      </c>
+      <c r="L27" s="9">
+        <v>100</v>
+      </c>
+      <c r="M27" s="10">
+        <v>45511</v>
+      </c>
+      <c r="N27" s="10">
+        <v>45699</v>
+      </c>
+      <c r="O27" s="10">
+        <v>46421</v>
+      </c>
+      <c r="P27" s="10">
+        <v>46303</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+      <c r="A28" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="20">
+        <v>100</v>
+      </c>
+      <c r="L28" s="20"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="X28" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="20">
+        <v>100</v>
+      </c>
+      <c r="L29" s="20"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="X29" s="23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="20">
+        <v>100</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="X30" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="20">
+        <v>100</v>
+      </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="X31" s="23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="20">
+        <v>100</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="X18" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="21">
-        <v>100</v>
-      </c>
-      <c r="L19" s="21"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="X19" s="24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="261" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="21">
-        <v>100</v>
-      </c>
-      <c r="L20" s="21"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="X20" s="24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="21">
-        <v>100</v>
-      </c>
-      <c r="L21" s="21"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="X21" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="21">
-        <v>100</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="X22" s="24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="21">
-        <v>100</v>
-      </c>
-      <c r="L23" s="21"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="X23" s="24" t="s">
+      <c r="X32" s="23" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="21">
-        <v>100</v>
-      </c>
-      <c r="L24" s="21"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="X24" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="21">
-        <v>100</v>
-      </c>
-      <c r="L25" s="21"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="X25" s="24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" ht="58" x14ac:dyDescent="0.35">
-      <c r="A26" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="21">
-        <v>100</v>
-      </c>
-      <c r="L26" s="21"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="X26" s="24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A27" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="21">
-        <v>100</v>
-      </c>
-      <c r="L27" s="21"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="X27" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="21">
-        <v>100</v>
-      </c>
-      <c r="L28" s="21"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="X28" s="24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="21">
-        <v>100</v>
-      </c>
-      <c r="L29" s="21"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="X29" s="24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="21">
-        <v>100</v>
-      </c>
-      <c r="L30" s="21"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="X30" s="24" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" ht="87" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="21">
-        <v>100</v>
-      </c>
-      <c r="L31" s="21"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="X31" s="24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="21">
-        <v>100</v>
-      </c>
-      <c r="L32" s="21"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="X32" s="24" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="21">
+      <c r="A33" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="20">
         <v>100</v>
       </c>
-      <c r="L33" s="21"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="X33" s="24" t="s">
-        <v>237</v>
+      <c r="L33" s="20"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="X33" s="23" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X33" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X33">
+      <sortCondition ref="B1:B33"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C12" r:id="rId1" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=9f176a9e87d4b2d434a7c8840cbb355e" xr:uid="{D79240FC-BF31-4540-8E8B-37A1E8FCED1C}"/>
-    <hyperlink ref="C13" r:id="rId2" display="https://www.detran.sp.gov.br/detransp/pb/regulacao/normas/portaria-normativa-detran-sp-n%C2%BA-1-de-20-de-mar%C3%A7o-de-2023?id=ver_norma&amp;sys_kb_id=298ae6de8718b2d434a7c8840cbb35cb" xr:uid="{D4340E15-B784-4FF5-B32E-0FCA8B3FA484}"/>
-    <hyperlink ref="C14" r:id="rId3" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=2b182a168718b2d434a7c8840cbb3562" xr:uid="{E6FD3251-2445-410D-875D-2B466D4FF5BD}"/>
-    <hyperlink ref="C15" r:id="rId4" display="https://www.al.sp.gov.br/repositorio/legislacao/lei.complementar/2021/lei.complementar-1361-21.10.2021.html" xr:uid="{70E8D4E1-70DC-4704-B34F-37D55A68DDDE}"/>
-    <hyperlink ref="C2" r:id="rId5" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=46221322471c7614f8000b54f26d4324" xr:uid="{75A86CE3-9906-40CF-978F-C67834022BB9}"/>
-    <hyperlink ref="C19" r:id="rId6" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=826c97e6879c3690bc19ea840cbb35c2" xr:uid="{4F07292F-3FE8-42B0-B6CD-69B2EB19D6F4}"/>
-    <hyperlink ref="C20" r:id="rId7" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=a2fed7e687dc3690bc19ea840cbb3528" xr:uid="{9F445065-2B6E-4292-83AC-AEAD9DC41ABF}"/>
-    <hyperlink ref="C4" r:id="rId8" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=f1b027a287107690bc19ea840cbb35f4" xr:uid="{615DFD73-D63A-4B10-B2B0-0D055F86F588}"/>
-    <hyperlink ref="C22" r:id="rId9" display="https://doe.sp.gov.br/executivo/decretos/decreto-n-69053-de-14-de-novembro-de-2024-20241114118202720093" xr:uid="{F4FD03CD-FFC5-4276-925C-158FC564465E}"/>
-    <hyperlink ref="C5" r:id="rId10" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=65ccccf597543ad400b3b55ef053af23" xr:uid="{4744191C-1687-40B7-9D2C-3909C7F8B057}"/>
-    <hyperlink ref="C23" r:id="rId11" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{BBE997A9-5DE5-4647-90FC-FAE593ED1233}"/>
-    <hyperlink ref="C26" r:id="rId12" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{44E65426-C3CD-405F-AC3B-5E68BBC3F50F}"/>
-    <hyperlink ref="C8" r:id="rId13" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{10DA6FA3-4706-49C9-AE5F-34C5EBF242C7}"/>
-    <hyperlink ref="C28" r:id="rId14" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{587FE85B-9654-4881-8170-157563EF79D8}"/>
-    <hyperlink ref="C30" r:id="rId15" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{BA244310-00E7-4148-9902-362A8FB194FA}"/>
-    <hyperlink ref="C31" r:id="rId16" display="https://www.detran.sp.gov.br/detransp/pb/regulacao/normas/decreto-n%C2%BA-68-347-de-29-de-fevereiro-de-2024?id=ver_norma&amp;sys_kb_id=48f4e36b3b9432501aaf0847f4e45a1f" xr:uid="{AABF2F15-B2D2-4A99-84D3-F29FFBB9A6EE}"/>
-    <hyperlink ref="C3" r:id="rId17" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{C86C679F-B17B-4050-905E-A9CDFDAC49BB}"/>
-    <hyperlink ref="C32" r:id="rId18" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=09f0e64697dcba145db3b4a6f053af33" xr:uid="{083B43A2-E954-487E-9138-61E228DFFFC6}"/>
+    <hyperlink ref="C9" r:id="rId1" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=9f176a9e87d4b2d434a7c8840cbb355e" xr:uid="{D79240FC-BF31-4540-8E8B-37A1E8FCED1C}"/>
+    <hyperlink ref="C11" r:id="rId2" display="https://www.detran.sp.gov.br/detransp/pb/regulacao/normas/portaria-normativa-detran-sp-n%C2%BA-1-de-20-de-mar%C3%A7o-de-2023?id=ver_norma&amp;sys_kb_id=298ae6de8718b2d434a7c8840cbb35cb" xr:uid="{D4340E15-B784-4FF5-B32E-0FCA8B3FA484}"/>
+    <hyperlink ref="C20" r:id="rId3" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=2b182a168718b2d434a7c8840cbb3562" xr:uid="{E6FD3251-2445-410D-875D-2B466D4FF5BD}"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://www.al.sp.gov.br/repositorio/legislacao/lei.complementar/2021/lei.complementar-1361-21.10.2021.html" xr:uid="{70E8D4E1-70DC-4704-B34F-37D55A68DDDE}"/>
+    <hyperlink ref="C10" r:id="rId5" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=46221322471c7614f8000b54f26d4324" xr:uid="{75A86CE3-9906-40CF-978F-C67834022BB9}"/>
+    <hyperlink ref="C29" r:id="rId6" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=826c97e6879c3690bc19ea840cbb35c2" xr:uid="{4F07292F-3FE8-42B0-B6CD-69B2EB19D6F4}"/>
+    <hyperlink ref="C7" r:id="rId7" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=a2fed7e687dc3690bc19ea840cbb3528" xr:uid="{9F445065-2B6E-4292-83AC-AEAD9DC41ABF}"/>
+    <hyperlink ref="C27" r:id="rId8" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=f1b027a287107690bc19ea840cbb35f4" xr:uid="{615DFD73-D63A-4B10-B2B0-0D055F86F588}"/>
+    <hyperlink ref="C25" r:id="rId9" display="https://doe.sp.gov.br/executivo/decretos/decreto-n-69053-de-14-de-novembro-de-2024-20241114118202720093" xr:uid="{F4FD03CD-FFC5-4276-925C-158FC564465E}"/>
+    <hyperlink ref="C12" r:id="rId10" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=65ccccf597543ad400b3b55ef053af23" xr:uid="{4744191C-1687-40B7-9D2C-3909C7F8B057}"/>
+    <hyperlink ref="C19" r:id="rId11" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{BBE997A9-5DE5-4647-90FC-FAE593ED1233}"/>
+    <hyperlink ref="C30" r:id="rId12" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{44E65426-C3CD-405F-AC3B-5E68BBC3F50F}"/>
+    <hyperlink ref="C22" r:id="rId13" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{10DA6FA3-4706-49C9-AE5F-34C5EBF242C7}"/>
+    <hyperlink ref="C8" r:id="rId14" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{587FE85B-9654-4881-8170-157563EF79D8}"/>
+    <hyperlink ref="C21" r:id="rId15" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{BA244310-00E7-4148-9902-362A8FB194FA}"/>
+    <hyperlink ref="C28" r:id="rId16" display="https://www.detran.sp.gov.br/detransp/pb/regulacao/normas/decreto-n%C2%BA-68-347-de-29-de-fevereiro-de-2024?id=ver_norma&amp;sys_kb_id=48f4e36b3b9432501aaf0847f4e45a1f" xr:uid="{AABF2F15-B2D2-4A99-84D3-F29FFBB9A6EE}"/>
+    <hyperlink ref="C4" r:id="rId17" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=b31eef2a87147690bc19ea840cbb352a" xr:uid="{C86C679F-B17B-4050-905E-A9CDFDAC49BB}"/>
+    <hyperlink ref="C24" r:id="rId18" display="https://www.detran.sp.gov.br/detransp?id=ver_norma&amp;sys_kb_id=09f0e64697dcba145db3b4a6f053af33" xr:uid="{083B43A2-E954-487E-9138-61E228DFFFC6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId19"/>
@@ -3517,7 +3565,7 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="10.6328125" customWidth="1"/>
+    <col min="1" max="7" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3642,7 +3690,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -3668,19 +3716,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="573712b6dcab840c7ca9e515c014ec61">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="066b26330b129ad48bd94428e47b6cce" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
     <xsd:import namespace="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
     <xsd:element name="properties">
@@ -3749,7 +3786,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2dab9438-f903-450b-a158-c86bb4a35dfc" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2dab9438-f903-450b-a158-c86bb4a35dfc" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -3782,7 +3819,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3de8a3b1-ed4f-410f-8887-f682d26381a0" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3801,7 +3838,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -3829,8 +3866,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -3919,6 +3956,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
@@ -3928,18 +3976,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13ED962-62B8-431A-A86F-38EF8F237874}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -3957,6 +3994,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B64915A-19CB-4437-BC01-14C6E762B6FB}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE5B9589-E3F8-4C8B-9349-831AE3A70F55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="278">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -367,9 +367,6 @@
   </si>
   <si>
     <t>BeSolution</t>
-  </si>
-  <si>
-    <t>Validação da jornadas</t>
   </si>
   <si>
     <t>CONCURSO PÚBLICO</t>
@@ -942,13 +939,6 @@
     <t>Próximos Passos</t>
   </si>
   <si>
-    <t>Projeto segue como planejado
-Implantação gradual:
-Classificação de Monta - 01/10/2026
-Mera identificação - 16/10/2026
-Compra e Venda de Veículos - 01/11/2026</t>
-  </si>
-  <si>
     <t>Período da última semana</t>
   </si>
   <si>
@@ -1040,19 +1030,6 @@
   </si>
   <si>
     <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
-  </si>
-  <si>
-    <t>Implantação MVP-1 que contempla os laudos de vistoria de estrutura e alteração veicular</t>
-  </si>
-  <si>
-    <t>Implantação MVP-1 que contempla os laudos de vistoria de estrutura e alteração veicular
-(Classificação de Monta)</t>
-  </si>
-  <si>
-    <t>Acompanhar funcionamento MVP-1
-Implantação Mera identificação - 16/10/2026
-Implantação Compra e Venda de Veículos - 01/11/2026
-Operação Assistida até 23/12/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas
@@ -1140,12 +1117,6 @@
 Todas as jornadas revisadas</t>
   </si>
   <si>
-    <t>Introduzir os analistas na fase 2 utilizando a ferramenta VSM</t>
-  </si>
-  <si>
-    <t>Aguardando validações e feedback</t>
-  </si>
-  <si>
     <t>Projeto apresenta significativo atraso e não há previsão para o término:
 Agente OCR
 Treinamento - 19/10
@@ -1178,25 +1149,11 @@
 </t>
   </si>
   <si>
-    <t>Live 1.0 - entregue
-Consulta de peças - entregue
-Plataforma estadual de vistorias e Live 2.0 em andamento sem impeditivos</t>
-  </si>
-  <si>
     <t>13/10/2026 a 16/10/2026</t>
-  </si>
-  <si>
-    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
-Plataforma estadual de vistoria: Implantação assistida.
-Emplacar Veículo 0KM realizado o Kickoff.</t>
   </si>
   <si>
     <t xml:space="preserve">Novo app segue em fase de testes.
  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
-Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) </t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1219,6 +1176,34 @@
     <t>Não tiveram atualizações:
 Autorização de Transporte Escolar (ATE): Aguardando contratação de fornecedor de desenvolvimento.
 Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
+  </si>
+  <si>
+    <t>Live 1.0 - entregue
+Consulta de peças - entregue
+Live 2.0 em andamento sem impeditivos</t>
+  </si>
+  <si>
+    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
+Emplacar Veículo 0KM realizado o Kickoff.</t>
+  </si>
+  <si>
+    <t>Em andamento sem impeditivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
+</t>
+  </si>
+  <si>
+    <t>Implantação assistida.</t>
+  </si>
+  <si>
+    <t>Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
+  </si>
+  <si>
+    <t>Realinhar formato de indicadores de cada melhoria.</t>
+  </si>
+  <si>
+    <t>Validação das jornadas.</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1340,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1435,6 +1420,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1769,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1784,19 +1772,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1814,7 +1802,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1837,17 +1825,17 @@
     </row>
     <row r="2" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>34</v>
@@ -1873,18 +1861,18 @@
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X2" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="19" t="s">
@@ -1917,10 +1905,10 @@
       <c r="U3" s="22"/>
       <c r="V3" s="22"/>
       <c r="W3" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -1931,7 +1919,7 @@
         <v>68</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>98</v>
@@ -1946,13 +1934,13 @@
         <v>13</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K4" s="9">
         <v>75</v>
@@ -1971,42 +1959,42 @@
         <v>46377</v>
       </c>
       <c r="P4" s="10">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>34</v>
@@ -2032,10 +2020,10 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
@@ -2043,7 +2031,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
@@ -2059,13 +2047,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K6" s="7">
         <v>15</v>
@@ -2095,27 +2083,27 @@
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="261" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>56</v>
@@ -2144,25 +2132,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>34</v>
@@ -2188,10 +2176,10 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
@@ -2199,14 +2187,14 @@
         <v>55</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>34</v>
@@ -2232,10 +2220,10 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
@@ -2246,7 +2234,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>43</v>
@@ -2261,13 +2249,13 @@
         <v>15</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K10" s="9">
         <v>79</v>
@@ -2286,33 +2274,33 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
@@ -2342,10 +2330,10 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2356,7 +2344,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>77</v>
@@ -2371,10 +2359,10 @@
         <v>15</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="7">
@@ -2413,15 +2401,15 @@
         <v>90</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2452,24 +2440,24 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>58</v>
@@ -2498,18 +2486,18 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
@@ -2540,10 +2528,10 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -2567,13 +2555,13 @@
         <v>15</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K16" s="7">
         <v>70</v>
@@ -2594,13 +2582,13 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
@@ -2609,7 +2597,7 @@
         <v>93</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
@@ -2633,19 +2621,19 @@
         <v>13</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K17" s="7">
         <v>90</v>
       </c>
-      <c r="L17" s="7">
-        <v>89</v>
+      <c r="L17" s="28">
+        <v>0.9</v>
       </c>
       <c r="M17" s="8">
         <v>45901</v>
@@ -2657,20 +2645,18 @@
         <v>46373</v>
       </c>
       <c r="P17" s="8">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>267</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>100</v>
+        <v>277</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
@@ -2682,14 +2668,14 @@
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>56</v>
@@ -2718,25 +2704,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>34</v>
@@ -2762,25 +2748,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>34</v>
@@ -2806,21 +2792,21 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
@@ -2850,10 +2836,10 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
@@ -2864,13 +2850,13 @@
         <v>70</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>12</v>
@@ -2879,16 +2865,16 @@
         <v>13</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="K22" s="7">
-        <v>93</v>
+        <v>274</v>
+      </c>
+      <c r="K22" s="28">
+        <v>0.94</v>
       </c>
       <c r="L22" s="7">
         <v>100</v>
@@ -2903,13 +2889,11 @@
         <v>46379</v>
       </c>
       <c r="P22" s="8">
-        <v>46300</v>
-      </c>
-      <c r="Q22" s="14" t="s">
-        <v>251</v>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="Q22" s="14"/>
       <c r="R22" s="3" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
@@ -2919,7 +2903,7 @@
         <v>94</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="232" x14ac:dyDescent="0.35">
@@ -2943,13 +2927,13 @@
         <v>15</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K23" s="7">
         <v>50</v>
@@ -2968,13 +2952,13 @@
         <v>46304</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="3"/>
@@ -2982,7 +2966,7 @@
         <v>75</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>96</v>
@@ -2990,17 +2974,17 @@
     </row>
     <row r="24" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>34</v>
@@ -3026,25 +3010,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>34</v>
@@ -3070,10 +3054,10 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
@@ -3081,7 +3065,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
@@ -3097,13 +3081,13 @@
         <v>15</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K26" s="7">
         <v>99</v>
@@ -3120,24 +3104,24 @@
         <v>46303</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>95</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
@@ -3148,7 +3132,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>46</v>
@@ -3163,13 +3147,13 @@
         <v>15</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K27" s="9">
         <v>92</v>
@@ -3190,17 +3174,17 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="R27" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
@@ -3212,13 +3196,13 @@
     </row>
     <row r="28" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
@@ -3248,21 +3232,21 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
@@ -3292,25 +3276,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>34</v>
@@ -3336,22 +3320,22 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>60</v>
@@ -3380,25 +3364,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="87" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>34</v>
@@ -3424,22 +3408,22 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>44</v>
@@ -3468,10 +3452,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE5B9589-E3F8-4C8B-9349-831AE3A70F55}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E3F88A3-A7B1-41FE-989E-AAAB7D631D4F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="279">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -262,13 +262,6 @@
   </si>
   <si>
     <t>Riscos</t>
-  </si>
-  <si>
-    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
-  </si>
-  <si>
-    <t>Realizar alinhamento de atividades com DHC e DTI
-Realizar alinhamento de atividades e cronograma com Assessoria da Presidência</t>
   </si>
   <si>
     <t>Priscilla Elias e Silva</t>
@@ -356,11 +349,6 @@
 Implementar rede colaborativa de parceiros em prol da segurança de todos
 Otimizar a experiência e a satisfação do usuário com o atendimento
 Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
-  </si>
-  <si>
-    <t>Publicação do Edital - prova 01/11/2026
-Realizada orientação para as sobre como preencher templates de treinamento
-Realizado alinhamento com DHC sobre aquisição e disponibilização dos tablets</t>
   </si>
   <si>
     <t>PRODESP</t>
@@ -887,10 +875,6 @@
     <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
   </si>
   <si>
-    <t xml:space="preserve">Correção de Bugs da V3 -30/09/2026 (54 itens)
-</t>
-  </si>
-  <si>
     <t>Possível revisão de escopo - impacto no cronograma
 Não há previsão para o término do projeto</t>
   </si>
@@ -950,9 +934,6 @@
   </si>
   <si>
     <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be</t>
-  </si>
-  <si>
-    <t>Alinhamento com as áreas de negócio sobre o conteúdo programático</t>
   </si>
   <si>
     <t>PRJ032</t>
@@ -1005,12 +986,6 @@
     <t>Aprovação da Etapa 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Base de Conhecimento - entregue 14/06/2026
-Sistema de Atendimento - entregue 14/06/2026 (homologação)
-Base de Conhecimento - correções - entregue 30/09/2026
-</t>
-  </si>
-  <si>
     <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
   </si>
   <si>
@@ -1032,28 +1007,8 @@
     <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
   </si>
   <si>
-    <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas
-A data prevista inicialmente de 25/09/2026 não foi atingida e não há ainda previsão para o fim do projeto
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Correção de BUGs da V2 e V3
 </t>
-  </si>
-  <si>
-    <t>Homologação (correção dos 54 itens) - 06/10/2026
-Subida em produção -  07/10/2026
-Correção de demais itens da V3 - 12/10/2026</t>
-  </si>
-  <si>
-    <t>O módulo Admin será entregue com a V4
-O  ininício da versão V4 está condicionada ao término da V3.
-Refinamento dos requisitos - início previsto 13/10/2026</t>
-  </si>
-  <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação.
-Alteração do conteúdo durante a etapa de ambientação no AVA
-Alterações normativas durante a produção do conteúdo da capacitação</t>
   </si>
   <si>
     <t>Projeto segue dentro do prazo, conforme planejado
@@ -1091,9 +1046,6 @@
     </r>
   </si>
   <si>
-    <t>05/10/2026 a 09/10/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
 </t>
   </si>
@@ -1128,14 +1080,6 @@
 Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão</t>
   </si>
   <si>
-    <t>Capacitação em prompts - 19/10/2026
-Agente OCR de Documentos de Credenciamento - integração com o portal -
-Treinamento - 19/10/2026
-Homologação - 20/10/2026
-GMUD - 27/10/2026
-Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
 Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
 </t>
@@ -1147,6 +1091,11 @@
 Agente Q&amp;A da Wiki ("Isa")
 Agente Revisor de conteúdo da Wiki
 </t>
+  </si>
+  <si>
+    <t>Live 1.0 - entregue
+Consulta de peças - entregue
+Live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
     <t>13/10/2026 a 16/10/2026</t>
@@ -1178,11 +1127,6 @@
 Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
   </si>
   <si>
-    <t>Live 1.0 - entregue
-Consulta de peças - entregue
-Live 2.0 em andamento sem impeditivos</t>
-  </si>
-  <si>
     <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
 Emplacar Veículo 0KM realizado o Kickoff.</t>
   </si>
@@ -1204,6 +1148,63 @@
   </si>
   <si>
     <t>Validação das jornadas.</t>
+  </si>
+  <si>
+    <t>Alinhamento com as áreas de negócio sobre o conteúdo programático, alinhamento com PO sobre entregas do projeto e detalhamento do fluxo de contratação com DAL;</t>
+  </si>
+  <si>
+    <t>Publicação do Edital - prova 01/11/2026
+Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes;</t>
+  </si>
+  <si>
+    <t>Atualização do cronograma, alinhamento com PO e EPT;</t>
+  </si>
+  <si>
+    <t>Atraso na revisão e validação do conteúdo da capacitação.
+Alterações normativas durante a produção do conteúdo da capacitação</t>
+  </si>
+  <si>
+    <t>16/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas, previsão de correção até 15/10/2026;
+</t>
+  </si>
+  <si>
+    <t>13/10/2026 a 06/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção de Bugs da V3 e subida na loja
+</t>
+  </si>
+  <si>
+    <t>Homologação (correção dos 54 itens) - 06/10/2026
+Subida na loja -  16/10/2026
+27/10/2026 Inicio da utilização e prova de campo por 20 dias;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O módulo Admin será entregue com a V4
+O  ininício da versão V4 está condicionada ao término da V3.
+Refinamento dos requisitos da V4 </t>
+  </si>
+  <si>
+    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.
+Risco de atraso na entrega:  OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de Conhecimento - entregue 14/06/2026
+Sistema de Atendimento - entregue 14/06/2026 (homologação)
+Base de Conhecimento - correções - entregue 30/09/2026
+OCR e Azure: tem bloqueio de configurações e migração para Produção </t>
+  </si>
+  <si>
+    <t>Capacitação em prompts - 19/10/2026
+Agente OCR de Documentos de Credenciamento - integração com o portal -
+Treinamento - 19/10/2026
+Homologação - 20/10/2026
+GMUD - 27/10/2026
+Denilson acionará Ricardo Aragão (superintendente da BU Prodesp) para destravar a migração de configuração OCR e Azure para Produção.
+Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
   </si>
 </sst>
 </file>
@@ -1441,6 +1442,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1728,28 +1733,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="35.54296875" customWidth="1"/>
-    <col min="3" max="3" width="55.54296875" customWidth="1"/>
-    <col min="4" max="5" width="22" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.54296875" customWidth="1"/>
-    <col min="9" max="9" width="25.54296875" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.54296875" customWidth="1"/>
-    <col min="23" max="23" width="50.54296875" customWidth="1"/>
-    <col min="24" max="24" width="120.54296875" customWidth="1"/>
+    <col min="17" max="22" width="40.5703125" customWidth="1"/>
+    <col min="23" max="23" width="50.5703125" customWidth="1"/>
+    <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>2</v>
@@ -1772,19 +1779,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>7</v>
@@ -1802,7 +1809,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="S1" s="13" t="s">
         <v>72</v>
@@ -1811,31 +1818,31 @@
         <v>73</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V1" s="13" t="s">
         <v>74</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>34</v>
@@ -1861,18 +1868,18 @@
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="X2" s="23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="246.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="19" t="s">
@@ -1905,13 +1912,13 @@
       <c r="U3" s="22"/>
       <c r="V3" s="22"/>
       <c r="W3" s="23" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="203.1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1919,10 +1926,10 @@
         <v>68</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>56</v>
@@ -1934,20 +1941,20 @@
         <v>13</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="K4" s="9">
         <v>75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.92638036809815949</v>
+        <v>0.92760736196319016</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -1962,39 +1969,39 @@
         <v>46310</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>34</v>
@@ -2020,18 +2027,18 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
@@ -2047,13 +2054,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="K6" s="7">
         <v>15</v>
@@ -2071,39 +2078,39 @@
         <v>46461</v>
       </c>
       <c r="P6" s="8">
-        <v>45939</v>
+        <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>56</v>
@@ -2132,25 +2139,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>34</v>
@@ -2176,25 +2183,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>34</v>
@@ -2220,13 +2227,13 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2234,7 +2241,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>43</v>
@@ -2249,13 +2256,13 @@
         <v>15</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K10" s="9">
         <v>79</v>
@@ -2274,33 +2281,33 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="29.1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
@@ -2330,13 +2337,13 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
@@ -2344,10 +2351,10 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>58</v>
@@ -2359,10 +2366,10 @@
         <v>15</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="7">
@@ -2382,34 +2389,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2440,24 +2447,24 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>228</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>233</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>58</v>
@@ -2486,18 +2493,18 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
@@ -2528,13 +2535,13 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -2555,13 +2562,13 @@
         <v>15</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K16" s="7">
         <v>70</v>
@@ -2582,25 +2589,25 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -2621,13 +2628,13 @@
         <v>13</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K17" s="7">
         <v>90</v>
@@ -2648,34 +2655,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>56</v>
@@ -2704,25 +2711,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>34</v>
@@ -2748,25 +2755,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>34</v>
@@ -2792,21 +2799,21 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" ht="101.45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
@@ -2836,13 +2843,13 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
@@ -2850,13 +2857,13 @@
         <v>70</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>12</v>
@@ -2865,13 +2872,13 @@
         <v>13</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="K22" s="28">
         <v>0.94</v>
@@ -2893,20 +2900,20 @@
       </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="232" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" ht="255" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
@@ -2915,25 +2922,25 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="K23" s="7">
         <v>50</v>
@@ -2949,42 +2956,42 @@
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="8">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="T23" s="6"/>
+        <v>251</v>
+      </c>
+      <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>141</v>
-      </c>
       <c r="C24" s="18" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>34</v>
@@ -3010,25 +3017,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>34</v>
@@ -3054,22 +3061,22 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>67</v>
@@ -3081,13 +3088,13 @@
         <v>15</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K26" s="7">
         <v>99</v>
@@ -3098,33 +3105,37 @@
       <c r="M26" s="8">
         <v>46042</v>
       </c>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
+      <c r="N26" s="8">
+        <v>46295</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="P26" s="8">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
@@ -3132,7 +3143,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>46</v>
@@ -3147,13 +3158,13 @@
         <v>15</v>
       </c>
       <c r="H27" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J27" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>225</v>
       </c>
       <c r="K27" s="9">
         <v>92</v>
@@ -3174,35 +3185,35 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>140</v>
-      </c>
       <c r="C28" s="18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
@@ -3232,21 +3243,21 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" ht="101.45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
@@ -3276,25 +3287,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>34</v>
@@ -3320,22 +3331,22 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="58" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>60</v>
@@ -3364,25 +3375,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>34</v>
@@ -3408,22 +3419,22 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>44</v>
@@ -3452,14 +3463,20 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X33" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Em andamento"/>
+        <filter val="Problema"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X33">
       <sortCondition ref="B1:B33"/>
     </sortState>
@@ -3547,12 +3564,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="10.54296875" customWidth="1"/>
+    <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3575,7 +3592,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3598,7 +3615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -3621,7 +3638,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3644,7 +3661,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -3663,7 +3680,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -3674,7 +3691,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -3691,6 +3708,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3699,7 +3727,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3940,18 +3968,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3959,7 +3993,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3978,23 +4012,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akihiro.hayashi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E3F88A3-A7B1-41FE-989E-AAAB7D631D4F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B0C205-A9EB-467C-B652-17AA7846A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="278">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -1169,9 +1169,6 @@
   <si>
     <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas, previsão de correção até 15/10/2026;
 </t>
-  </si>
-  <si>
-    <t>13/10/2026 a 06/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Correção de Bugs da V3 e subida na loja
@@ -1442,10 +1439,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1918,7 +1911,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="203.1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1954,7 +1947,7 @@
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.92760736196319016</v>
+        <v>0.93128834355828216</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -2607,7 +2600,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -2849,7 +2842,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
@@ -2959,10 +2952,10 @@
         <v>46311</v>
       </c>
       <c r="Q23" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>251</v>
@@ -2970,7 +2963,7 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>252</v>
@@ -3091,7 +3084,7 @@
         <v>271</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="J26" s="14" t="s">
         <v>242</v>
@@ -3115,13 +3108,13 @@
         <v>46308</v>
       </c>
       <c r="Q26" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="R26" s="3" t="s">
+      <c r="S26" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
@@ -3708,26 +3701,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3968,32 +3941,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4012,6 +3980,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akihiro.hayashi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B0C205-A9EB-467C-B652-17AA7846A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C89E25-6125-441E-93E7-47A0CCCE31E4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Projetos!$A$1:$X$33</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -45,6 +48,9 @@
     <t>Projeto</t>
   </si>
   <si>
+    <t>Portaria</t>
+  </si>
+  <si>
     <t>GP</t>
   </si>
   <si>
@@ -57,9 +63,22 @@
     <t>Situação</t>
   </si>
   <si>
+    <t>Justificativa da Situação</t>
+  </si>
+  <si>
+    <t>Período da última semana</t>
+  </si>
+  <si>
+    <t>O que foi feito na última semana</t>
+  </si>
+  <si>
     <t>% Execução</t>
   </si>
   <si>
+    <t>%Consumo 
+Prazo</t>
+  </si>
+  <si>
     <t>Data Início</t>
   </si>
   <si>
@@ -72,7 +91,98 @@
     <t>Data Última RAP</t>
   </si>
   <si>
-    <t>PRJ001</t>
+    <t>Últimas Atualizações</t>
+  </si>
+  <si>
+    <t>Próximos Passos</t>
+  </si>
+  <si>
+    <t>Pontos de Atenção</t>
+  </si>
+  <si>
+    <t>Impedimentos</t>
+  </si>
+  <si>
+    <t>Pendências</t>
+  </si>
+  <si>
+    <t>Riscos</t>
+  </si>
+  <si>
+    <t>Escopo</t>
+  </si>
+  <si>
+    <t>Objetivos Estratégicos</t>
+  </si>
+  <si>
+    <t>PRJ020</t>
+  </si>
+  <si>
+    <t>#SOUDETRAN</t>
+  </si>
+  <si>
+    <t>Edson Arcas</t>
+  </si>
+  <si>
+    <t>ASCOM</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e implementação de um ambiente de trabalho digital (digital workplace) para os colaboradores do Detran-SP, consolidando em uma única plataforma as informações e ferramentas necessárias para o seu dia a dia, desde o onboarding até a aposentadoria.
+Esta solução estará alinhada com a essência do employee experience, visando aumentar o engajamento dos colaboradores através de funcionalidades que promovam a comunicação e transparência, a colaboração, o aprendizado e a produtividade.
+A solução tecnológica será integrada ao ecossistema da Microsoft, podendo ser acessada via Teams e contará com três subprodutos principais:
+Intranet (#SouDetranSP) – Microsoft Viva Connections: Portal interno com ênfase na organização, produtividade, comunicação institucional, interação e gestão de pessoas (praVC).
+Será o principal ponto de acesso para o colaborador obter informações institucionais, atualizações e encontrar as ferramentas necessárias para a execução de suas tarefas.
+Rede Social Corporativa – Microsoft Viva Engage: Ferramenta dedicada a promover a comunicação ágil com e entre os colaboradores, incentivando a colaboração e troca de conhecimentos.
+Permitirá a criação de comunidades baseadas em processos de negócio, possibilitando uma coleta de informações bottom-up, o que contribuirá para a melhoria contínua dos processos internos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otimizar a gestão de pessoas e adequar a força de trabalho
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implantar mecanismos de gestão meritocrática e promover o espírito de equipe
+</t>
+  </si>
+  <si>
+    <t>PRJ023</t>
+  </si>
+  <si>
+    <t>ARQUITETURA DE TIC</t>
+  </si>
+  <si>
+    <t>Sérgio Araújo</t>
+  </si>
+  <si>
+    <t>DTI</t>
+  </si>
+  <si>
+    <t>Dar visibilidade a todos os aspectos que compõem o parque tecnológico, incluindo a compreensão de todo investimento ativo e recorrente, sua disponibilidade, duplicidades, efetividade e eficiência operacional, assim como identificar e avaliar a necessidade e manutenção, mirando a melhoria contínua.
+Ainda, atualizar o desenho da topologia dos sistemas, destacando todas as suas conexões e integrações, possíveis pontos de melhorias e recomendações, e preparação dos ambientes para mudança.
+Priorizar os sistemas estratégicos para tomada de decisão quanto a investimento, aposentadoria de sistemas, convivência e reestruturação.
+O projeto engloba o mapeamento de todos os componentes do Detran-SP e interfaces que compõem a arquitetura dos sistemas, considerando, mas não se limitando, aos seguintes aspectos:</t>
+  </si>
+  <si>
+    <t>Empregar soluções tecnológicas inovadoras para alavancar os resultados
+Garantir a segurança, integridade e efetiva governança de dados e informações
+Otimizar a alocação e modernização dos equipamentos e da infraestrutura
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implementar gestão de performance e subsidiar as decisões com evidências
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
+  </si>
+  <si>
+    <t>PRJ002</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 5.561, de 20 de setembro de 2024</t>
+  </si>
+  <si>
+    <t>PRODESP</t>
   </si>
   <si>
     <t>Em andamento</t>
@@ -81,473 +191,70 @@
     <t>Saudável</t>
   </si>
   <si>
-    <t>PRJ002</t>
-  </si>
-  <si>
-    <t>Atenção</t>
-  </si>
-  <si>
-    <t>Concluída</t>
-  </si>
-  <si>
-    <t>Próxima etapa</t>
-  </si>
-  <si>
-    <t>Impacto</t>
-  </si>
-  <si>
-    <t>Não iniciado</t>
-  </si>
-  <si>
-    <t>Probabilidade</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Alto</t>
-  </si>
-  <si>
-    <t>Status Entrega</t>
-  </si>
-  <si>
-    <t>Status Passo</t>
-  </si>
-  <si>
-    <t>Status Decisão</t>
-  </si>
-  <si>
-    <t>Backlog</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Baixo</t>
-  </si>
-  <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Em planejamento</t>
-  </si>
-  <si>
-    <t>Médio</t>
-  </si>
-  <si>
-    <t>Em análise</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Decidida</t>
-  </si>
-  <si>
-    <t>Suspenso</t>
-  </si>
-  <si>
-    <t>Atrasada</t>
-  </si>
-  <si>
-    <t>Atrasado</t>
-  </si>
-  <si>
-    <t>Escalonada</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>FOCUS</t>
-  </si>
-  <si>
-    <t>Isabella Monteiro</t>
-  </si>
-  <si>
-    <t>DFT</t>
-  </si>
-  <si>
-    <t>SIAUT</t>
-  </si>
-  <si>
-    <t>Cyntia Tiemi Nihy</t>
-  </si>
-  <si>
-    <t>PRJ003</t>
-  </si>
-  <si>
-    <t>PRJ004</t>
-  </si>
-  <si>
-    <t>PRJ005</t>
-  </si>
-  <si>
-    <t>PRJ006</t>
-  </si>
-  <si>
-    <t>PRJ007</t>
-  </si>
-  <si>
-    <t>PRJ008</t>
-  </si>
-  <si>
-    <t>PRJ009</t>
-  </si>
-  <si>
-    <t>PRJ010</t>
-  </si>
-  <si>
-    <t>PRJ011</t>
-  </si>
-  <si>
-    <t>DTI</t>
-  </si>
-  <si>
-    <t>HABILITA-SP</t>
-  </si>
-  <si>
-    <t>AEPE</t>
-  </si>
-  <si>
-    <t>Lincon Santos</t>
-  </si>
-  <si>
-    <t>AEGE</t>
-  </si>
-  <si>
-    <t>ITSM-2026</t>
-  </si>
-  <si>
-    <t>Arturo Sangiovani</t>
-  </si>
-  <si>
-    <t>POLESTAR - MSFT</t>
-  </si>
-  <si>
-    <t>DGR</t>
-  </si>
-  <si>
-    <t>Sérgio Araújo</t>
-  </si>
-  <si>
-    <t>DAC</t>
-  </si>
-  <si>
-    <t>DSV</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JORNADA DO CIDADÃO </t>
-  </si>
-  <si>
-    <t>PLATAFORMA ESTADUAL DE VISTORIA</t>
-  </si>
-  <si>
-    <t>Últimas Atualizações</t>
-  </si>
-  <si>
-    <t>Pontos de Atenção</t>
-  </si>
-  <si>
-    <t>Impedimentos</t>
-  </si>
-  <si>
-    <t>Riscos</t>
-  </si>
-  <si>
-    <t>Priscilla Elias e Silva</t>
-  </si>
-  <si>
-    <t>Artur Giannini</t>
-  </si>
-  <si>
-    <t>Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP;
-Desenvolvimento das definições de layout, fluxos, materialidade e aplicabilidade do conceito;
-Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026; Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade</t>
-  </si>
-  <si>
-    <t>Prosseguimento, pela área de Infraestrutura, dos procedimentos necessários para contratação e implantação da unidade, contemplando os projetos e serviços necessários à execução da obra.
-Paralelamente, as definições consolidadas no projeto-piloto deverão subsidiar a padronização e replicabilidade do Habilita SP, com as devidas adequações às características e necessidades de cada futura unidade.</t>
-  </si>
-  <si>
-    <t>Necessidade de acompanhamento do andamento da contratação pela Infraestrutura, considerando que os desenhos técnicos estão disponibilizados desde julho/2026.
-Por se tratar do projeto-piloto, eventuais ajustes identificados durante as etapas de projeto executivo e implantação deverão ser avaliados quanto ao seu impacto no padrão a ser replicado nas demais unidades do Habilita SP.</t>
-  </si>
-  <si>
-    <t>Risco de impacto no cronograma de implantação, caso haja prolongamento das etapas de contratação dos projetos, obra e serviços.
-Considerando o caráter piloto da Estaiadinha, eventual atraso também poderá repercutir na validação prática das soluções e na consolidação do padrão para expansão do Habilita SP.</t>
-  </si>
-  <si>
-    <t>Pendências</t>
-  </si>
-  <si>
-    <t>Cronograma com estimativa do prazo final</t>
-  </si>
-  <si>
-    <t>Escopo</t>
-  </si>
-  <si>
-    <t>Objetivos Estratégicos</t>
-  </si>
-  <si>
-    <t>Estudar e implementar solução de monitoramento audiovisual da atuação do Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP).</t>
-  </si>
-  <si>
-    <t>O Projeto SIAUT tem por objetivo operacionalizar a lavratura de autuações e a aplicação das respectivas penalidades administrativas oriunda as infrações administrativas conhecidas como "multas de balcão", de competência do DETRAN-SP, que serão implantadas através de 04 (quatro) ETAPAS.
-ETAPA1 (MULTAS ART. 165-D)
-ETAPA2 (MULTAS ARTS.233 e 257, § 8º - NIC)
-ETAPA3 (MULTAS ARTS. 162, 163 ou 164)
-ETAPA4 (MULTAS ARTS. 240, 241, 242 e 243)</t>
-  </si>
-  <si>
-    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
-  </si>
-  <si>
-    <t>Desenvolver e implementar, no âmbito do Estado de São Paulo, as localidades e instalações de realização dos exames práticos de direção veicular, com fundamento no artigo 12, da Resolução CONTRAN nº 789, 18 de junho de 2020, promovendo a formação responsável de condutores e contribuindo para a segurança viária, por meio de processos íntegros e eficientes, atendimento de excelência e infraestrutura de alta qualidade.</t>
-  </si>
-  <si>
-    <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
-  </si>
-  <si>
-    <t>Disseminar a cultura de inovação, a gestão de projetos e processos
+    <t>Live 1.0 - entregue
+Consulta de peças - entregue
+Live 2.0 em andamento sem impeditivos</t>
+  </si>
+  <si>
+    <t>13/10/2026 a 16/10/2026</t>
+  </si>
+  <si>
+    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
+Emplacar Veículo 0KM realizado o Kickoff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo app segue em fase de testes.
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
+</t>
+  </si>
+  <si>
+    <t>Não tiveram atualizações:
+Autorização de Transporte Escolar (ATE): Aguardando contratação de fornecedor de desenvolvimento.
+Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
+  </si>
+  <si>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Emplacar Veículo 0Km: Chaintec não forneceu cronograma de desenvolvimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
+Primeira Habilitação
+Renovação da CNH
+Live2.0
+Autorização de Transporte Escolar (ATE)
+Gestão de Procuração 2.0
+Emplacar Veículo 0Km
+Novo APP DETRAN-SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otimizar a experiência e a satisfação do usuário com o atendimento
 Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Otimizar a experiência e a satisfação do usuário com o atendimento</t>
-  </si>
-  <si>
-    <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
-Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
-O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
-  </si>
-  <si>
-    <t>O RST (Registro de Sinistro de Trânsito) é um sistema digital inovador desenvolvido para modernizar o processo de registro e acompanhamento de acidentes de trânsito.
-O projeto tem como foco usabilidade, automação inteligente e integração com fontes oficiais, operando totalmente em nuvem e com arquitetura escalável, responsiva e segura.
-O sistema foi construído sobre bases técnicas e operacionais que garantem segurança, desempenho e conformidade.
-Foco em entregar App com módulo RST, sendo aplicativo único para todos órgãos de trânsito, com transcrição IA para agente de trânsito/GCM para reportar notificações e integração monta Infosiga.</t>
-  </si>
-  <si>
-    <t>Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
-Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Comunicar com foco nos serviços, na prestação de contas e na construção da marca
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
 Empregar soluções tecnológicas inovadoras para alavancar os resultados
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de "compliance" (conformidade)
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implementar rede colaborativa de parceiros em prol da segurança de todos
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
-  </si>
-  <si>
-    <t>PRODESP</t>
-  </si>
-  <si>
-    <t>BeSolution</t>
-  </si>
-  <si>
-    <t>CONCURSO PÚBLICO</t>
-  </si>
-  <si>
-    <t>PRJ012</t>
-  </si>
-  <si>
-    <t>ESTRATÉGIA DETRAN-SP</t>
-  </si>
-  <si>
-    <t>PRJ013</t>
+</t>
   </si>
   <si>
     <t>PRJ014</t>
   </si>
   <si>
-    <t>PRJ015</t>
-  </si>
-  <si>
-    <t>PRJ016</t>
-  </si>
-  <si>
-    <t>PRJ017</t>
-  </si>
-  <si>
-    <t>PRJ018</t>
-  </si>
-  <si>
-    <t>PRJ019</t>
-  </si>
-  <si>
-    <t>PRJ020</t>
-  </si>
-  <si>
-    <t>PRJ021</t>
-  </si>
-  <si>
-    <t>PRJ022</t>
-  </si>
-  <si>
-    <t>PRJ023</t>
-  </si>
-  <si>
-    <t>PRJ024</t>
-  </si>
-  <si>
-    <t>PRJ025</t>
-  </si>
-  <si>
-    <t>PRJ026</t>
-  </si>
-  <si>
-    <t>PRJ027</t>
-  </si>
-  <si>
-    <t>PRJ028</t>
-  </si>
-  <si>
-    <t>PRJ029</t>
-  </si>
-  <si>
-    <t>GUILHOTINA REGULATÓRIA</t>
-  </si>
-  <si>
-    <t>MARCA DO DETRAN-SP</t>
-  </si>
-  <si>
     <t>BONIFICAÇÃO POR RESULTADOS</t>
   </si>
   <si>
-    <t>WIKI</t>
-  </si>
-  <si>
-    <t>HEIMDALL</t>
-  </si>
-  <si>
-    <t>LGPD</t>
-  </si>
-  <si>
-    <t>SUPERNOVA</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>#SOUDETRAN</t>
-  </si>
-  <si>
-    <t>REFORMA ADMINISTRATIVA</t>
-  </si>
-  <si>
-    <t>LIVE</t>
-  </si>
-  <si>
-    <t>ARQUITETURA DE TIC</t>
-  </si>
-  <si>
-    <t>INFOSIGA</t>
-  </si>
-  <si>
-    <t>TDV</t>
-  </si>
-  <si>
-    <t>WS ROTA DOS EXAMINADORES</t>
-  </si>
-  <si>
-    <t>DETRAN PAY</t>
-  </si>
-  <si>
-    <t>WS ROTA SEGURA</t>
-  </si>
-  <si>
-    <t>PRJ030</t>
-  </si>
-  <si>
-    <t>PRJ031</t>
-  </si>
-  <si>
-    <t>NORMAS</t>
-  </si>
-  <si>
-    <t>SISTEMA ESTADUAL DO TRÂNSITO</t>
-  </si>
-  <si>
-    <t>PROGRAMA DE INTEGRIDADE</t>
-  </si>
-  <si>
-    <t>Justificativa da Situação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura.
-Desenhos técnicos necessários para contratação disponibilizados desde julho/2026.
+    <t>LEI COMPLEMENTAR N° 1.361, DE 21 DE OUTUBRO DE 2021</t>
+  </si>
+  <si>
+    <t>Presidência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar a bonificação por resultados no DETRAN-SP, nos termos da LEI COMPLEMENTAR N° 1.361, DE 21 DE OUTUBRO DE 2021.
 </t>
-  </si>
-  <si>
-    <t>Portaria</t>
-  </si>
-  <si>
-    <t>Portaria Normativa DETRAN-SP nº 6, de 31 de agosto de 2023</t>
-  </si>
-  <si>
-    <t>Portaria Normativa DETRAN-SP nº 1, de 20 de março de 2023</t>
-  </si>
-  <si>
-    <t>Portaria Normativa DETRAN-SP nº 3, de 20 de julho de 2023</t>
-  </si>
-  <si>
-    <t>LEI COMPLEMENTAR N° 1.361, DE 21 DE OUTUBRO DE 2021</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP Nº 2.889, DE 25 DE ABRIL DE 2024</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 3.481, de 23 de maio de 2024</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 4.021, de 13 de junho de 2024</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 4.830, de 30 de julho de 2024</t>
-  </si>
-  <si>
-    <t>DECRETO N° 69.053, DE 14 DE NOVEMBRO DE 2024</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 49, de 22 de janeiro de 2025</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 5.561, de 20 de setembro de 2024</t>
-  </si>
-  <si>
-    <t>DECRETO N° 68.347, DE 29 DE FEVEREIRO DE 2024</t>
-  </si>
-  <si>
-    <t>Portaria Normativa DETRAN-SP nº 21, de 1º de março de 2024</t>
-  </si>
-  <si>
-    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Disseminar a cultura de inovação, a gestão de projetos e processos
-Implementar gestão de performance e subsidiar as decisões com evidências
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Adotar o modelo de governança multinível em rede</t>
-  </si>
-  <si>
-    <t>Simplificar a gestão regulatória e induzir avanços nas normas de trânsito
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
-  </si>
-  <si>
-    <t>Comunicar com foco nos serviços, na prestação de contas e na construção da marca
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas</t>
   </si>
   <si>
     <t>Desenvolver competências convergentes com a estratégia institucional
@@ -561,459 +268,32 @@
 Subsidiar políticas públicas com foco em resultados concretos e mensuráveis</t>
   </si>
   <si>
-    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Disseminar a cultura de inovação, a gestão de projetos e processos
-Implantar mecanismos de gestão meritocrática e promover o espírito de equipe
-Empregar soluções tecnológicas inovadoras para alavancar os resultados</t>
-  </si>
-  <si>
-    <t>Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
-Garantir a segurança, integridade e efetiva governança de dados e informações</t>
-  </si>
-  <si>
-    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
-Garantir a segurança, integridade e efetiva governança de dados e informações
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance</t>
-  </si>
-  <si>
-    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
-Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Comunicar com foco nos serviços, na prestação de contas e na construção da marca
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
-Ser a plataforma de integração, informação e cooperação para o trânsito
-Empregar soluções tecnológicas inovadoras para alavancar os resultados</t>
-  </si>
-  <si>
-    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
-Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implementar gestão de performance e subsidiar as decisões com evidências
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
-Empregar soluções tecnológicas inovadoras para alavancar resultados
-Aperfeiçoar a estrutura organizacional e a qualificação do atendimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Otimizar a gestão de pessoas e adequar a força de trabalho
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implantar mecanismos de gestão meritocrática e promover o espírito de equipe
-</t>
-  </si>
-  <si>
-    <t>Adotar o modelo de governança multinível em rede</t>
-  </si>
-  <si>
-    <t>Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas 
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
-  </si>
-  <si>
-    <t>Empregar soluções tecnológicas inovadoras para alavancar os resultados
-Garantir a segurança, integridade e efetiva governança de dados e informações
-Otimizar a alocação e modernização dos equipamentos e da infraestrutura
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implementar gestão de performance e subsidiar as decisões com evidências
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
-  </si>
-  <si>
-    <t>Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
-Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
-Ser a plataforma de integração, informação e cooperação para o trânsito</t>
-  </si>
-  <si>
-    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade</t>
-  </si>
-  <si>
-    <t>Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Desenvolver competências convergentes com a estratégia institucional
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
-Aprimorar a educação corporativa e para o trânsito</t>
-  </si>
-  <si>
-    <t>Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Aprimorar a gestão de receitas e a aplicação de recursos orçamentários e financeiros</t>
-  </si>
-  <si>
-    <t>Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Desenvolver competências convergentes com a estratégia institucional
-Aprimorar a educação corporativa e para o trânsito</t>
-  </si>
-  <si>
-    <t>Simplificar a gestão regulatória e indizir avanços nas normas de trânsito
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
-Ser a plataforma de integração, informação e cooperação para o trânsito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estruturar o Sistema Estadual de Trânsito
-Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
-Ser a plataforma de integração, informação e cooperação para o trânsito
-Implementar rede colaborativa de parceiros em prol da segurança de todos
-</t>
-  </si>
-  <si>
-    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
-Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
-Comunicar com foco nos serviços, na prestação de contas e na construção da marca
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados</t>
-  </si>
-  <si>
-    <t>Contempla o mapa estratégico, cadeia de valor, portfólio de projetos estratégicos, portfólio de indicadores estratégicos e carta de serviços</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construção da marca do Detran-SP.
-Transmitir ao cidadão a eficiência e a confiança nos serviços.
-Transmitir o conceito disponibilidade do Detran-SP em atender o cidadão.
-</t>
-  </si>
-  <si>
-    <t>DCI</t>
-  </si>
-  <si>
-    <t>DHC</t>
-  </si>
-  <si>
-    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Cuidar das pessoas e valorizar o desempenho e o mérito
-Empregar soluções tecnológicas inovadoras para alavancar os resultados
-Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
-Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
-  </si>
-  <si>
-    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
-Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Otimizar a alocação e modernização dos equipamentos e da infraestrutura
-Otimizar a experiência e a satisfação do usuário com o atendimento
-Garantir a qualidade dos serviços delegados, com foco na excelência operacional
-Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Ser a plataforma de integração, informação e cooperação para o trânsito
-Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
-Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empregar soluções tecnológicas inovadoras para alavancar os resultados
-Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Otimizar a alocação e modernização dos equipamentos e da infraestrutura
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implementar gestão de performance e subsidiar as decisões com evidências
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
-Assegurar a qualidade dos serviços delegados com foco na excelência operacional
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Otimizar a experiência e a satisfação do usuário com o atendimento
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Comunicar com foco nos serviços, na prestação de contas e na construção da marca
-Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
-Empregar soluções tecnológicas inovadoras para alavancar os resultados
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
-Otimizar a gestão de pessoas e adequar a força de trabalho
-Desenvolver competências convergentes com a estratégia institucional
-Aprimorar a educação corporativa e para o trânsito
-Otimizar a experiência e a satisfação do usuário com o atendimento
-</t>
-  </si>
-  <si>
-    <t>ASCOM</t>
-  </si>
-  <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>Presidência</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implementação de um ambiente de trabalho digital (digital workplace) para os colaboradores do Detran-SP, consolidando em uma única plataforma as informações e ferramentas necessárias para o seu dia a dia, desde o onboarding até a aposentadoria.
-Esta solução estará alinhada com a essência do employee experience, visando aumentar o engajamento dos colaboradores através de funcionalidades que promovam a comunicação e transparência, a colaboração, o aprendizado e a produtividade.
-A solução tecnológica será integrada ao ecossistema da Microsoft, podendo ser acessada via Teams e contará com três subprodutos principais:
-Intranet (#SouDetranSP) – Microsoft Viva Connections: Portal interno com ênfase na organização, produtividade, comunicação institucional, interação e gestão de pessoas (praVC).
-Será o principal ponto de acesso para o colaborador obter informações institucionais, atualizações e encontrar as ferramentas necessárias para a execução de suas tarefas.
-Rede Social Corporativa – Microsoft Viva Engage: Ferramenta dedicada a promover a comunicação ágil com e entre os colaboradores, incentivando a colaboração e troca de conhecimentos.
-Permitirá a criação de comunidades baseadas em processos de negócio, possibilitando uma coleta de informações bottom-up, o que contribuirá para a melhoria contínua dos processos internos.</t>
-  </si>
-  <si>
-    <t>Dar visibilidade a todos os aspectos que compõem o parque tecnológico, incluindo a compreensão de todo investimento ativo e recorrente, sua disponibilidade, duplicidades, efetividade e eficiência operacional, assim como identificar e avaliar a necessidade e manutenção, mirando a melhoria contínua.
-Ainda, atualizar o desenho da topologia dos sistemas, destacando todas as suas conexões e integrações, possíveis pontos de melhorias e recomendações, e preparação dos ambientes para mudança.
-Priorizar os sistemas estratégicos para tomada de decisão quanto a investimento, aposentadoria de sistemas, convivência e reestruturação.
-O projeto engloba o mapeamento de todos os componentes do Detran-SP e interfaces que compõem a arquitetura dos sistemas, considerando, mas não se limitando, aos seguintes aspectos:</t>
-  </si>
-  <si>
-    <t>FASE 1 - Implementação do Serviço de Atendimento ao Cidadão (SAC), destinado ao tratamento das manifestações dos cidadãos.
-Desenvolvimento do Portal SAC com integração GOV.br
-Governança na gestão de contas.
-Governança na gestão da retaguarda (grupos e assuntos).
-Desenvolvimento de API para governança de dados.
-FASE 2 - Provimento de serviços aos usuários externos, bem como de serviços internos para as diretorias do Departamento Estadual de Trânsito de São Paulo (DETRAN-SP).
-Desenvolvimento do módulo serviços.
-Desenvolvimento da integração ao SEI.
-Integração com a Intranet.
-Desenvolvimento da TI para governança de dados.
-Disponibilização dos serviços de forma responsiva no novo APP Detran.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Plataforma Detran-Pay é a solução institucional responsável por gerar, processar e validar
-pagamentos oficiais, habilitar a execução de serviços, controlar o ciclo de vida da vistoria e
-realizar a distribuição financeira dos valores arrecadados entre os entes envolvidos no processo.
-A plataforma atua como núcleo financeiro e operacional, integrando cidadãos, meios de pagamento, Backoffice Operacional, Empresas Credenciadas de Vistoria (ECVs), Integradoras e Auditoras, garantindo que todo serviço executado esteja formalmente vinculado a um pagamento válido, conciliado e distribuído conforme regras institucionais.
-O Detran-Pay é responsável por:
-● gerar o QRCode de pagamento do serviço
-● processar e confirmar o pagamento
-● gerar o token de vistoria somente após confirmação financeira
-● controlar os status da vistoria em comunicação direta com o Backoffice Operacional
-● receber o encerramento da vistoria
-● realizar a distribuição financeira do valor total da vistoria entre:  ECV, Integradora e  Auditora
-● encaminhar a parcela institucional do Detran-SP por meio de pagamento via DARE
-● disponibilizar consulta de pagamentos para o Portal dos Credenciados
-● manter serviço de cadastro, atualização e consulta de dados bancários das entidades credenciadas
-● disponibilizar extrato de pagamentos ao cidadão autenticado
-● receber e registrar pedidos de restituição.
-</t>
-  </si>
-  <si>
-    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
-O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
-Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
-O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransomware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
-Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
-O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
-O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
-O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
-  </si>
-  <si>
-    <t>DCA</t>
-  </si>
-  <si>
-    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamentodos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
-  </si>
-  <si>
-    <t>O projeto tem por finalidade a implantação no âmbito do DETRAN-SP, dos dispositivos estabelecidos pela Lei Geral de Proteção de Dados, envolvendo todas as operações que possuam tratamento de dados pessoais no setor de Atendimento ao Cliente e domínio do site DETRAN-SP.
-Tem por finalidade, ainda, mapear os processos internos, estabelecer o plano de riscos e falhas, editar e/ou revisar políticas de privacidade, termos de privacidade, contratos e procedimentos operacionais e administrativos, bem como promover a conscientização dentro da autarquia sobre referida lei e boas práticas, visando garantir a total adesão à LGPD.
-Ao final do projeto, estima-se que o DETRAN-SP conte com os seguintes resultados:
-Política de Privacidade do Site.
-Política de Privacidade de Cookies.
-Políticas de Privacidade Institucionais.
-Programa Corporativo de Conscientização sobre à LGPD.
-Treinamento.
-Estruturação do Comitê de Privacidade
-Mapeamento de Dados Pessoais (Data Mapping) do Site e Atendimento ao Cliente.
-Gap Analysis do Site e Atendimento ao Cliente.
-Record Of Processing Activities (ROPA) inicial.
-Relatório de Impacto a Proteção de Dados (RIPD).
-Controle de Evidências.
-Adequação de aditivos contratuais.
-Termos de privacidade.
-Due Diligence.
-Privacy by Design.
-Plano de Resposta a Incidentes de Segurança.
-Criação do Controle de solicitações e resposta a titulares de dados.
-Criação do Processo de Sustentação ao Programa de Privacidade</t>
-  </si>
-  <si>
-    <t>Criação de um framework para estruturar a gestão e governança normativa do Estado de São Paulo, por meio de uma curadoria automatizada e centralizada, com o objetivo de realizar o gerenciamento do arcabouço legislativo do Estado, abrangendo o ciclo de vida da norma, no tempo e no espaço e garantindo a fidelidade dos dados ao longo do tempo.</t>
-  </si>
-  <si>
-    <t>Planejar, implementar e gerir a equipe de fornecedores para desenvolvimento do novo portal de serviços ao cidadão e do aplicativo móvel.</t>
-  </si>
-  <si>
-    <t>Implementar a transferência de propriedade de veículos de forma digital através do aplicativo CDT (Carteira Digital de Trânsito)</t>
-  </si>
-  <si>
-    <t>Realizar um workshop para reciclagem dos examinadores, com oficinas teóricas e práticas sobre o exame pratico de direção.
-Padronizar o exame em todo o estado.
-Criar um novo manual do exame prático.</t>
-  </si>
-  <si>
-    <t>Realizar o primeiro workshop com aulas teóricas e oficinas práticas para formação de público docentes e discentes de agentes de trânsito ativos/aptos para exercer a função de fiscalização de trânsito.
-A Diretoria de Fiscalização de Trânsito de forma inédita, junto com a EPT, formará seus próprios agentes de Fiscalização de trânsito para que atuem com foco na educação e segurança no trânsito em suas abordagens, juntamente com o apoio da PM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Definir a forma de como se publica portarias, revogar uma série de portarias e enxugar as novas portarias.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar uma plataforma de conhecimento para o Detran-SP, permitindo que os colaboradores de todas as áreas possam acessar, compartilhar e atualizar informações essenciais de forma prática e ágil. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
-  </si>
-  <si>
-    <t>Possível revisão de escopo - impacto no cronograma
-Não há previsão para o término do projeto</t>
-  </si>
-  <si>
-    <t>Aprovar a Estrutura Organizacional e o Quadro Demonstrativo dos Cargos em Comissão e das Funções de Confiança do Departamento Estadual de Trânsito - DETRAN-SP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Instituir o Sistema Estadual de Trânsito - SISTRAN-SP, com o objetivo de promover, no âmbito do Estado de São Paulo, a integração e a cooperação dos órgãos e entidades integrantes do Sistema Nacional de Trânsito - SNT, assegurando, entre esses, atuação uniforme, harmônica e coordenada.</t>
-  </si>
-  <si>
-    <t>Implementar o Programa de Integridade, que consiste em um conjunto estuturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar a bonificação por resultados no DETRAN-SP, nos termos da LEI COMPLEMENTAR N° 1.361, DE 21 DE OUTUBRO DE 2021.
-</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
-  </si>
-  <si>
-    <t>O projeto original contemplava os módulos ITSM, ITAM e ITOM
-Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
-  </si>
-  <si>
-    <t>Etapa 3 - concluída em 07/08/2026
-Etapa 4 definida pela DFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Etapa 4 -aprovação da presidência
-Etapa 4 - início - requisitos
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprovação  da etapa 4 - apenas após 13/10/2026, devido as férias do P.O. do projeto 
-</t>
-  </si>
-  <si>
-    <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
-Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 13/10/2026</t>
-  </si>
-  <si>
-    <t>Próximos Passos</t>
-  </si>
-  <si>
-    <t>Período da última semana</t>
-  </si>
-  <si>
-    <t>O que foi feito na última semana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhuma realização relevante registrada no período.
-</t>
-  </si>
-  <si>
-    <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be</t>
-  </si>
-  <si>
-    <t>PRJ032</t>
-  </si>
-  <si>
-    <t>HIVE</t>
-  </si>
-  <si>
-    <t>Implantar e desenvolver o Centro de Monitoramento, Comando e Controle de Operações deste Departamento Estadual de Trânsito (DETRAN-SP), destinado ao monitoramento e à gestão das operações da autarquia, utilizando-se de tecnologias para otimização do fluxo de informações e capacidade de pronta resposta aos incidentes e riscos operacionais.</t>
-  </si>
-  <si>
-    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
-Empregar soluções tecnológicas inovadoras para alavancar os resultados
-Estruturar o controle interno e a gestão de riscos com as melhores práticas de "compliance" (conformidade)
-Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
-Garantir a segurança, integridade e efetiva governança de dados e informações
-Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
-Implementar gestão de performance e subsidiar as decisões com evidências
-Otimizar a fiscalização com foco na promoção da segurança e da eficiência
-Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 4.429, de 17 de julho de 2024</t>
-  </si>
-  <si>
-    <t>Norma Gregório</t>
-  </si>
-  <si>
-    <t>Lucas Helder</t>
-  </si>
-  <si>
-    <t>Edson Arcas</t>
-  </si>
-  <si>
-    <t>José Iberê Fernandes Jr</t>
-  </si>
-  <si>
-    <t>Lucas Cesário</t>
-  </si>
-  <si>
-    <t>Akihiro Hayashi</t>
-  </si>
-  <si>
-    <t>Transformação Visual do Portal de Serviços DETRAN-SP -28/09/20026</t>
-  </si>
-  <si>
-    <t>Dependência da licitação da PRF</t>
-  </si>
-  <si>
-    <t>Aprovação da Etapa 4</t>
-  </si>
-  <si>
-    <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Catálogo de Auditoria Forense Digital - 04/11/2026
-Catálogoo de Segurança da Informação - 10/11/2026
-Catálogo de Gestão e Monitoramento - 03/12/2026
-Catálogo de Monitoramento de Incidentes - 09/12/2026
-</t>
-  </si>
-  <si>
-    <t>Implantação Catálogo de Proteção de Dados - 05/10/2026</t>
-  </si>
-  <si>
-    <t>%Consumo 
-Prazo</t>
-  </si>
-  <si>
-    <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correção de BUGs da V2 e V3
-</t>
+    <t>PRJ010</t>
+  </si>
+  <si>
+    <t>CONCURSO PÚBLICO</t>
+  </si>
+  <si>
+    <t>DSV</t>
   </si>
   <si>
     <t>Projeto segue dentro do prazo, conforme planejado
 Edital  publicado - provas 01/11/2026 (DAL)
 Material de treinamento em elaboração</t>
+  </si>
+  <si>
+    <t>Alinhamento com as áreas de negócio sobre o conteúdo programático, alinhamento com PO sobre entregas do projeto e detalhamento do fluxo de contratação com DAL;</t>
+  </si>
+  <si>
+    <t>Publicação do Edital - prova 01/11/2026
+Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes;</t>
+  </si>
+  <si>
+    <t>Atualização do cronograma, alinhamento com PO e EPT;</t>
+  </si>
+  <si>
+    <t>Atraso na revisão e validação do conteúdo da capacitação.
+Alterações normativas durante a produção do conteúdo da capacitação</t>
   </si>
   <si>
     <r>
@@ -1046,8 +326,116 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
+    <t xml:space="preserve">Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Otimizar a gestão de pessoas e adequar a força de trabalho
+Desenvolver competências convergentes com a estratégia institucional
+Aprimorar a educação corporativa e para o trânsito
+Otimizar a experiência e a satisfação do usuário com o atendimento
 </t>
+  </si>
+  <si>
+    <t>PRJ019</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 4.021, de 13 de junho de 2024</t>
+  </si>
+  <si>
+    <t>Lucas Cesário</t>
+  </si>
+  <si>
+    <t>FASE 1 - Implementação do Serviço de Atendimento ao Cidadão (SAC), destinado ao tratamento das manifestações dos cidadãos.
+Desenvolvimento do Portal SAC com integração GOV.br
+Governança na gestão de contas.
+Governança na gestão da retaguarda (grupos e assuntos).
+Desenvolvimento de API para governança de dados.
+FASE 2 - Provimento de serviços aos usuários externos, bem como de serviços internos para as diretorias do Departamento Estadual de Trânsito de São Paulo (DETRAN-SP).
+Desenvolvimento do módulo serviços.
+Desenvolvimento da integração ao SEI.
+Integração com a Intranet.
+Desenvolvimento da TI para governança de dados.
+Disponibilização dos serviços de forma responsiva no novo APP Detran.</t>
+  </si>
+  <si>
+    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
+Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implementar gestão de performance e subsidiar as decisões com evidências
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
+Empregar soluções tecnológicas inovadoras para alavancar resultados
+Aperfeiçoar a estrutura organizacional e a qualificação do atendimento</t>
+  </si>
+  <si>
+    <t>PRJ027</t>
+  </si>
+  <si>
+    <t>DETRAN PAY</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Plataforma Detran-Pay é a solução institucional responsável por gerar, processar e validar
+pagamentos oficiais, habilitar a execução de serviços, controlar o ciclo de vida da vistoria e
+realizar a distribuição financeira dos valores arrecadados entre os entes envolvidos no processo.
+A plataforma atua como núcleo financeiro e operacional, integrando cidadãos, meios de pagamento, Backoffice Operacional, Empresas Credenciadas de Vistoria (ECVs), Integradoras e Auditoras, garantindo que todo serviço executado esteja formalmente vinculado a um pagamento válido, conciliado e distribuído conforme regras institucionais.
+O Detran-Pay é responsável por:
+● gerar o QRCode de pagamento do serviço
+● processar e confirmar o pagamento
+● gerar o token de vistoria somente após confirmação financeira
+● controlar os status da vistoria em comunicação direta com o Backoffice Operacional
+● receber o encerramento da vistoria
+● realizar a distribuição financeira do valor total da vistoria entre:  ECV, Integradora e  Auditora
+● encaminhar a parcela institucional do Detran-SP por meio de pagamento via DARE
+● disponibilizar consulta de pagamentos para o Portal dos Credenciados
+● manter serviço de cadastro, atualização e consulta de dados bancários das entidades credenciadas
+● disponibilizar extrato de pagamentos ao cidadão autenticado
+● receber e registrar pedidos de restituição.
+</t>
+  </si>
+  <si>
+    <t>Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Aprimorar a gestão de receitas e a aplicação de recursos orçamentários e financeiros</t>
+  </si>
+  <si>
+    <t>PRJ011</t>
+  </si>
+  <si>
+    <t>ESTRATÉGIA DETRAN-SP</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 6, de 31 de agosto de 2023</t>
+  </si>
+  <si>
+    <t>Contempla o mapa estratégico, cadeia de valor, portfólio de projetos estratégicos, portfólio de indicadores estratégicos e carta de serviços</t>
+  </si>
+  <si>
+    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Disseminar a cultura de inovação, a gestão de projetos e processos
+Implementar gestão de performance e subsidiar as decisões com evidências
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Adotar o modelo de governança multinível em rede</t>
+  </si>
+  <si>
+    <t>PRJ001</t>
+  </si>
+  <si>
+    <t>FOCUS</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP Nº 2.889, DE 25 DE ABRIL DE 2024</t>
+  </si>
+  <si>
+    <t>Isabella Monteiro</t>
+  </si>
+  <si>
+    <t>DFT</t>
+  </si>
+  <si>
+    <t>Atenção</t>
   </si>
   <si>
     <t>Mudança de estratégia : 
@@ -1056,6 +444,10 @@
 Até o momento não temos resposta da PRF sobre a licitação</t>
   </si>
   <si>
+    <t xml:space="preserve">Nenhuma realização relevante registrada no período.
+</t>
+  </si>
+  <si>
     <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
 Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
 Não houve resposta da PRF até o momento.</t>
@@ -1065,24 +457,403 @@
 </t>
   </si>
   <si>
+    <t>Dependência da licitação da PRF</t>
+  </si>
+  <si>
+    <t>Estudar e implementar solução de monitoramento audiovisual da atuação do Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP).</t>
+  </si>
+  <si>
+    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Cuidar das pessoas e valorizar o desempenho e o mérito
+Empregar soluções tecnológicas inovadoras para alavancar os resultados
+Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
+Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
+  </si>
+  <si>
+    <t>PRJ012</t>
+  </si>
+  <si>
+    <t>GUILHOTINA REGULATÓRIA</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 1, de 20 de março de 2023</t>
+  </si>
+  <si>
+    <t>DGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Definir a forma de como se publica portarias, revogar uma série de portarias e enxugar as novas portarias.</t>
+  </si>
+  <si>
+    <t>Simplificar a gestão regulatória e induzir avanços nas normas de trânsito
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
+  </si>
+  <si>
+    <t>PRJ004</t>
+  </si>
+  <si>
+    <t>HABILITA-SP</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 49, de 22 de janeiro de 2025</t>
+  </si>
+  <si>
+    <t>Priscilla Elias e Silva</t>
+  </si>
+  <si>
+    <t>AEPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura.
+Desenhos técnicos necessários para contratação disponibilizados desde julho/2026.
+</t>
+  </si>
+  <si>
+    <t>Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP;
+Desenvolvimento das definições de layout, fluxos, materialidade e aplicabilidade do conceito;
+Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026; Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade</t>
+  </si>
+  <si>
+    <t>Prosseguimento, pela área de Infraestrutura, dos procedimentos necessários para contratação e implantação da unidade, contemplando os projetos e serviços necessários à execução da obra.
+Paralelamente, as definições consolidadas no projeto-piloto deverão subsidiar a padronização e replicabilidade do Habilita SP, com as devidas adequações às características e necessidades de cada futura unidade.</t>
+  </si>
+  <si>
+    <t>Necessidade de acompanhamento do andamento da contratação pela Infraestrutura, considerando que os desenhos técnicos estão disponibilizados desde julho/2026.
+Por se tratar do projeto-piloto, eventuais ajustes identificados durante as etapas de projeto executivo e implantação deverão ser avaliados quanto ao seu impacto no padrão a ser replicado nas demais unidades do Habilita SP.</t>
+  </si>
+  <si>
+    <t>Cronograma com estimativa do prazo final</t>
+  </si>
+  <si>
+    <t>Risco de impacto no cronograma de implantação, caso haja prolongamento das etapas de contratação dos projetos, obra e serviços.
+Considerando o caráter piloto da Estaiadinha, eventual atraso também poderá repercutir na validação prática das soluções e na consolidação do padrão para expansão do Habilita SP.</t>
+  </si>
+  <si>
+    <t>Desenvolver e implementar, no âmbito do Estado de São Paulo, as localidades e instalações de realização dos exames práticos de direção veicular, com fundamento no artigo 12, da Resolução CONTRAN nº 789, 18 de junho de 2020, promovendo a formação responsável de condutores e contribuindo para a segurança viária, por meio de processos íntegros e eficientes, atendimento de excelência e infraestrutura de alta qualidade.</t>
+  </si>
+  <si>
+    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
+Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Otimizar a alocação e modernização dos equipamentos e da infraestrutura
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Garantir a qualidade dos serviços delegados, com foco na excelência operacional
+Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção</t>
+  </si>
+  <si>
+    <t>PRJ016</t>
+  </si>
+  <si>
+    <t>HEIMDALL</t>
+  </si>
+  <si>
+    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
+O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
+Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
+O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransomware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
+Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
+O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
+O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
+O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
+  </si>
+  <si>
+    <t>Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
+Garantir a segurança, integridade e efetiva governança de dados e informações</t>
+  </si>
+  <si>
+    <t>PRJ032</t>
+  </si>
+  <si>
+    <t>HIVE</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 4.429, de 17 de julho de 2024</t>
+  </si>
+  <si>
+    <t>Norma Gregório</t>
+  </si>
+  <si>
+    <t>Implantar e desenvolver o Centro de Monitoramento, Comando e Controle de Operações deste Departamento Estadual de Trânsito (DETRAN-SP), destinado ao monitoramento e à gestão das operações da autarquia, utilizando-se de tecnologias para otimização do fluxo de informações e capacidade de pronta resposta aos incidentes e riscos operacionais.</t>
+  </si>
+  <si>
+    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
+Empregar soluções tecnológicas inovadoras para alavancar os resultados
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de "compliance" (conformidade)
+Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
+Garantir a segurança, integridade e efetiva governança de dados e informações
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implementar gestão de performance e subsidiar as decisões com evidências
+Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
+  </si>
+  <si>
+    <t>PRJ024</t>
+  </si>
+  <si>
+    <t>INFOSIGA</t>
+  </si>
+  <si>
+    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamentodos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
+  </si>
+  <si>
+    <t>Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
+Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
+Ser a plataforma de integração, informação e cooperação para o trânsito</t>
+  </si>
+  <si>
+    <t>PRJ006</t>
+  </si>
+  <si>
+    <t>ITSM-2026</t>
+  </si>
+  <si>
+    <t>Arturo Sangiovani</t>
+  </si>
+  <si>
+    <t>O projeto original contemplava os módulos ITSM, ITAM e ITOM
+Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
+  </si>
+  <si>
+    <t>Transformação Visual do Portal de Serviços DETRAN-SP -28/09/20026</t>
+  </si>
+  <si>
+    <t>Implantação Catálogo de Proteção de Dados - 05/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Catálogo de Auditoria Forense Digital - 04/11/2026
+Catálogoo de Segurança da Informação - 10/11/2026
+Catálogo de Gestão e Monitoramento - 03/12/2026
+Catálogo de Monitoramento de Incidentes - 09/12/2026
+</t>
+  </si>
+  <si>
+    <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
+  </si>
+  <si>
+    <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empregar soluções tecnológicas inovadoras para alavancar os resultados
+Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Otimizar a alocação e modernização dos equipamentos e da infraestrutura
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implementar gestão de performance e subsidiar as decisões com evidências
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
+</t>
+  </si>
+  <si>
+    <t>PRJ005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORNADA DO CIDADÃO </t>
+  </si>
+  <si>
+    <t>Lincon Santos</t>
+  </si>
+  <si>
+    <t>AEGE</t>
+  </si>
+  <si>
+    <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
+  </si>
+  <si>
+    <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be</t>
+  </si>
+  <si>
     <t>Todas jornadas finalizadas
 Todas as jornadas revisadas</t>
   </si>
   <si>
-    <t>Projeto apresenta significativo atraso e não há previsão para o término:
-Agente OCR
-Treinamento - 19/10
-Homologação - 20/10
-GMUD - 27/10
-Agente Q&amp;A da Wiki ("Isa") -Integração com o portal - Best 
-GMUD - 06/11
-Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
-Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão</t>
+    <t>Realinhar formato de indicadores de cada melhoria.</t>
+  </si>
+  <si>
+    <t>Validação das jornadas.</t>
+  </si>
+  <si>
+    <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
+  </si>
+  <si>
+    <t>Disseminar a cultura de inovação, a gestão de projetos e processos
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Otimizar a experiência e a satisfação do usuário com o atendimento</t>
+  </si>
+  <si>
+    <t>PRJ017</t>
+  </si>
+  <si>
+    <t>LGPD</t>
+  </si>
+  <si>
+    <t>Lucas Helder</t>
+  </si>
+  <si>
+    <t>O projeto tem por finalidade a implantação no âmbito do DETRAN-SP, dos dispositivos estabelecidos pela Lei Geral de Proteção de Dados, envolvendo todas as operações que possuam tratamento de dados pessoais no setor de Atendimento ao Cliente e domínio do site DETRAN-SP.
+Tem por finalidade, ainda, mapear os processos internos, estabelecer o plano de riscos e falhas, editar e/ou revisar políticas de privacidade, termos de privacidade, contratos e procedimentos operacionais e administrativos, bem como promover a conscientização dentro da autarquia sobre referida lei e boas práticas, visando garantir a total adesão à LGPD.
+Ao final do projeto, estima-se que o DETRAN-SP conte com os seguintes resultados:
+Política de Privacidade do Site.
+Política de Privacidade de Cookies.
+Políticas de Privacidade Institucionais.
+Programa Corporativo de Conscientização sobre à LGPD.
+Treinamento.
+Estruturação do Comitê de Privacidade
+Mapeamento de Dados Pessoais (Data Mapping) do Site e Atendimento ao Cliente.
+Gap Analysis do Site e Atendimento ao Cliente.
+Record Of Processing Activities (ROPA) inicial.
+Relatório de Impacto a Proteção de Dados (RIPD).
+Controle de Evidências.
+Adequação de aditivos contratuais.
+Termos de privacidade.
+Due Diligence.
+Privacy by Design.
+Plano de Resposta a Incidentes de Segurança.
+Criação do Controle de solicitações e resposta a titulares de dados.
+Criação do Processo de Sustentação ao Programa de Privacidade</t>
+  </si>
+  <si>
+    <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
+Garantir a segurança, integridade e efetiva governança de dados e informações
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance</t>
+  </si>
+  <si>
+    <t>PRJ022</t>
+  </si>
+  <si>
+    <t>LIVE</t>
+  </si>
+  <si>
+    <t>DCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
+  </si>
+  <si>
+    <t>Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas 
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
+  </si>
+  <si>
+    <t>PRJ013</t>
+  </si>
+  <si>
+    <t>MARCA DO DETRAN-SP</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 3, de 20 de julho de 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construção da marca do Detran-SP.
+Transmitir ao cidadão a eficiência e a confiança nos serviços.
+Transmitir o conceito disponibilidade do Detran-SP em atender o cidadão.
+</t>
+  </si>
+  <si>
+    <t>Comunicar com foco nos serviços, na prestação de contas e na construção da marca
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas</t>
+  </si>
+  <si>
+    <t>PRJ029</t>
+  </si>
+  <si>
+    <t>NORMAS</t>
+  </si>
+  <si>
+    <t>Criação de um framework para estruturar a gestão e governança normativa do Estado de São Paulo, por meio de uma curadoria automatizada e centralizada, com o objetivo de realizar o gerenciamento do arcabouço legislativo do Estado, abrangendo o ciclo de vida da norma, no tempo e no espaço e garantindo a fidelidade dos dados ao longo do tempo.</t>
+  </si>
+  <si>
+    <t>Simplificar a gestão regulatória e indizir avanços nas normas de trânsito
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
+Ser a plataforma de integração, informação e cooperação para o trânsito</t>
+  </si>
+  <si>
+    <t>PRJ007</t>
+  </si>
+  <si>
+    <t>PLATAFORMA ESTADUAL DE VISTORIA</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>Em andamento sem impeditivo.</t>
+  </si>
+  <si>
+    <t>Implantação assistida.</t>
+  </si>
+  <si>
+    <t>Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
+Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
+O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+</t>
+  </si>
+  <si>
+    <t>PRJ009</t>
+  </si>
+  <si>
+    <t>POLESTAR - MSFT</t>
+  </si>
+  <si>
+    <t>Artur Giannini</t>
+  </si>
+  <si>
+    <t>Projeto apresenta significativo atraso e não há previsão para o término.
+Agente OCR - Integração com portal - Best:
+-Treinamento - 19/10
+-Homologação - 20/10
+-GMUD - 27/10
+Agente Q&amp;A da Wiki ("Isa") - Integração com o portal - Best:
+-GMUD - 06/11
+Agente Revisor de Conteúdo da wiki:
+-Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de Conhecimento - entregue 14/06/2026
+Sistema de Atendimento - entregue 14/06/2026 (homologação)
+Base de Conhecimento - correções - entregue 30/09/2026
+OCR e Azure: tem bloqueio de configurações e migração para Produção </t>
+  </si>
+  <si>
+    <t>Capacitação em prompts - 19/10/2026
+Agente OCR de Documentos de Credenciamento - integração com o portal:
+-Treinamento - 19/10/2026
+-Homologação - 20/10/2026
+-GMUD - 27/10/2026
+-Denilson (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
+Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
 Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
 </t>
+  </si>
+  <si>
+    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.
+Risco de atraso na entrega:  OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção</t>
   </si>
   <si>
     <t xml:space="preserve">Base de Conhecimento
@@ -1093,82 +864,73 @@
 </t>
   </si>
   <si>
-    <t>Live 1.0 - entregue
-Consulta de peças - entregue
-Live 2.0 em andamento sem impeditivos</t>
-  </si>
-  <si>
-    <t>13/10/2026 a 16/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo app segue em fase de testes.
- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
-Primeira Habilitação
-Renovação da CNH
-Live2.0
-Autorização de Transporte Escolar (ATE)
-Gestão de Procuração 2.0
-Emplacar Veículo 0Km
-Novo APP DETRAN-SP</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Emplacar Veículo 0Km: Chaintec não forneceu cronograma de desenvolvimento.</t>
-  </si>
-  <si>
-    <t>Não tiveram atualizações:
-Autorização de Transporte Escolar (ATE): Aguardando contratação de fornecedor de desenvolvimento.
-Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
-  </si>
-  <si>
-    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
-Emplacar Veículo 0KM realizado o Kickoff.</t>
-  </si>
-  <si>
-    <t>Em andamento sem impeditivo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
-</t>
-  </si>
-  <si>
-    <t>Implantação assistida.</t>
-  </si>
-  <si>
-    <t>Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
-  </si>
-  <si>
-    <t>Realinhar formato de indicadores de cada melhoria.</t>
-  </si>
-  <si>
-    <t>Validação das jornadas.</t>
-  </si>
-  <si>
-    <t>Alinhamento com as áreas de negócio sobre o conteúdo programático, alinhamento com PO sobre entregas do projeto e detalhamento do fluxo de contratação com DAL;</t>
-  </si>
-  <si>
-    <t>Publicação do Edital - prova 01/11/2026
-Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes;</t>
-  </si>
-  <si>
-    <t>Atualização do cronograma, alinhamento com PO e EPT;</t>
-  </si>
-  <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação.
-Alterações normativas durante a produção do conteúdo da capacitação</t>
-  </si>
-  <si>
-    <t>16/11/2026</t>
+    <t>Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
+Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Assegurar a qualidade dos serviços delegados com foco na excelência operacional
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Empregar soluções tecnológicas inovadoras para alavancar os resultados
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de "compliance" (conformidade)
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Implementar rede colaborativa de parceiros em prol da segurança de todos
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo</t>
+  </si>
+  <si>
+    <t>PRJ031</t>
+  </si>
+  <si>
+    <t>PROGRAMA DE INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 21, de 1º de março de 2024</t>
+  </si>
+  <si>
+    <t>DCI</t>
+  </si>
+  <si>
+    <t>Implementar o Programa de Integridade, que consiste em um conjunto estuturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
+  </si>
+  <si>
+    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
+Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
+Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
+Comunicar com foco nos serviços, na prestação de contas e na construção da marca
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados</t>
+  </si>
+  <si>
+    <t>PRJ021</t>
+  </si>
+  <si>
+    <t>REFORMA ADMINISTRATIVA</t>
+  </si>
+  <si>
+    <t>DECRETO N° 69.053, DE 14 DE NOVEMBRO DE 2024</t>
+  </si>
+  <si>
+    <t>Aprovar a Estrutura Organizacional e o Quadro Demonstrativo dos Cargos em Comissão e das Funções de Confiança do Departamento Estadual de Trânsito - DETRAN-SP.</t>
+  </si>
+  <si>
+    <t>Adotar o modelo de governança multinível em rede</t>
+  </si>
+  <si>
+    <t>PRJ008</t>
+  </si>
+  <si>
+    <t>RST - REGISTRO DE SINISTRO DE TRÂNSITO</t>
+  </si>
+  <si>
+    <t>BeSolution</t>
   </si>
   <si>
     <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas, previsão de correção até 15/10/2026;
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção de BUGs da V2 e V3
+</t>
+  </si>
+  <si>
+    <t>16/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Correção de Bugs da V3 e subida na loja
@@ -1185,30 +947,271 @@
 Refinamento dos requisitos da V4 </t>
   </si>
   <si>
-    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.
-Risco de atraso na entrega:  OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de Conhecimento - entregue 14/06/2026
-Sistema de Atendimento - entregue 14/06/2026 (homologação)
-Base de Conhecimento - correções - entregue 30/09/2026
-OCR e Azure: tem bloqueio de configurações e migração para Produção </t>
-  </si>
-  <si>
-    <t>Capacitação em prompts - 19/10/2026
-Agente OCR de Documentos de Credenciamento - integração com o portal -
-Treinamento - 19/10/2026
-Homologação - 20/10/2026
-GMUD - 27/10/2026
-Denilson acionará Ricardo Aragão (superintendente da BU Prodesp) para destravar a migração de configuração OCR e Azure para Produção.
-Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
+    <t>Possível revisão de escopo - impacto no cronograma
+Não há previsão para o término do projeto</t>
+  </si>
+  <si>
+    <t>O RST (Registro de Sinistro de Trânsito) é um sistema digital inovador desenvolvido para modernizar o processo de registro e acompanhamento de acidentes de trânsito.
+O projeto tem como foco usabilidade, automação inteligente e integração com fontes oficiais, operando totalmente em nuvem e com arquitetura escalável, responsiva e segura.
+O sistema foi construído sobre bases técnicas e operacionais que garantem segurança, desempenho e conformidade.
+Foco em entregar App com módulo RST, sendo aplicativo único para todos órgãos de trânsito, com transcrição IA para agente de trânsito/GCM para reportar notificações e integração monta Infosiga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Ser a plataforma de integração, informação e cooperação para o trânsito
+Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
+Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas 
+</t>
+  </si>
+  <si>
+    <t>PRJ003</t>
+  </si>
+  <si>
+    <t>SIAUT</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 4.830, de 30 de julho de 2024</t>
+  </si>
+  <si>
+    <t>Cyntia Tiemi Nihy</t>
+  </si>
+  <si>
+    <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
+Devido a férias do P.O. do projeto essa aprovação só ocorrerá após seu retorno em 29/10.</t>
+  </si>
+  <si>
+    <t>Etapa 3 - concluída em 07/08/2026
+Etapa 4 definida pela DFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Etapa 4 -aprovação da presidência
+Etapa 4 - início - requisitos
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovação  da etapa 4 - apenas após 29/10/2026, devido as férias do P.O. do projeto 
+</t>
+  </si>
+  <si>
+    <t>Aprovação da Etapa 4</t>
+  </si>
+  <si>
+    <t>O Projeto SIAUT tem por objetivo operacionalizar a lavratura de autuações e a aplicação das respectivas penalidades administrativas oriunda as infrações administrativas conhecidas como "multas de balcão", de competência do DETRAN-SP, que serão implantadas através de 04 (quatro) ETAPAS.
+ETAPA1 (MULTAS ART. 165-D)
+ETAPA2 (MULTAS ARTS.233 e 257, § 8º - NIC)
+ETAPA3 (MULTAS ARTS. 162, 163 ou 164)
+ETAPA4 (MULTAS ARTS. 240, 241, 242 e 243)</t>
+  </si>
+  <si>
+    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros</t>
+  </si>
+  <si>
+    <t>PRJ030</t>
+  </si>
+  <si>
+    <t>SISTEMA ESTADUAL DO TRÂNSITO</t>
+  </si>
+  <si>
+    <t>DECRETO N° 68.347, DE 29 DE FEVEREIRO DE 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Instituir o Sistema Estadual de Trânsito - SISTRAN-SP, com o objetivo de promover, no âmbito do Estado de São Paulo, a integração e a cooperação dos órgãos e entidades integrantes do Sistema Nacional de Trânsito - SNT, assegurando, entre esses, atuação uniforme, harmônica e coordenada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estruturar o Sistema Estadual de Trânsito
+Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
+Ser a plataforma de integração, informação e cooperação para o trânsito
+Implementar rede colaborativa de parceiros em prol da segurança de todos
+</t>
+  </si>
+  <si>
+    <t>PRJ018</t>
+  </si>
+  <si>
+    <t>SUPERNOVA</t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 3.481, de 23 de maio de 2024</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>Planejar, implementar e gerir a equipe de fornecedores para desenvolvimento do novo portal de serviços ao cidadão e do aplicativo móvel.</t>
+  </si>
+  <si>
+    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
+Ampliar a disponibilidade, a eficiência e a acessibilidade digital de todos os serviços a todas as pessoas
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Comunicar com foco nos serviços, na prestação de contas e na construção da marca
+Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
+Ser a plataforma de integração, informação e cooperação para o trânsito
+Empregar soluções tecnológicas inovadoras para alavancar os resultados</t>
+  </si>
+  <si>
+    <t>PRJ025</t>
+  </si>
+  <si>
+    <t>TDV</t>
+  </si>
+  <si>
+    <t>Implementar a transferência de propriedade de veículos de forma digital através do aplicativo CDT (Carteira Digital de Trânsito)</t>
+  </si>
+  <si>
+    <t>Otimizar a experiência e a satisfação do usuário com o atendimento
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade</t>
+  </si>
+  <si>
+    <t>PRJ015</t>
+  </si>
+  <si>
+    <t>WIKI</t>
+  </si>
+  <si>
+    <t>José Iberê Fernandes Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar uma plataforma de conhecimento para o Detran-SP, permitindo que os colaboradores de todas as áreas possam acessar, compartilhar e atualizar informações essenciais de forma prática e ágil. </t>
+  </si>
+  <si>
+    <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
+Disseminar a cultura de inovação, a gestão de projetos e processos
+Implantar mecanismos de gestão meritocrática e promover o espírito de equipe
+Empregar soluções tecnológicas inovadoras para alavancar os resultados</t>
+  </si>
+  <si>
+    <t>PRJ026</t>
+  </si>
+  <si>
+    <t>WS ROTA DOS EXAMINADORES</t>
+  </si>
+  <si>
+    <t>DHC</t>
+  </si>
+  <si>
+    <t>Realizar um workshop para reciclagem dos examinadores, com oficinas teóricas e práticas sobre o exame pratico de direção.
+Padronizar o exame em todo o estado.
+Criar um novo manual do exame prático.</t>
+  </si>
+  <si>
+    <t>Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Desenvolver competências convergentes com a estratégia institucional
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
+Aprimorar a educação corporativa e para o trânsito</t>
+  </si>
+  <si>
+    <t>PRJ028</t>
+  </si>
+  <si>
+    <t>WS ROTA SEGURA</t>
+  </si>
+  <si>
+    <t>Akihiro Hayashi</t>
+  </si>
+  <si>
+    <t>Realizar o primeiro workshop com aulas teóricas e oficinas práticas para formação de público docentes e discentes de agentes de trânsito ativos/aptos para exercer a função de fiscalização de trânsito.
+A Diretoria de Fiscalização de Trânsito de forma inédita, junto com a EPT, formará seus próprios agentes de Fiscalização de trânsito para que atuem com foco na educação e segurança no trânsito em suas abordagens, juntamente com o apoio da PM.</t>
+  </si>
+  <si>
+    <t>Otimizar a fiscalização com foco na promoção da segurança e da eficiência
+Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
+Otimizar a experiência e a satisfação do usuário com o atendimento
+Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
+Desenvolver competências convergentes com a estratégia institucional
+Aprimorar a educação corporativa e para o trânsito</t>
+  </si>
+  <si>
+    <t>Status Entrega</t>
+  </si>
+  <si>
+    <t>Status Passo</t>
+  </si>
+  <si>
+    <t>Probabilidade</t>
+  </si>
+  <si>
+    <t>Impacto</t>
+  </si>
+  <si>
+    <t>Status Decisão</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Concluída</t>
+  </si>
+  <si>
+    <t>Não iniciado</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Baixo</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Em planejamento</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Médio</t>
+  </si>
+  <si>
+    <t>Em análise</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Próxima etapa</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Decidida</t>
+  </si>
+  <si>
+    <t>Suspenso</t>
+  </si>
+  <si>
+    <t>Atrasada</t>
+  </si>
+  <si>
+    <t>Atrasado</t>
+  </si>
+  <si>
+    <t>Escalonada</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1728,7 +1731,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1749,7 +1752,7 @@
     <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1757,91 +1760,91 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>219</v>
+        <v>8</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>220</v>
+        <v>9</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>240</v>
+        <v>11</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="409.5" hidden="1">
       <c r="A2" s="16" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="19" t="s">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H2" s="17"/>
       <c r="I2" s="20"/>
@@ -1861,31 +1864,31 @@
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="23" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="X2" s="23" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="246.6" hidden="1">
       <c r="A3" s="16" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="19" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="20"/>
@@ -1905,42 +1908,42 @@
       <c r="U3" s="22"/>
       <c r="V3" s="22"/>
       <c r="W3" s="23" t="s">
-        <v>191</v>
+        <v>35</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>167</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="203.1">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>253</v>
+        <v>43</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>259</v>
+        <v>45</v>
       </c>
       <c r="K4" s="9">
         <v>75</v>
@@ -1962,45 +1965,45 @@
         <v>46310</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>255</v>
+        <v>46</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>261</v>
+        <v>47</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>258</v>
+        <v>48</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>257</v>
+        <v>49</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="130.5" hidden="1">
       <c r="A5" s="16" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="20"/>
@@ -2020,40 +2023,40 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="285">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>243</v>
+        <v>61</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>266</v>
+        <v>62</v>
       </c>
       <c r="K6" s="7">
         <v>15</v>
@@ -2074,45 +2077,45 @@
         <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>269</v>
+        <v>65</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>186</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="261" hidden="1">
       <c r="A7" s="16" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="20"/>
@@ -2132,31 +2135,31 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="409.5" hidden="1">
       <c r="A8" s="16" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="20"/>
@@ -2176,31 +2179,31 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>171</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A9" s="16" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="20"/>
@@ -2220,42 +2223,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="120">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>254</v>
-      </c>
       <c r="J10" s="14" t="s">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="K10" s="9">
         <v>79</v>
@@ -2274,43 +2277,43 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>247</v>
+        <v>92</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>248</v>
+        <v>93</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>235</v>
+        <v>94</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29.1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="29.1" hidden="1">
       <c r="A11" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>117</v>
-      </c>
       <c r="C11" s="18" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="20"/>
@@ -2330,39 +2333,39 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="180">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="7">
@@ -2382,45 +2385,45 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="409.5" hidden="1">
       <c r="A13" s="16" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="20"/>
@@ -2440,33 +2443,33 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="130.5" hidden="1">
       <c r="A14" s="16" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>227</v>
+        <v>122</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="20"/>
@@ -2486,29 +2489,29 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>225</v>
+        <v>124</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>226</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="130.5" hidden="1">
       <c r="A15" s="16" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="20"/>
@@ -2528,40 +2531,40 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="150">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="K16" s="7">
         <v>70</v>
@@ -2582,52 +2585,52 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="43.5">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>237</v>
+        <v>144</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="K17" s="7">
         <v>90</v>
@@ -2648,43 +2651,43 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="409.5" hidden="1">
       <c r="A18" s="16" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="20"/>
@@ -2704,31 +2707,31 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A19" s="16" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="20"/>
@@ -2748,31 +2751,31 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="87" hidden="1">
       <c r="A20" s="16" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="20"/>
@@ -2792,31 +2795,31 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="101.45" hidden="1">
       <c r="A21" s="16" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="20"/>
@@ -2836,42 +2839,42 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="X21" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="174">
+      <c r="A22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" ht="180" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="I22" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="K22" s="28">
         <v>0.94</v>
@@ -2893,47 +2896,47 @@
       </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="3" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="255" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="229.5">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="K23" s="7">
         <v>50</v>
@@ -2952,45 +2955,45 @@
         <v>46311</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>277</v>
+        <v>184</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>252</v>
+        <v>187</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A24" s="16" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="20"/>
@@ -3010,31 +3013,31 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="57.95" hidden="1">
       <c r="A25" s="16" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="20"/>
@@ -3054,40 +3057,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="229.5">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="K26" s="7">
         <v>99</v>
@@ -3102,62 +3105,62 @@
         <v>46295</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="P26" s="8">
         <v>46308</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="152.25">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>212</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="E27" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>254</v>
-      </c>
       <c r="J27" s="14" t="s">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="K27" s="9">
         <v>92</v>
@@ -3178,45 +3181,45 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>86</v>
+        <v>221</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>87</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="87" hidden="1">
       <c r="A28" s="16" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="20"/>
@@ -3236,31 +3239,31 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>174</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="101.45" hidden="1">
       <c r="A29" s="16" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="20"/>
@@ -3280,31 +3283,31 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="57.95" hidden="1">
       <c r="A30" s="16" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="20"/>
@@ -3324,31 +3327,31 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="57.95" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="57.95" hidden="1">
       <c r="A31" s="16" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="20"/>
@@ -3368,31 +3371,31 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="87" hidden="1">
       <c r="A32" s="16" t="s">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="20"/>
@@ -3412,31 +3415,31 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>170</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="130.5" hidden="1">
       <c r="A33" s="16" t="s">
-        <v>115</v>
+        <v>248</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="20"/>
@@ -3456,10 +3459,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3557,125 +3560,125 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>258</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>259</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="45">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>266</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="45">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>268</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>271</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>36</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>273</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>274</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>275</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -3684,9 +3687,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>277</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3701,6 +3704,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3941,68 +3964,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C89E25-6125-441E-93E7-47A0CCCE31E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3169633-B441-438A-AFE6-F6DD014D5CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,13 +819,13 @@
   <si>
     <t>Projeto apresenta significativo atraso e não há previsão para o término.
 Agente OCR - Integração com portal - Best:
--Treinamento - 19/10
--Homologação - 20/10
--GMUD - 27/10
+--    Treinamento - 19/10
+--    Homologação - 20/10
+--    GMUD - 27/10
 Agente Q&amp;A da Wiki ("Isa") - Integração com o portal - Best:
--GMUD - 06/11
+--    GMUD - 06/11
 Agente Revisor de Conteúdo da wiki:
--Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
+--    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
     <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
@@ -840,10 +840,10 @@
   <si>
     <t>Capacitação em prompts - 19/10/2026
 Agente OCR de Documentos de Credenciamento - integração com o portal:
--Treinamento - 19/10/2026
--Homologação - 20/10/2026
--GMUD - 27/10/2026
--Denilson (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
+--    Treinamento - 19/10/2026
+--    Homologação - 20/10/2026
+--    GMUD - 27/10/2026
+--    Denilson (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
 Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
   </si>
   <si>
@@ -3704,26 +3704,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3964,8 +3944,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3973,7 +3973,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3169633-B441-438A-AFE6-F6DD014D5CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B2D8A81-12F9-4965-93BC-F31860816747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -981,7 +981,7 @@
   </si>
   <si>
     <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
-Devido a férias do P.O. do projeto essa aprovação só ocorrerá após seu retorno em 29/10.</t>
+Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
   </si>
   <si>
     <t>Etapa 3 - concluída em 07/08/2026
@@ -3704,6 +3704,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3944,15 +3953,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3965,11 +3965,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B2D8A81-12F9-4965-93BC-F31860816747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E476518-DFF0-4C02-B823-92C4C4075AB5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="280">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -197,29 +197,6 @@
   </si>
   <si>
     <t>13/10/2026 a 16/10/2026</t>
-  </si>
-  <si>
-    <t>Live 2.0: Executado testes integrados da jornada ponta a ponta, preparado treinamento e material de suporte da retaguarda do Portal. Efetuado testes e correções. Planejado desenvolvimento do app. Iniciado integração do Sispl com o mainframe.
-Emplacar Veículo 0KM realizado o Kickoff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo app segue em fase de testes.
- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live 2.0: Abrir GMUD do Socket-SISPL;
-</t>
-  </si>
-  <si>
-    <t>Não tiveram atualizações:
-Autorização de Transporte Escolar (ATE): Aguardando contratação de fornecedor de desenvolvimento.
-Gestão de Procuração 2.0: Em desenvolvimento de história de usuário.</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Emplacar Veículo 0Km: Chaintec não forneceu cronograma de desenvolvimento.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -280,9 +257,6 @@
     <t>Projeto segue dentro do prazo, conforme planejado
 Edital  publicado - provas 01/11/2026 (DAL)
 Material de treinamento em elaboração</t>
-  </si>
-  <si>
-    <t>Alinhamento com as áreas de negócio sobre o conteúdo programático, alinhamento com PO sobre entregas do projeto e detalhamento do fluxo de contratação com DAL;</t>
   </si>
   <si>
     <t>Publicação do Edital - prova 01/11/2026
@@ -656,9 +630,6 @@
     <t xml:space="preserve">JORNADA DO CIDADÃO </t>
   </si>
   <si>
-    <t>Lincon Santos</t>
-  </si>
-  <si>
     <t>AEGE</t>
   </si>
   <si>
@@ -790,12 +761,6 @@
     <t>Em andamento sem impeditivo.</t>
   </si>
   <si>
-    <t>Implantação assistida.</t>
-  </si>
-  <si>
-    <t>Plataforma estadual de vistorias: Implantar laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
-  </si>
-  <si>
     <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
 Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
 O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
@@ -1206,12 +1171,54 @@
   <si>
     <t>Cancelado</t>
   </si>
+  <si>
+    <t>Lincon Lacerda</t>
+  </si>
+  <si>
+    <t>19/10/2026 a 23/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo app
+</t>
+  </si>
+  <si>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Emplacar Veículo 0Km e Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
+Novo app: Provisionamento do ambiente de produção para o app.
+Live 2.0: Desenvolvido SISPL sem socket; Executado os testes de QA - Portal.</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário
+Novo app: Realizar correções do lote 1 dos serviços csm
+Autorização de Transporte Escolar: Iniciar desenvolvimento.
+Live 2.0: Homologar o desenvolvimento do portal; Abrir GMUD do Socket-SISPL, Executar QA-SISPL Sem socket.</t>
+  </si>
+  <si>
+    <t>19/20/2026 a 23/10/2026</t>
+  </si>
+  <si>
+    <t>Implantar-Laudos de Vistoria de Identificação Veicular-MVP2 (19/10/26)</t>
+  </si>
+  <si>
+    <t>Monitoramento do MVP-1 extendida até 30/10/26, sem impacto no prazo final.</t>
+  </si>
+  <si>
+    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronogama. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1341,7 +1348,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1424,6 +1431,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1731,28 +1741,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="2" max="2" width="25" style="29" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.5703125" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" customWidth="1"/>
+    <col min="8" max="8" width="40.54296875" customWidth="1"/>
+    <col min="9" max="9" width="25.54296875" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.5703125" customWidth="1"/>
-    <col min="23" max="23" width="50.5703125" customWidth="1"/>
-    <col min="24" max="24" width="120.5703125" customWidth="1"/>
+    <col min="17" max="22" width="40.54296875" customWidth="1"/>
+    <col min="23" max="23" width="50.54296875" customWidth="1"/>
+    <col min="24" max="24" width="120.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.95" customHeight="1">
+    <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1836,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1">
+    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1870,7 +1880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.6" hidden="1">
+    <row r="3" spans="1:24" ht="246.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1914,7 +1924,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="203.1">
+    <row r="4" spans="1:24" ht="203" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1940,17 +1950,17 @@
         <v>43</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>273</v>
       </c>
       <c r="K4" s="9">
         <v>75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.93128834355828216</v>
+        <v>0.93251533742331283</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -1962,42 +1972,38 @@
         <v>46377</v>
       </c>
       <c r="P4" s="10">
-        <v>46310</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>46315</v>
+      </c>
+      <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>49</v>
+        <v>272</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1">
+    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>28</v>
@@ -2023,25 +2029,25 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="285">
+    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -2050,13 +2056,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>62</v>
+        <v>271</v>
       </c>
       <c r="K6" s="7">
         <v>15</v>
@@ -2077,36 +2083,36 @@
         <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>65</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="261" hidden="1">
-      <c r="A7" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2135,25 +2141,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1">
+    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2179,25 +2185,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="9" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>28</v>
@@ -2223,42 +2229,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="X9" s="23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="120">
-      <c r="A10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K10" s="9">
         <v>79</v>
@@ -2277,37 +2283,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29.1" hidden="1">
+    <row r="11" spans="1:24" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2333,36 +2339,36 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="X11" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="X11" s="23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="180">
-      <c r="A12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>44</v>
@@ -2385,34 +2391,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1">
+    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2443,27 +2449,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1">
+    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2489,23 +2495,23 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1">
+    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>28</v>
@@ -2531,22 +2537,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="150">
+    <row r="16" spans="1:24" ht="145" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2555,16 +2561,16 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K16" s="7">
         <v>70</v>
@@ -2585,37 +2591,37 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="43.5">
+    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>142</v>
+        <v>269</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2624,13 +2630,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K17" s="7">
         <v>90</v>
@@ -2651,34 +2657,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1">
+    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2707,25 +2713,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="19" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2751,25 +2757,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" hidden="1">
+    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>28</v>
@@ -2795,25 +2801,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.45" hidden="1">
+    <row r="21" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2839,27 +2845,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174">
+    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2868,16 +2874,16 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>44</v>
+        <v>275</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="K22" s="28">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="L22" s="7">
         <v>100</v>
@@ -2892,51 +2898,55 @@
         <v>46379</v>
       </c>
       <c r="P22" s="8">
-        <v>46310</v>
-      </c>
-      <c r="Q22" s="14"/>
+        <v>46315</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>277</v>
+      </c>
       <c r="R22" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="S22" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="229.5">
+    <row r="23" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>179</v>
+        <v>169</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="K23" s="7">
         <v>50</v>
@@ -2955,39 +2965,39 @@
         <v>46311</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="24" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3013,25 +3023,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="57.95" hidden="1">
+    <row r="25" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>28</v>
@@ -3057,40 +3067,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="229.5">
+    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="K26" s="7">
         <v>99</v>
@@ -3105,62 +3115,62 @@
         <v>46295</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="P26" s="8">
         <v>46308</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="152.25">
+    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K27" s="9">
         <v>92</v>
@@ -3181,39 +3191,39 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1">
+    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F28" s="19" t="s">
         <v>28</v>
@@ -3239,25 +3249,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.45" hidden="1">
+    <row r="29" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3283,25 +3293,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="57.95" hidden="1">
+    <row r="30" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3327,25 +3337,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="57.95" hidden="1">
+    <row r="31" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3371,25 +3381,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1">
+    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3415,25 +3425,25 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1">
+    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3459,10 +3469,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3480,6 @@
     <filterColumn colId="5">
       <filters>
         <filter val="Em andamento"/>
-        <filter val="Problema"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X33">
@@ -3560,12 +3569,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="10.5703125" customWidth="1"/>
+    <col min="1" max="7" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30">
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3573,50 +3582,50 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30">
+    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45">
+    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3625,58 +3634,58 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45">
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3687,9 +3696,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3965,15 +3974,41 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E476518-DFF0-4C02-B823-92C4C4075AB5}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62ED204-F093-4D34-8E57-D118D995FCE5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -196,7 +196,24 @@
 Live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
-    <t>13/10/2026 a 16/10/2026</t>
+    <t>19/20/2026 a 23/10/2026</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
+Novo app: Provisionamento do ambiente de produção para o app.
+Live 2.0: Desenvolvido SISPL sem socket; Executado os testes de QA - Portal.</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário
+Novo app: Realizar correções do lote 1 dos serviços csm
+Autorização de Transporte Escolar: Iniciar desenvolvimento.
+Live 2.0: Homologar o desenvolvimento do portal; Abrir GMUD do Socket-SISPL, Executar QA-SISPL Sem socket.</t>
+  </si>
+  <si>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Emplacar Veículo 0Km e Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -257,6 +274,10 @@
     <t>Projeto segue dentro do prazo, conforme planejado
 Edital  publicado - provas 01/11/2026 (DAL)
 Material de treinamento em elaboração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo app
+</t>
   </si>
   <si>
     <t>Publicação do Edital - prova 01/11/2026
@@ -630,6 +651,9 @@
     <t xml:space="preserve">JORNADA DO CIDADÃO </t>
   </si>
   <si>
+    <t>Lincon Lacerda</t>
+  </si>
+  <si>
     <t>AEGE</t>
   </si>
   <si>
@@ -761,6 +785,18 @@
     <t>Em andamento sem impeditivo.</t>
   </si>
   <si>
+    <t>Implantar-Laudos de Vistoria de Identificação Veicular-MVP2 (19/10/26)</t>
+  </si>
+  <si>
+    <t>Monitoramento do MVP-1 extendida até 30/10/26, sem impacto no prazo final.</t>
+  </si>
+  <si>
+    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronogama. </t>
+  </si>
+  <si>
     <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
 Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
 O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
@@ -783,13 +819,14 @@
   </si>
   <si>
     <t>Projeto apresenta significativo atraso e não há previsão para o término.
-Agente OCR - Integração com portal - Best:
---    Treinamento - 19/10
---    Homologação - 20/10
---    GMUD - 27/10
-Agente Q&amp;A da Wiki ("Isa") - Integração com o portal - Best:
+Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure.
+--    Treinamento - TBD
+--    Homologação - TBD
+--    GMUD - TBD
+Agente Q&amp;A da Wiki ("Isa") - wave 2 - Integração com o portal - Best:
+--    Desenvolvimento - 30/10
 --    GMUD - 06/11
-Agente Revisor de Conteúdo da wiki:
+Agente Revisor de Conteúdo da wiki - wave 3:
 --    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
@@ -797,28 +834,29 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Base de Conhecimento - entregue 14/06/2026
+    <t>Base de Conhecimento - entregue 14/06/2026
 Sistema de Atendimento - entregue 14/06/2026 (homologação)
 Base de Conhecimento - correções - entregue 30/09/2026
-OCR e Azure: tem bloqueio de configurações e migração para Produção </t>
-  </si>
-  <si>
-    <t>Capacitação em prompts - 19/10/2026
-Agente OCR de Documentos de Credenciamento - integração com o portal:
---    Treinamento - 19/10/2026
---    Homologação - 20/10/2026
---    GMUD - 27/10/2026
---    Denilson (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
-Agente Q&amp;A da Wiki ("Isa") - Microsoft - 06/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente Revisor de Conteúdo da wiki - Microsoft - sem previsão
-Agente Revisor de Conteúdo da wiki - Integração com o portal - Best - sem previsão
-</t>
-  </si>
-  <si>
-    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.
-Risco de atraso na entrega:  OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção</t>
+Capacitação em prompts - 19/10/2026</t>
+  </si>
+  <si>
+    <t>Agente OCR de Documentos de Credenciamento - integração com o portal:
+--    Treinamento - TBD
+--    Homologação - TBD
+--    GMUD - TBD
+--    Denilson/Gianini (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
+Agente Q&amp;A da Wiki ("Isa") - wave 2 - Microsoft - 06/11/2026
+Agente Revisor de Conteúdo da wiki - wave 3:
+--    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
+  </si>
+  <si>
+    <t>Pendente aprovação de recursos Azure pela Prodesp para definição de cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
+  </si>
+  <si>
+    <t>OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção.</t>
+  </si>
+  <si>
+    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
   </si>
   <si>
     <t xml:space="preserve">Base de Conhecimento
@@ -887,33 +925,35 @@
     <t>BeSolution</t>
   </si>
   <si>
-    <t xml:space="preserve">Na homologação da V2 e V3 do aplicativo foram encontrados mais de 80 problemas, previsão de correção até 15/10/2026;
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correção de BUGs da V2 e V3
-</t>
-  </si>
-  <si>
-    <t>16/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correção de Bugs da V3 e subida na loja
-</t>
-  </si>
-  <si>
-    <t>Homologação (correção dos 54 itens) - 06/10/2026
-Subida na loja -  16/10/2026
-27/10/2026 Inicio da utilização e prova de campo por 20 dias;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O módulo Admin será entregue com a V4
-O  ininício da versão V4 está condicionada ao término da V3.
-Refinamento dos requisitos da V4 </t>
-  </si>
-  <si>
-    <t>Possível revisão de escopo - impacto no cronograma
-Não há previsão para o término do projeto</t>
+    <t>Entrega V3.1: Correção de 10 itens prioritários:
+--Homologação Detran: 11/11.
+Publicação do app RST concluída nas lojas Android (Google Play) e iOS (App Store): aguardando aprovação das lojas.
+Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo)
+Mapa de lesões V4 - em desenvolvimento: 
+--Homologação em 30/10.
+Módulo CST (V4):
+--Homologação Detran: 15/11.
+--Estimativa Be Solution e viabilidade técnica: 23/10.</t>
+  </si>
+  <si>
+    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App nas lojas e cadastro de usuários</t>
+  </si>
+  <si>
+    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço;
+Entrega V3.1: Correção de 10 itens prioritários:
+--Homologação Detran: 11/11.
+Aprovação do APP pela lojas Android (Google Play) e iOS (App Store)
+Mapa de lesões V4 em desenvolvimento:
+--Homologação: 30/10.
+Módulo CST (V4):
+--Homologação Detran: 15/11.
+--Estimativa Be Solution e viabilidade técnica: 23/10.</t>
+  </si>
+  <si>
+    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)</t>
+  </si>
+  <si>
+    <t>Possível revisão de escopo - impacto no cronograma</t>
   </si>
   <si>
     <t>O RST (Registro de Sinistro de Trânsito) é um sistema digital inovador desenvolvido para modernizar o processo de registro e acompanhamento de acidentes de trânsito.
@@ -1171,54 +1211,12 @@
   <si>
     <t>Cancelado</t>
   </si>
-  <si>
-    <t>Lincon Lacerda</t>
-  </si>
-  <si>
-    <t>19/10/2026 a 23/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo app
-</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Emplacar Veículo 0Km e Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
-Novo app: Provisionamento do ambiente de produção para o app.
-Live 2.0: Desenvolvido SISPL sem socket; Executado os testes de QA - Portal.</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário
-Novo app: Realizar correções do lote 1 dos serviços csm
-Autorização de Transporte Escolar: Iniciar desenvolvimento.
-Live 2.0: Homologar o desenvolvimento do portal; Abrir GMUD do Socket-SISPL, Executar QA-SISPL Sem socket.</t>
-  </si>
-  <si>
-    <t>19/20/2026 a 23/10/2026</t>
-  </si>
-  <si>
-    <t>Implantar-Laudos de Vistoria de Identificação Veicular-MVP2 (19/10/26)</t>
-  </si>
-  <si>
-    <t>Monitoramento do MVP-1 extendida até 30/10/26, sem impacto no prazo final.</t>
-  </si>
-  <si>
-    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronogama. </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1741,28 +1739,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
-    <col min="3" max="3" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.54296875" customWidth="1"/>
-    <col min="9" max="9" width="25.54296875" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.54296875" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.54296875" customWidth="1"/>
-    <col min="23" max="23" width="50.54296875" customWidth="1"/>
-    <col min="24" max="24" width="120.54296875" customWidth="1"/>
+    <col min="17" max="22" width="40.5703125" customWidth="1"/>
+    <col min="23" max="23" width="50.5703125" customWidth="1"/>
+    <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1836,7 +1834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="409.5" hidden="1">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1880,7 +1878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="246.6" hidden="1">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1924,7 +1922,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="229.5">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1950,17 +1948,17 @@
         <v>43</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>273</v>
+        <v>45</v>
       </c>
       <c r="K4" s="9">
         <v>75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.93251533742331283</v>
+        <v>0.93619631901840494</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -1976,34 +1974,34 @@
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>274</v>
+        <v>46</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>272</v>
+        <v>47</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="130.5" hidden="1">
       <c r="A5" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>28</v>
@@ -2029,25 +2027,25 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="275.25">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -2056,13 +2054,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>271</v>
+        <v>60</v>
       </c>
       <c r="K6" s="7">
         <v>15</v>
@@ -2083,36 +2081,36 @@
         <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="261" hidden="1">
       <c r="A7" s="16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2141,25 +2139,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="409.5" hidden="1">
       <c r="A8" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2185,25 +2183,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A9" s="16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>28</v>
@@ -2229,42 +2227,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="121.5">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K10" s="9">
         <v>79</v>
@@ -2283,37 +2281,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="29.1" hidden="1">
       <c r="A11" s="16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2339,36 +2337,36 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="183">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>44</v>
@@ -2391,34 +2389,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="409.5" hidden="1">
       <c r="A13" s="16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2449,27 +2447,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="130.5" hidden="1">
       <c r="A14" s="16" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2495,23 +2493,23 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="130.5" hidden="1">
       <c r="A15" s="16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>28</v>
@@ -2537,22 +2535,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="152.25">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2561,16 +2559,16 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K16" s="7">
         <v>70</v>
@@ -2591,37 +2589,37 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" ht="45.75">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2630,13 +2628,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K17" s="7">
         <v>90</v>
@@ -2657,34 +2655,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" ht="409.5" hidden="1">
       <c r="A18" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2713,25 +2711,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A19" s="16" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2757,25 +2755,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" ht="87" hidden="1">
       <c r="A20" s="16" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>28</v>
@@ -2801,25 +2799,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" ht="101.45" hidden="1">
       <c r="A21" s="16" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2845,27 +2843,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" ht="180">
       <c r="A22" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2874,13 +2872,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>275</v>
+        <v>44</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="K22" s="28">
         <v>0.93</v>
@@ -2901,52 +2899,52 @@
         <v>46315</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" ht="275.25">
       <c r="A23" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="K23" s="7">
         <v>50</v>
@@ -2962,42 +2960,44 @@
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="8">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="T23" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A24" s="16" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3023,25 +3023,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" ht="57.95" hidden="1">
       <c r="A25" s="16" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>28</v>
@@ -3067,40 +3067,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" ht="229.5">
       <c r="A26" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K26" s="7">
         <v>99</v>
@@ -3114,63 +3114,63 @@
       <c r="N26" s="8">
         <v>46295</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>196</v>
+      <c r="O26" s="8">
+        <v>46356</v>
       </c>
       <c r="P26" s="8">
-        <v>46308</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>198</v>
+        <v>46317</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>206</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" ht="152.25">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K27" s="9">
         <v>92</v>
@@ -3191,39 +3191,39 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" ht="87" hidden="1">
       <c r="A28" s="16" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F28" s="19" t="s">
         <v>28</v>
@@ -3249,25 +3249,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" ht="101.45" hidden="1">
       <c r="A29" s="16" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3293,25 +3293,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" ht="57.95" hidden="1">
       <c r="A30" s="16" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3337,25 +3337,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" ht="57.95" hidden="1">
       <c r="A31" s="16" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3381,25 +3381,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" ht="87" hidden="1">
       <c r="A32" s="16" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3425,25 +3425,25 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" ht="130.5" hidden="1">
       <c r="A33" s="16" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3469,10 +3469,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3558,7 +3558,7 @@
           <x14:formula1>
             <xm:f>Listas!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>J9:J33 J2:J5 G2:I33</xm:sqref>
+          <xm:sqref>J9:J33 J2:J5 Q26:R26 G2:I33</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3569,12 +3569,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="7" width="10.54296875" customWidth="1"/>
+    <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="30">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3582,50 +3582,50 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="30">
       <c r="A2" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="45">
       <c r="A3" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3634,58 +3634,58 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="45">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="30">
       <c r="A5" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3696,9 +3696,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3713,6 +3713,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3721,7 +3732,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3962,53 +3973,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62ED204-F093-4D34-8E57-D118D995FCE5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9651C031-81B3-420B-B132-377A7286F9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -927,7 +927,7 @@
   <si>
     <t>Entrega V3.1: Correção de 10 itens prioritários:
 --Homologação Detran: 11/11.
-Publicação do app RST concluída nas lojas Android (Google Play) e iOS (App Store): aguardando aprovação das lojas.
+Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): aguardando aprovação das lojas.
 Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo)
 Mapa de lesões V4 - em desenvolvimento: 
 --Homologação em 30/10.
@@ -3713,26 +3713,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3973,8 +3953,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3982,7 +3982,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9651C031-81B3-420B-B132-377A7286F9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BAD7AF6-24F8-494C-A969-D44B6DCEC10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -830,8 +830,8 @@
 --    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
-    <t xml:space="preserve">Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
-</t>
+    <t>Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
+Capacitação em prompts - 19/10/2026</t>
   </si>
   <si>
     <t>Base de Conhecimento - entregue 14/06/2026
@@ -3713,6 +3713,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3953,28 +3973,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3982,7 +3982,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BAD7AF6-24F8-494C-A969-D44B6DCEC10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9E2C08A-8D49-4AB4-9838-6FC55FAB22AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -830,7 +830,7 @@
 --    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
-    <t>Sistema de Atendimento GMUD  para produção - 05/10 - apenas ECVs
+    <t>Sistema de Atendimento: GMUD  apenas ECVs - 05/10/2026
 Capacitação em prompts - 19/10/2026</t>
   </si>
   <si>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9E2C08A-8D49-4AB4-9838-6FC55FAB22AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C87F15E-5C04-4FC5-9F25-D0D3404F2D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="278">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -200,7 +200,7 @@
   </si>
   <si>
     <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
-Novo app: Provisionamento do ambiente de produção para o app.
+Novo app: Realizado o Provisionamento do ambiente de produção para o app.
 Live 2.0: Desenvolvido SISPL sem socket; Executado os testes de QA - Portal.</t>
   </si>
   <si>
@@ -220,6 +220,7 @@
 Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
 Primeira Habilitação
 Renovação da CNH
+Live 1.0
 Live2.0
 Autorização de Transporte Escolar (ATE)
 Gestão de Procuração 2.0
@@ -276,19 +277,22 @@
 Material de treinamento em elaboração</t>
   </si>
   <si>
+    <t>19/10/2026 a 23/10/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Novo app
 </t>
   </si>
   <si>
-    <t>Publicação do Edital - prova 01/11/2026
-Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes;</t>
-  </si>
-  <si>
-    <t>Atualização do cronograma, alinhamento com PO e EPT;</t>
-  </si>
-  <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação.
-Alterações normativas durante a produção do conteúdo da capacitação</t>
+    <t>Publicação do Edital - Prova 01/11/2026;
+Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes.</t>
+  </si>
+  <si>
+    <t>Atualização do cronograma, alinhamento com PO e EPT.</t>
+  </si>
+  <si>
+    <t>Atraso na revisão e validação do conteúdo da capacitação;
+Alterações normativas durante a produção do conteúdo da capacitação.</t>
   </si>
   <si>
     <r>
@@ -433,10 +437,10 @@
     <t>Atenção</t>
   </si>
   <si>
-    <t>Mudança de estratégia : 
-Decisão de entrar na licitação da PRF para aquisição das câmeras corporais.
-Dependência de licitação a ser realizada por outro órgão.
-Até o momento não temos resposta da PRF sobre a licitação</t>
+    <t>Mudança de estratégia: 
+Decisão de entrar na licitação da PRF para aquisição das câmeras corporais;
+Dependência de licitação a ser realizada por outro órgão;
+Até o momento não temos resposta da PRF sobre a licitação.</t>
   </si>
   <si>
     <t xml:space="preserve">Nenhuma realização relevante registrada no período.
@@ -448,11 +452,11 @@
 Não houve resposta da PRF até o momento.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação
+    <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação.
 </t>
   </si>
   <si>
-    <t>Dependência da licitação da PRF</t>
+    <t>Dependência da licitação da PRF.</t>
   </si>
   <si>
     <t>Estudar e implementar solução de monitoramento audiovisual da atuação do Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP).</t>
@@ -612,25 +616,25 @@
     <t>Arturo Sangiovani</t>
   </si>
   <si>
-    <t>O projeto original contemplava os módulos ITSM, ITAM e ITOM
-Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
-  </si>
-  <si>
-    <t>Transformação Visual do Portal de Serviços DETRAN-SP -28/09/20026</t>
-  </si>
-  <si>
-    <t>Implantação Catálogo de Proteção de Dados - 05/10/2026</t>
+    <t>O projeto original contemplava os módulos ITSM, ITAM e ITOM.
+Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
+  </si>
+  <si>
+    <t>Transformação Visual do Portal de Serviços DETRAN-SP -28/09/20026.</t>
+  </si>
+  <si>
+    <t>Implantação Catálogo de Proteção de Dados - 05/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">
-Catálogo de Auditoria Forense Digital - 04/11/2026
-Catálogoo de Segurança da Informação - 10/11/2026
-Catálogo de Gestão e Monitoramento - 03/12/2026
-Catálogo de Monitoramento de Incidentes - 09/12/2026
+Catálogo de Auditoria Forense Digital - 04/11/2026;
+Catálogo de Segurança da Informação - 10/11/2026;
+Catálogo de Gestão e Monitoramento - 03/12/2026;
+Catálogo de Monitoramento de Incidentes - 09/12/2026.
 </t>
   </si>
   <si>
-    <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM</t>
+    <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
   </si>
   <si>
     <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
@@ -660,7 +664,7 @@
     <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
   </si>
   <si>
-    <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be</t>
+    <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be.</t>
   </si>
   <si>
     <t>Todas jornadas finalizadas
@@ -670,7 +674,7 @@
     <t>Realinhar formato de indicadores de cada melhoria.</t>
   </si>
   <si>
-    <t>Validação das jornadas.</t>
+    <t xml:space="preserve">Validação das jornadas. </t>
   </si>
   <si>
     <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
@@ -791,7 +795,7 @@
     <t>Monitoramento do MVP-1 extendida até 30/10/26, sem impacto no prazo final.</t>
   </si>
   <si>
-    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026</t>
+    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronogama. </t>
@@ -820,40 +824,38 @@
   <si>
     <t>Projeto apresenta significativo atraso e não há previsão para o término.
 Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure.
---    Treinamento - TBD
---    Homologação - TBD
---    GMUD - TBD
+- Treinamento - TBD;
+- Homologação - TBD;
+- GMUD - TBD.
 Agente Q&amp;A da Wiki ("Isa") - wave 2 - Integração com o portal - Best:
---    Desenvolvimento - 30/10
---    GMUD - 06/11
+- Desenvolvimento - 30/10;
+- GMUD - 06/11.
 Agente Revisor de Conteúdo da wiki - wave 3:
---    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
-  </si>
-  <si>
-    <t>Sistema de Atendimento: GMUD  apenas ECVs - 05/10/2026
-Capacitação em prompts - 19/10/2026</t>
+- Entrega Microsoft e Integração com portal pela Best - sem previsão.</t>
+  </si>
+  <si>
+    <t>Sistema de Atendimento: GMUD  apenas ECVs - 05/10/2026</t>
   </si>
   <si>
     <t>Base de Conhecimento - entregue 14/06/2026
 Sistema de Atendimento - entregue 14/06/2026 (homologação)
-Base de Conhecimento - correções - entregue 30/09/2026
-Capacitação em prompts - 19/10/2026</t>
+Base de Conhecimento - correções - entregue 30/09/2026</t>
   </si>
   <si>
     <t>Agente OCR de Documentos de Credenciamento - integração com o portal:
 --    Treinamento - TBD
 --    Homologação - TBD
 --    GMUD - TBD
---    Denilson/Gianini (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção.
+--    Denilson/Gianini (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção e seguir com cronograma de entrega.
 Agente Q&amp;A da Wiki ("Isa") - wave 2 - Microsoft - 06/11/2026
 Agente Revisor de Conteúdo da wiki - wave 3:
 --    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
-    <t>Pendente aprovação de recursos Azure pela Prodesp para definição de cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
-  </si>
-  <si>
-    <t>OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção.</t>
+    <t>O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e dar continuidade ao cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
+  </si>
+  <si>
+    <t>OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção. Esta aprovação foi realizada em 23/10.</t>
   </si>
   <si>
     <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
@@ -926,28 +928,28 @@
   </si>
   <si>
     <t>Entrega V3.1: Correção de 10 itens prioritários:
---Homologação Detran: 11/11.
+- Homologação Detran: 11/11.
 Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): aguardando aprovação das lojas.
 Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo)
 Mapa de lesões V4 - em desenvolvimento: 
---Homologação em 30/10.
+- Homologação em 30/10.
 Módulo CST (V4):
---Homologação Detran: 15/11.
---Estimativa Be Solution e viabilidade técnica: 23/10.</t>
-  </si>
-  <si>
-    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App nas lojas e cadastro de usuários</t>
+- Homologação Detran: 15/11;
+- Estimativa Be Solution e viabilidade técnica: 23/10.</t>
+  </si>
+  <si>
+    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App nas lojas e cadastro de usuários.</t>
   </si>
   <si>
     <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço;
 Entrega V3.1: Correção de 10 itens prioritários:
---Homologação Detran: 11/11.
+- Homologação Detran: 11/11.
 Aprovação do APP pela lojas Android (Google Play) e iOS (App Store)
 Mapa de lesões V4 em desenvolvimento:
---Homologação: 30/10.
+- Homologação: 30/10.
 Módulo CST (V4):
---Homologação Detran: 15/11.
---Estimativa Be Solution e viabilidade técnica: 23/10.</t>
+- Homologação Detran: 15/11.
+- Estimativa Be Solution e viabilidade técnica: 23/10.</t>
   </si>
   <si>
     <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)</t>
@@ -989,13 +991,13 @@
 Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
   </si>
   <si>
-    <t>Etapa 3 - concluída em 07/08/2026
-Etapa 4 definida pela DFT</t>
+    <t>Etapa 3 - Concluída em 07/08/2026;
+Etapa 4 definida pela DFT.</t>
   </si>
   <si>
     <t xml:space="preserve">
-Etapa 4 -aprovação da presidência
-Etapa 4 - início - requisitos
+Etapa 4 -aprovação da presidência;
+Etapa 4 - início - requisitos.
 </t>
   </si>
   <si>
@@ -1346,7 +1348,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1432,6 +1434,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1739,7 +1744,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
@@ -1922,7 +1927,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="229.5">
+    <row r="4" spans="1:24" ht="217.5">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1953,12 +1958,12 @@
       <c r="J4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="9">
-        <v>75</v>
+      <c r="K4" s="30">
+        <v>0.75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.93619631901840494</v>
+        <v>0.93987730061349695</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -2033,7 +2038,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="275.25">
+    <row r="6" spans="1:24" ht="246.6">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
@@ -2057,16 +2062,16 @@
         <v>59</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="7">
-        <v>15</v>
-      </c>
-      <c r="L6" s="7">
-        <v>36</v>
+        <v>61</v>
+      </c>
+      <c r="K6" s="28">
+        <v>0.15</v>
+      </c>
+      <c r="L6" s="28">
+        <v>0.36</v>
       </c>
       <c r="M6" s="8">
         <v>46210</v>
@@ -2081,36 +2086,36 @@
         <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="261" hidden="1">
       <c r="A7" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2139,25 +2144,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="409.5" hidden="1">
       <c r="A8" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2183,21 +2188,21 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A9" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
@@ -2227,48 +2232,48 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="121.5">
+    <row r="10" spans="1:24" ht="116.1">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="9">
-        <v>79</v>
-      </c>
-      <c r="L10" s="9">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="K10" s="30">
+        <v>0.79</v>
+      </c>
+      <c r="L10" s="30">
+        <v>1</v>
       </c>
       <c r="M10" s="10">
         <v>45407</v>
@@ -2281,37 +2286,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="29.1" hidden="1">
       <c r="A11" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2337,46 +2342,46 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="183">
+    <row r="12" spans="1:24" ht="174">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J12" s="14"/>
-      <c r="K12" s="7">
-        <v>53</v>
-      </c>
-      <c r="L12" s="9">
-        <v>100</v>
+      <c r="K12" s="28">
+        <v>0.53</v>
+      </c>
+      <c r="L12" s="30">
+        <v>1</v>
       </c>
       <c r="M12" s="8">
         <v>45659</v>
@@ -2389,34 +2394,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="409.5" hidden="1">
       <c r="A13" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2447,27 +2452,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="130.5" hidden="1">
       <c r="A14" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2493,18 +2498,18 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="130.5" hidden="1">
       <c r="A15" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
@@ -2535,22 +2540,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="152.25">
+    <row r="16" spans="1:24" ht="144.94999999999999">
       <c r="A16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2559,22 +2564,22 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="K16" s="7">
-        <v>70</v>
-      </c>
-      <c r="L16" s="7">
-        <v>82</v>
+        <v>133</v>
+      </c>
+      <c r="K16" s="28">
+        <v>0.7</v>
+      </c>
+      <c r="L16" s="28">
+        <v>0.82</v>
       </c>
       <c r="M16" s="8">
         <v>45938</v>
@@ -2589,37 +2594,37 @@
         <v>46300</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="45.75">
+    <row r="17" spans="1:24" ht="43.5">
       <c r="A17" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2628,16 +2633,16 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="K17" s="7">
-        <v>90</v>
+        <v>144</v>
+      </c>
+      <c r="K17" s="28">
+        <v>0.9</v>
       </c>
       <c r="L17" s="28">
         <v>0.9</v>
@@ -2655,34 +2660,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" hidden="1">
       <c r="A18" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2711,25 +2716,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A19" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2755,21 +2760,21 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="87" hidden="1">
       <c r="A20" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
@@ -2799,25 +2804,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="101.45" hidden="1">
       <c r="A21" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2843,27 +2848,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="180">
+    <row r="22" spans="1:24" ht="174">
       <c r="A22" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2872,19 +2877,19 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K22" s="28">
         <v>0.93</v>
       </c>
-      <c r="L22" s="7">
-        <v>100</v>
+      <c r="L22" s="28">
+        <v>1</v>
       </c>
       <c r="M22" s="8">
         <v>45988</v>
@@ -2899,58 +2904,58 @@
         <v>46315</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="275.25">
       <c r="A23" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="K23" s="7">
-        <v>50</v>
-      </c>
-      <c r="L23" s="7">
-        <v>100</v>
+        <v>183</v>
+      </c>
+      <c r="K23" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="28">
+        <v>1</v>
       </c>
       <c r="M23" s="8">
         <v>46111</v>
@@ -2963,41 +2968,41 @@
         <v>46318</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A24" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3023,21 +3028,21 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="57.95" hidden="1">
       <c r="A25" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
@@ -3067,22 +3072,22 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="229.5">
+    <row r="26" spans="1:24" ht="203.1">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>58</v>
@@ -3091,22 +3096,22 @@
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="K26" s="7">
-        <v>99</v>
-      </c>
-      <c r="L26" s="7">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="K26" s="28">
+        <v>0.99</v>
+      </c>
+      <c r="L26" s="28">
+        <v>1</v>
       </c>
       <c r="M26" s="8">
         <v>46042</v>
@@ -3121,62 +3126,62 @@
         <v>46317</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R26" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="152.25">
+    <row r="27" spans="1:24" ht="144.94999999999999">
       <c r="A27" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K27" s="9">
-        <v>92</v>
-      </c>
-      <c r="L27" s="9">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="K27" s="30">
+        <v>0.92</v>
+      </c>
+      <c r="L27" s="30">
+        <v>1</v>
       </c>
       <c r="M27" s="10">
         <v>45511</v>
@@ -3191,35 +3196,35 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="87" hidden="1">
       <c r="A28" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
@@ -3249,25 +3254,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="101.45" hidden="1">
       <c r="A29" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3293,25 +3298,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="57.95" hidden="1">
       <c r="A30" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3337,25 +3342,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="57.95" hidden="1">
       <c r="A31" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3381,25 +3386,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="87" hidden="1">
       <c r="A32" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3425,25 +3430,25 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" hidden="1">
       <c r="A33" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3469,10 +3474,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3569,12 +3574,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30">
+    <row r="1" spans="1:7" ht="29.1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3582,50 +3587,50 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30">
+    <row r="2" spans="1:7" ht="29.1">
       <c r="A2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45">
+    <row r="3" spans="1:7" ht="43.5">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3634,55 +3639,55 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45">
+    <row r="4" spans="1:7" ht="29.1">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3698,7 +3703,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3713,26 +3718,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3973,16 +3958,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akihiro.hayashi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C87F15E-5C04-4FC5-9F25-D0D3404F2D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438812A1-E9E3-4985-8C03-CA23865BCF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="281">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -196,7 +196,7 @@
 Live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
-    <t>19/20/2026 a 23/10/2026</t>
+    <t>26/10/2026 a 29/10/2026</t>
   </si>
   <si>
     <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
@@ -443,13 +443,11 @@
 Até o momento não temos resposta da PRF sobre a licitação.</t>
   </si>
   <si>
+    <t>19/20/2026 a 23/10/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nenhuma realização relevante registrada no período.
 </t>
-  </si>
-  <si>
-    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
-Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
-Não houve resposta da PRF até o momento.</t>
   </si>
   <si>
     <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação.
@@ -497,7 +495,7 @@
     <t>HABILITA-SP</t>
   </si>
   <si>
-    <t>Portaria DETRAN-SP nº 49, de 22 de janeiro de 2025</t>
+    <t>Portaria DETRAN-SP nº 49, de 22 de Janeiro de 2025</t>
   </si>
   <si>
     <t>Priscilla Elias e Silva</t>
@@ -548,18 +546,6 @@
   </si>
   <si>
     <t>HEIMDALL</t>
-  </si>
-  <si>
-    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
-O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
-Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
-O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransomware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
-Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
-O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
-O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
-O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
   </si>
   <si>
     <t>Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
@@ -599,9 +585,6 @@
     <t>INFOSIGA</t>
   </si>
   <si>
-    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamentodos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
-  </si>
-  <si>
     <t>Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
 Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
 Ser a plataforma de integração, informação e cooperação para o trânsito</t>
@@ -620,21 +603,16 @@
 Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
   </si>
   <si>
-    <t>Transformação Visual do Portal de Serviços DETRAN-SP -28/09/20026.</t>
-  </si>
-  <si>
-    <t>Implantação Catálogo de Proteção de Dados - 05/10/2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Catálogo de Auditoria Forense Digital - 04/11/2026;
-Catálogo de Segurança da Informação - 10/11/2026;
-Catálogo de Gestão e Monitoramento - 03/12/2026;
-Catálogo de Monitoramento de Incidentes - 09/12/2026.
-</t>
+    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
   </si>
   <si>
     <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
+  </si>
+  <si>
+    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
   </si>
   <si>
     <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
@@ -731,9 +709,6 @@
     <t>DCA</t>
   </si>
   <si>
-    <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
-  </si>
-  <si>
     <t>Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
 Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas 
 Otimizar a experiência e a satisfação do usuário com o atendimento
@@ -771,12 +746,6 @@
     <t>Criação de um framework para estruturar a gestão e governança normativa do Estado de São Paulo, por meio de uma curadoria automatizada e centralizada, com o objetivo de realizar o gerenciamento do arcabouço legislativo do Estado, abrangendo o ciclo de vida da norma, no tempo e no espaço e garantindo a fidelidade dos dados ao longo do tempo.</t>
   </si>
   <si>
-    <t>Simplificar a gestão regulatória e indizir avanços nas normas de trânsito
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
-Ser a plataforma de integração, informação e cooperação para o trânsito</t>
-  </si>
-  <si>
     <t>PRJ007</t>
   </si>
   <si>
@@ -792,13 +761,7 @@
     <t>Implantar-Laudos de Vistoria de Identificação Veicular-MVP2 (19/10/26)</t>
   </si>
   <si>
-    <t>Monitoramento do MVP-1 extendida até 30/10/26, sem impacto no prazo final.</t>
-  </si>
-  <si>
     <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronogama. </t>
   </si>
   <si>
     <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
@@ -855,7 +818,7 @@
     <t>O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e dar continuidade ao cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
   </si>
   <si>
-    <t>OCR e Azure: tem bloqueio de configurações e migração para produção -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção. Esta aprovação foi realizada em 23/10.</t>
+    <t>OCR e Azure: tinha bloqueio de configurações e migração para produção até 23/10 -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção. Esta aprovação foi realizada em 23/10.</t>
   </si>
   <si>
     <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
@@ -893,9 +856,6 @@
     <t>DCI</t>
   </si>
   <si>
-    <t>Implementar o Programa de Integridade, que consiste em um conjunto estuturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
-  </si>
-  <si>
     <t>Otimizar a experiência e a satisfação do usuário com o atendimento
 Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
 Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
@@ -987,10 +947,6 @@
     <t>Cyntia Tiemi Nihy</t>
   </si>
   <si>
-    <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
-Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
-  </si>
-  <si>
     <t>Etapa 3 - Concluída em 07/08/2026;
 Etapa 4 definida pela DFT.</t>
   </si>
@@ -1213,12 +1169,60 @@
   <si>
     <t>Cancelado</t>
   </si>
+  <si>
+    <t>Projeto paralisado aguardando aprovação da etapa 4 pela Presidência
+Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
+  </si>
+  <si>
+    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
+Foi solicitado formalmente à PRF a inclusão das câmeras para o DETRAN-SP na licitação.
+Não houve resposta da PRF até o momento.</t>
+  </si>
+  <si>
+    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
+O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
+Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
+O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransonware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
+Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
+O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
+O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
+O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
+  </si>
+  <si>
+    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamento dos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
+  </si>
+  <si>
+    <t>Entrega dos Catálogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026.</t>
+  </si>
+  <si>
+    <t>Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentes técnicos 3, adicionar função para criação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar aplicativo parta a liberação imediata de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
+  </si>
+  <si>
+    <t>Simplificar a gestão regulatória e induzir avanços nas normas de trânsito
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
+Ser a plataforma de integração, informação e cooperação para o trânsito</t>
+  </si>
+  <si>
+    <t>Monitoramento do MVP-1 estendida até 30/10/26, sem impacto no prazo final.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronograma. </t>
+  </si>
+  <si>
+    <t>Implementar o Programa de Integridade, que consiste em um conjunto estruturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1744,7 +1748,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
@@ -1765,7 +1769,7 @@
     <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.95" customHeight="1">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1839,7 +1843,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1">
+    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1883,7 +1887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.6" hidden="1">
+    <row r="3" spans="1:24" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1927,7 +1931,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="217.5">
+    <row r="4" spans="1:24" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1994,7 +1998,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1">
+    <row r="5" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>50</v>
       </c>
@@ -2038,7 +2042,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="246.6">
+    <row r="6" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
@@ -2104,7 +2108,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" hidden="1">
+    <row r="7" spans="1:24" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>67</v>
       </c>
@@ -2150,7 +2154,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1">
+    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>73</v>
       </c>
@@ -2194,7 +2198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="9" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>78</v>
       </c>
@@ -2238,7 +2242,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="116.1">
+    <row r="10" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>83</v>
       </c>
@@ -2264,10 +2268,10 @@
         <v>89</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" s="30">
         <v>0.79</v>
@@ -2286,7 +2290,7 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
@@ -2304,7 +2308,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29.1" hidden="1">
+    <row r="11" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>96</v>
       </c>
@@ -2348,7 +2352,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="174">
+    <row r="12" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>102</v>
       </c>
@@ -2374,7 +2378,7 @@
         <v>107</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="28">
@@ -2416,7 +2420,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1">
+    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>115</v>
       </c>
@@ -2452,24 +2456,24 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="X13" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="X13" s="23" t="s">
+    </row>
+    <row r="14" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1">
-      <c r="A14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>121</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>122</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>106</v>
@@ -2498,18 +2502,18 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="X14" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="X14" s="23" t="s">
+    </row>
+    <row r="15" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1">
-      <c r="A15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>125</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>126</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
@@ -2540,22 +2544,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="X15" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="X15" s="23" t="s">
+      <c r="B16" s="2" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="144.94999999999999">
-      <c r="A16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2567,16 +2571,16 @@
         <v>88</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="K16" s="28">
-        <v>0.7</v>
+        <v>0.81</v>
       </c>
       <c r="L16" s="28">
         <v>0.82</v>
@@ -2591,40 +2595,44 @@
         <v>46365</v>
       </c>
       <c r="P16" s="8">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="Q16" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="V16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="W16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="X16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="T16" s="6"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="X16" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="43.5">
-      <c r="A17" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2633,13 +2641,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K17" s="28">
         <v>0.9</v>
@@ -2660,34 +2668,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="X17" s="3" t="s">
+      <c r="B18" s="17" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1">
-      <c r="A18" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>151</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2716,25 +2724,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="X18" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="X18" s="23" t="s">
+      <c r="B19" s="17" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
-      <c r="A19" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>156</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2760,21 +2768,21 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="X19" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="X19" s="23" t="s">
+      <c r="C20" s="18" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="87" hidden="1">
-      <c r="A20" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>162</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
@@ -2804,18 +2812,18 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="X20" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>163</v>
-      </c>
-      <c r="X20" s="23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="101.45" hidden="1">
-      <c r="A21" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>166</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
@@ -2848,27 +2856,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>168</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174">
+    <row r="22" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2877,13 +2885,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K22" s="28">
         <v>0.93</v>
@@ -2904,34 +2912,34 @@
         <v>46315</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="275.25">
+    <row r="23" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>99</v>
@@ -2943,13 +2951,13 @@
         <v>88</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="K23" s="28">
         <v>0.5</v>
@@ -2968,41 +2976,41 @@
         <v>46318</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="24" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3028,21 +3036,21 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>195</v>
+        <v>280</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="57.95" hidden="1">
+    <row r="25" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
@@ -3072,22 +3080,22 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="203.1">
+    <row r="26" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>58</v>
@@ -3099,13 +3107,13 @@
         <v>88</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="K26" s="28">
         <v>0.99</v>
@@ -3126,38 +3134,38 @@
         <v>46317</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="R26" s="14" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="144.94999999999999">
+    <row r="27" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>87</v>
@@ -3169,13 +3177,13 @@
         <v>88</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" s="30">
         <v>0.92</v>
@@ -3196,35 +3204,35 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1">
+    <row r="28" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
@@ -3254,25 +3262,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.45" hidden="1">
+    <row r="29" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3298,25 +3306,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="57.95" hidden="1">
+    <row r="30" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3342,25 +3350,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="57.95" hidden="1">
+    <row r="31" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3386,25 +3394,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1">
+    <row r="32" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3430,22 +3438,22 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1">
+    <row r="33" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>87</v>
@@ -3474,10 +3482,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3574,12 +3582,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29.1">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3587,47 +3595,47 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29.1">
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>88</v>
@@ -3639,58 +3647,58 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29.1">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3701,9 +3709,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3718,6 +3726,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3958,36 +3986,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akihiro.hayashi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438812A1-E9E3-4985-8C03-CA23865BCF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4D2808-A13E-4B24-81AE-59B6DE91114A}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="280">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -196,24 +196,7 @@
 Live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
-    <t>26/10/2026 a 29/10/2026</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Desenvolvido história de usuário.
-Novo app: Realizado o Provisionamento do ambiente de produção para o app.
-Live 2.0: Desenvolvido SISPL sem socket; Executado os testes de QA - Portal.</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário
-Novo app: Realizar correções do lote 1 dos serviços csm
-Autorização de Transporte Escolar: Iniciar desenvolvimento.
-Live 2.0: Homologar o desenvolvimento do portal; Abrir GMUD do Socket-SISPL, Executar QA-SISPL Sem socket.</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Emplacar Veículo 0Km e Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
+    <t>19/20/2026 a 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -443,11 +426,13 @@
 Até o momento não temos resposta da PRF sobre a licitação.</t>
   </si>
   <si>
-    <t>19/20/2026 a 23/10/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nenhuma realização relevante registrada no período.
 </t>
+  </si>
+  <si>
+    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
+Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
+Não houve resposta da PRF até o momento.</t>
   </si>
   <si>
     <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação.
@@ -495,9 +480,6 @@
     <t>HABILITA-SP</t>
   </si>
   <si>
-    <t>Portaria DETRAN-SP nº 49, de 22 de Janeiro de 2025</t>
-  </si>
-  <si>
     <t>Priscilla Elias e Silva</t>
   </si>
   <si>
@@ -546,6 +528,18 @@
   </si>
   <si>
     <t>HEIMDALL</t>
+  </si>
+  <si>
+    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
+O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
+Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
+O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransomware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
+Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
+O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
+Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
+O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
+O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
   </si>
   <si>
     <t>Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
@@ -585,6 +579,9 @@
     <t>INFOSIGA</t>
   </si>
   <si>
+    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamentodos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
+  </si>
+  <si>
     <t>Promover a segurança no trânsito e reduzir os indicadores de óbitos e feridos em sinistros
 Subsidiar políticas públicas com foco em resultados concretos e mensuráveis
 Ser a plataforma de integração, informação e cooperação para o trânsito</t>
@@ -603,16 +600,16 @@
 Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
   </si>
   <si>
-    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
+    <t>26/10/2026 a 29/10/2026</t>
+  </si>
+  <si>
+    <t>Entrega dos Catalogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026.</t>
+  </si>
+  <si>
+    <t>Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentens técnicos 3, adicionar função para ciação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB;</t>
   </si>
   <si>
     <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
-  </si>
-  <si>
-    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
   </si>
   <si>
     <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
@@ -709,6 +706,9 @@
     <t>DCA</t>
   </si>
   <si>
+    <t xml:space="preserve">Criar aplicativo parta a liberação imediada de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
+  </si>
+  <si>
     <t>Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
 Ampliar a disponibilidade, a eficiência e a acessibilidade de todos os serviços a todas as pessoas 
 Otimizar a experiência e a satisfação do usuário com o atendimento
@@ -746,6 +746,12 @@
     <t>Criação de um framework para estruturar a gestão e governança normativa do Estado de São Paulo, por meio de uma curadoria automatizada e centralizada, com o objetivo de realizar o gerenciamento do arcabouço legislativo do Estado, abrangendo o ciclo de vida da norma, no tempo e no espaço e garantindo a fidelidade dos dados ao longo do tempo.</t>
   </si>
   <si>
+    <t>Simplificar a gestão regulatória e indizir avanços nas normas de trânsito
+Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
+Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
+Ser a plataforma de integração, informação e cooperação para o trânsito</t>
+  </si>
+  <si>
     <t>PRJ007</t>
   </si>
   <si>
@@ -756,12 +762,6 @@
   </si>
   <si>
     <t>Em andamento sem impeditivo.</t>
-  </si>
-  <si>
-    <t>Implantar-Laudos de Vistoria de Identificação Veicular-MVP2 (19/10/26)</t>
-  </si>
-  <si>
-    <t>Acompanhar a implantação laudos de Vistoria de Identificação Veicular (MVP-2) - 19/10/2026.</t>
   </si>
   <si>
     <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
@@ -856,6 +856,9 @@
     <t>DCI</t>
   </si>
   <si>
+    <t>Implementar o Programa de Integridade, que consiste em um conjunto estuturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
+  </si>
+  <si>
     <t>Otimizar a experiência e a satisfação do usuário com o atendimento
 Estruturar o controle interno e a gestão de riscos com as melhores práticas de compliance
 Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
@@ -947,6 +950,10 @@
     <t>Cyntia Tiemi Nihy</t>
   </si>
   <si>
+    <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
+Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
+  </si>
+  <si>
     <t>Etapa 3 - Concluída em 07/08/2026;
 Etapa 4 definida pela DFT.</t>
   </si>
@@ -1170,52 +1177,45 @@
     <t>Cancelado</t>
   </si>
   <si>
-    <t>Projeto paralisado aguardando aprovação da etapa 4 pela Presidência
-Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
-  </si>
-  <si>
-    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
-Foi solicitado formalmente à PRF a inclusão das câmeras para o DETRAN-SP na licitação.
-Não houve resposta da PRF até o momento.</t>
-  </si>
-  <si>
-    <t>Contratação direta da Companhia de Processamento de Dados do Estado de São Paulo – PRODESP para prestação de Serviços de Segurança de Identidade em TI (Tecnologia da Informação) composto de:
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas (Privilegie Access Management - PAM);
-O serviço de proteção e gerenciamento de identidades privilegiadas tem como objetivo proteger as contas privilegiadas através da descoberta e troca periódica de senhas/contas.
-Serviço de Proteção e Gerenciamento de Privilégios de Estações de Trabalho (Enterprise Performance Management - EPM);
-O serviço de proteção e gerenciamento de privilégios de estações de trabalho tem como objetivo proteger endpoints contra-ataques, reduzindo o risco de informações serem roubadas ou criptografadas, como um ataque ransonware, além da prevenção de roubo de credenciais, realizar o bloqueio de instalações de aplicações não autorizadas e elevação de privilégios.
-Serviço de Proteção e Gerenciamento de Usuários de Negócio (Identity and Access Management - IAM) e;
-O serviço de Gerenciamento de Usuários de Negócio fornece uma plataforma unificada para a centralização dos logins dos usuários, bem como Múltiplos Fatores de Autenticação para proteger os acessos às aplicações de negócio.
-Serviço de Proteção e Gerenciamento de Identidades Privilegiadas não Humanas.
-O serviço de proteção de identidades de aplicações modernas é capaz de gerenciar e rotacionar credenciais de aplicações em contêineres, entregando as credenciais para suas aplicações diretamente na esteira de desenvolvimento.
-O serviço se adequa a disciplina de proteção e gerenciamento de identidades privilegiadas, capaz de remover credenciais embutidas em código e garantir o conceito de menor privilégio.</t>
-  </si>
-  <si>
-    <t>Melhorar a qualidade dos dados por meio da aplicação de inteligência artificial, ampliar a capacidade de georreferenciamento dos sinistros, com uso de metodologias baseadas em CadLoge APIs, integrar dados externos estratégicos, implementar alertas gerenciais e enriquecimento de painéis com indicadores críticos, favorecendo a tomada de decisão e o monitoramento contínuo dos dados e aprimoramento da interface como usuário por meio de alterações no front-end.</t>
-  </si>
-  <si>
-    <t>Entrega dos Catálogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026.</t>
-  </si>
-  <si>
-    <t>Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentes técnicos 3, adicionar função para criação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar aplicativo parta a liberação imediata de veículo recolhido, mediante o pagamento de todas as taxas recolhido </t>
-  </si>
-  <si>
-    <t>Simplificar a gestão regulatória e induzir avanços nas normas de trânsito
-Automatizar os processos com emprego de inteligência artificial e aprendizagem de máquinas
-Reduzir o custo dos serviços e contribuir para a competitividade e a prosperidade do Estado de São Paulo
-Ser a plataforma de integração, informação e cooperação para o trânsito</t>
-  </si>
-  <si>
-    <t>Monitoramento do MVP-1 estendida até 30/10/26, sem impacto no prazo final.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregas da Chaintec estão necessitando de muito retrabalho, podendo afetar cronograma. </t>
-  </si>
-  <si>
-    <t>Implementar o Programa de Integridade, que consiste em um conjunto estruturado de ações e medidas institucionais para prevenção, detecção e punição de práticas de corrupção, de fraude, de desvios éticos e de outros ilícitos.</t>
+    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
+  </si>
+  <si>
+    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 49, de 22 de Janeiro de 2025</t>
+  </si>
+  <si>
+    <t>Acompanhamento da implantação do MVP2, com avanço de 50% com previsão de término para 03/11/2026.</t>
+  </si>
+  <si>
+    <t>Monitoramento da implantação MVP-1 extendida até 30/10/26, sem impacto no prazo final, com 90% de andamento.
+Monitoramento da implantação MVP-2, com 50% de andamento e término em 03/11/2026.</t>
+  </si>
+  <si>
+    <t>Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3).</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Ajustando história de usuário.
+Novo app: Área realizaou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
+Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
+Emplacar veículo 0Km: Detalhado cronograma de execução</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
+Novo app: Realizar ajustes no app, até 29/10/26.
+Autorização de Transporte Escolar:Detalhar cronograma de desenvolvimento.
+Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
+Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
+  </si>
+  <si>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
   </si>
 </sst>
 </file>
@@ -1459,6 +1459,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1748,28 +1752,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.5703125" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" customWidth="1"/>
+    <col min="8" max="8" width="40.54296875" customWidth="1"/>
+    <col min="9" max="9" width="25.54296875" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.5703125" customWidth="1"/>
-    <col min="23" max="23" width="50.5703125" customWidth="1"/>
-    <col min="24" max="24" width="120.5703125" customWidth="1"/>
+    <col min="17" max="22" width="40.54296875" customWidth="1"/>
+    <col min="23" max="23" width="50.54296875" customWidth="1"/>
+    <col min="24" max="24" width="120.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1843,7 +1847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1887,7 +1891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="246.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1931,7 +1935,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="240" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1957,10 +1961,10 @@
         <v>43</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>277</v>
       </c>
       <c r="K4" s="30">
         <v>0.75</v>
@@ -1976,41 +1980,41 @@
         <v>46370</v>
       </c>
       <c r="O4" s="10">
-        <v>46377</v>
+        <v>46475</v>
       </c>
       <c r="P4" s="10">
-        <v>46315</v>
+        <v>46321</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>46</v>
+        <v>278</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>47</v>
+        <v>279</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="C5" s="18" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>28</v>
@@ -2036,25 +2040,25 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="X5" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="X5" s="23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="285" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -2063,13 +2067,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K6" s="28">
         <v>0.15</v>
@@ -2090,36 +2094,36 @@
         <v>45946</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="B7" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="C7" s="18" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" ht="300" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="D7" s="19" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>70</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2148,25 +2152,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="X7" s="23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2192,25 +2196,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="X8" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="X8" s="23" t="s">
+      <c r="C9" s="18" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>80</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>28</v>
@@ -2236,42 +2240,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="X9" s="23" t="s">
+      <c r="C10" s="15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="D10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K10" s="30">
         <v>0.79</v>
@@ -2290,37 +2294,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>271</v>
+        <v>88</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="B11" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="C11" s="18" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>98</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2346,39 +2350,39 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="X11" s="23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X11" s="23" t="s">
+      <c r="C12" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" ht="180" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="E12" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="28">
@@ -2398,34 +2402,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="V12" s="3" t="s">
+      <c r="B13" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>116</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2456,27 +2460,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="X13" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="D14" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="E14" s="19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2502,23 +2506,23 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="X14" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>122</v>
-      </c>
-      <c r="X14" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>28</v>
@@ -2544,22 +2548,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>273</v>
+        <v>123</v>
       </c>
       <c r="X15" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="135" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2568,16 +2572,16 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H16" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>274</v>
       </c>
       <c r="K16" s="28">
         <v>0.81</v>
@@ -2598,41 +2602,41 @@
         <v>46321</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>275</v>
+        <v>131</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>131</v>
+        <v>270</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="W16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="V16" s="3" t="s">
+      <c r="X16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="W16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="X16" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2641,13 +2645,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K17" s="28">
         <v>0.9</v>
@@ -2668,34 +2672,34 @@
         <v>46310</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="X17" s="3" t="s">
+      <c r="B18" s="17" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>149</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2724,25 +2728,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="X18" s="23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="X18" s="23" t="s">
+      <c r="B19" s="17" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>154</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2768,25 +2772,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>276</v>
+        <v>154</v>
       </c>
       <c r="X19" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>158</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>159</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>28</v>
@@ -2812,25 +2816,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="X20" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="X20" s="23" t="s">
+    </row>
+    <row r="21" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>162</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>163</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2856,13 +2860,13 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="X21" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="X21" s="23" t="s">
-        <v>277</v>
-      </c>
     </row>
-    <row r="22" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>165</v>
       </c>
@@ -2873,7 +2877,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>167</v>
@@ -2888,13 +2892,13 @@
         <v>168</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>169</v>
+        <v>274</v>
       </c>
       <c r="K22" s="28">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="L22" s="28">
         <v>1</v>
@@ -2909,55 +2913,53 @@
         <v>46379</v>
       </c>
       <c r="P22" s="8">
-        <v>46315</v>
+        <v>46321</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>279</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="285" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K23" s="28">
         <v>0.5</v>
@@ -2976,41 +2978,41 @@
         <v>46318</v>
       </c>
       <c r="Q23" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="X23" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="W23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="X23" s="3" t="s">
+      <c r="B24" s="17" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="C24" s="18" t="s">
         <v>185</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>187</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3036,25 +3038,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>280</v>
+        <v>187</v>
       </c>
       <c r="X24" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="B25" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>191</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>192</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>28</v>
@@ -3080,40 +3082,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="X25" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="X25" s="23" t="s">
+    </row>
+    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" ht="225" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H26" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>199</v>
       </c>
       <c r="K26" s="28">
         <v>0.99</v>
@@ -3134,56 +3136,56 @@
         <v>46317</v>
       </c>
       <c r="Q26" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="R26" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="R26" s="14" t="s">
+      <c r="S26" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="W26" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="W26" s="3" t="s">
+      <c r="X26" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="X26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" ht="150" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>208</v>
-      </c>
       <c r="E27" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K27" s="30">
         <v>0.92</v>
@@ -3224,7 +3226,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
         <v>215</v>
       </c>
@@ -3236,7 +3238,7 @@
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F28" s="19" t="s">
         <v>28</v>
@@ -3268,7 +3270,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
         <v>220</v>
       </c>
@@ -3312,7 +3314,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
         <v>226</v>
       </c>
@@ -3356,7 +3358,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
         <v>230</v>
       </c>
@@ -3368,7 +3370,7 @@
         <v>232</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3400,7 +3402,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
         <v>235</v>
       </c>
@@ -3444,7 +3446,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
         <v>240</v>
       </c>
@@ -3456,7 +3458,7 @@
         <v>242</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3582,12 +3584,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="10.5703125" customWidth="1"/>
+    <col min="1" max="7" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3610,7 +3612,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>250</v>
       </c>
@@ -3633,12 +3635,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3656,7 +3658,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -3679,7 +3681,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>265</v>
       </c>
@@ -3698,7 +3700,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3709,7 +3711,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>269</v>
       </c>
@@ -3726,26 +3728,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3986,26 +3968,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4024,6 +4007,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4D2808-A13E-4B24-81AE-59B6DE91114A}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7714442D-3E09-4920-AF54-3EDBC52590BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,14 +642,7 @@
     <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be.</t>
   </si>
   <si>
-    <t>Todas jornadas finalizadas
-Todas as jornadas revisadas</t>
-  </si>
-  <si>
     <t>Realinhar formato de indicadores de cada melhoria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validação das jornadas. </t>
   </si>
   <si>
     <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
@@ -1199,23 +1192,29 @@
     <t>Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3).</t>
   </si>
   <si>
-    <t>Gestão de procuração 2.0: Ajustando história de usuário.
-Novo app: Área realizaou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
-Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
-Emplacar veículo 0Km: Detalhado cronograma de execução</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
-Novo app: Realizar ajustes no app, até 29/10/26.
-Autorização de Transporte Escolar:Detalhar cronograma de desenvolvimento.
-Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
-Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
-  </si>
-  <si>
     <t>Não houve report pelo GP do projeto:
 Primeira Habilitação;
 Renovação da CNH.
 Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Ajustando história de usuário.
+Novo app: Área realizou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
+Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
+Emplacar veículo 0Km: Detalhado cronograma de execução</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
+Novo app: Realizar ajustes no app, até 29/10/26.
+Autorização de Transporte Escolar: Detalhar cronograma de desenvolvimento.
+Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
+Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
+  </si>
+  <si>
+    <t>Analistas estudando a teoria de Indicadores para aplicarem no projeto, conforme orientação AME e APC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validação e feedback das jornadas to-be feitas. </t>
   </si>
 </sst>
 </file>
@@ -1459,10 +1458,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1964,14 +1959,14 @@
         <v>129</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K4" s="30">
         <v>0.75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.93987730061349695</v>
+        <v>0.94233128834355828</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -1987,12 +1982,12 @@
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
@@ -2364,7 +2359,7 @@
         <v>100</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>101</v>
@@ -2605,17 +2600,17 @@
         <v>131</v>
       </c>
       <c r="R16" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3" t="s">
         <v>132</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>133</v>
@@ -2669,37 +2664,37 @@
         <v>46373</v>
       </c>
       <c r="P17" s="8">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="Q17" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>143</v>
+        <v>279</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2728,25 +2723,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2772,21 +2767,21 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>156</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>158</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
@@ -2816,18 +2811,18 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
@@ -2860,18 +2855,18 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
@@ -2880,7 +2875,7 @@
         <v>127</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2889,13 +2884,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>129</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K22" s="28">
         <v>0.95</v>
@@ -2916,32 +2911,32 @@
         <v>46321</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>96</v>
@@ -2953,13 +2948,13 @@
         <v>85</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K23" s="28">
         <v>0.5</v>
@@ -2978,41 +2973,41 @@
         <v>46318</v>
       </c>
       <c r="Q23" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="X23" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>183</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>185</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3038,21 +3033,21 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>191</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
@@ -3082,22 +3077,22 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>55</v>
@@ -3109,13 +3104,13 @@
         <v>85</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K26" s="28">
         <v>0.99</v>
@@ -3136,38 +3131,38 @@
         <v>46317</v>
       </c>
       <c r="Q26" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="X26" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="D27" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>84</v>
@@ -3179,7 +3174,7 @@
         <v>85</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>44</v>
@@ -3206,35 +3201,35 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="18" t="s">
         <v>215</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>217</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
@@ -3264,25 +3259,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>220</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>222</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3308,25 +3303,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3352,22 +3347,22 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>138</v>
@@ -3396,25 +3391,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3440,22 +3435,22 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>84</v>
@@ -3484,10 +3479,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3597,47 +3592,47 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>85</v>
@@ -3649,13 +3644,13 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3663,41 +3658,41 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3713,7 +3708,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3728,6 +3723,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3968,27 +3983,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4007,25 +4021,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" enabled="0" method="" siteId="{3a78b0cd-7c8e-4929-83d5-190a6cc01365}" removed="1"/>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{C022C224-A2A7-44D3-B1AB-68C62AAA0AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7714442D-3E09-4920-AF54-3EDBC52590BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6E36CCD-40C1-44B9-BCA9-46D8D52C8FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="280">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -196,7 +196,26 @@
 Live 2.0 em andamento sem impeditivos</t>
   </si>
   <si>
-    <t>19/20/2026 a 23/10/2026</t>
+    <t>26/10/2026 a 29/10/2026</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Ajustando história de usuário.
+Novo app: Área realizou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
+Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
+Emplacar veículo 0Km: Detalhado cronograma de execução</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
+Novo app: Realizar ajustes no app, até 29/10/26.
+Autorização de Transporte Escolar: Detalhar cronograma de desenvolvimento.
+Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
+Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
+  </si>
+  <si>
+    <t>Não houve report pelo GP do projeto:
+Primeira Habilitação;
+Renovação da CNH.
+Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -257,21 +276,24 @@
   <si>
     <t>Projeto segue dentro do prazo, conforme planejado
 Edital  publicado - provas 01/11/2026 (DAL)
-Material de treinamento em elaboração</t>
-  </si>
-  <si>
-    <t>19/10/2026 a 23/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo app
-</t>
-  </si>
-  <si>
-    <t>Publicação do Edital - Prova 01/11/2026;
-Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes.</t>
-  </si>
-  <si>
-    <t>Atualização do cronograma, alinhamento com PO e EPT.</t>
+Material de treinamento em elaboração
+Concurso Público ocorre no domingo (01/11) conforme planejado</t>
+  </si>
+  <si>
+    <t>Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar - pendente validação da grade de formação dos 60 dias.</t>
+  </si>
+  <si>
+    <t>Publicação do Edital - Prova 01/11/2026.
+Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes.
+Concurso Público ocorre no domingo (01/11) conforme planejado.
+Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar.</t>
+  </si>
+  <si>
+    <t>Atualização do cronograma.
+Novo alinhamento com Tati e EPT para concluir as definições/validação de grade dos 60 dias.
+Definição dos locais na SEDE para realização do curso EAD para os ingressantes com Norma - depende da estratégia a ser definida para a formação em 60 dias com EPT e Tati.
+DCI finalizar a pesquisa dos docentes da DHC.
+DAC abrir SEI direcionado a DCI para solicitar pesquisa de seus docentes.</t>
   </si>
   <si>
     <t>Atraso na revisão e validação do conteúdo da capacitação;
@@ -426,13 +448,14 @@
 Até o momento não temos resposta da PRF sobre a licitação.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nenhuma realização relevante registrada no período.
-</t>
+    <t>Nenhuma realização relevante registrada no período.
+Não houve necessidade de agenda do projeto</t>
   </si>
   <si>
     <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
 Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
-Não houve resposta da PRF até o momento.</t>
+Não houve resposta da PRF até o momento.
+Não houve necessidade de agenda do projeto</t>
   </si>
   <si>
     <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação.
@@ -480,6 +503,9 @@
     <t>HABILITA-SP</t>
   </si>
   <si>
+    <t>Portaria DETRAN-SP nº 49, de 22 de Janeiro de 2025</t>
+  </si>
+  <si>
     <t>Priscilla Elias e Silva</t>
   </si>
   <si>
@@ -491,9 +517,13 @@
 </t>
   </si>
   <si>
+    <t>Não houve necessidade de agenda do projeto</t>
+  </si>
+  <si>
     <t>Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP;
 Desenvolvimento das definições de layout, fluxos, materialidade e aplicabilidade do conceito;
-Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026; Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade</t>
+Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026; Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade.
+Não houve necessidade de agenda do projeto.</t>
   </si>
   <si>
     <t>Prosseguimento, pela área de Infraestrutura, dos procedimentos necessários para contratação e implantação da unidade, contemplando os projetos e serviços necessários à execução da obra.
@@ -600,16 +630,22 @@
 Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
   </si>
   <si>
-    <t>26/10/2026 a 29/10/2026</t>
-  </si>
-  <si>
     <t>Entrega dos Catalogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026.</t>
   </si>
   <si>
     <t>Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentens técnicos 3, adicionar função para ciação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB;</t>
   </si>
   <si>
+    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
+  </si>
+  <si>
     <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
+  </si>
+  <si>
+    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
   </si>
   <si>
     <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
@@ -642,7 +678,13 @@
     <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be.</t>
   </si>
   <si>
+    <t>Analistas estudando a teoria de Indicadores para aplicarem no projeto, conforme orientação AME e APC.</t>
+  </si>
+  <si>
     <t>Realinhar formato de indicadores de cada melhoria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validação e feedback das jornadas to-be feitas. </t>
   </si>
   <si>
     <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
@@ -757,6 +799,16 @@
     <t>Em andamento sem impeditivo.</t>
   </si>
   <si>
+    <t>Acompanhamento da implantação do MVP2, com avanço de 50% com previsão de término para 03/11/2026.</t>
+  </si>
+  <si>
+    <t>Monitoramento da implantação MVP-1 extendida até 30/10/26, sem impacto no prazo final, com 90% de andamento.
+Monitoramento da implantação MVP-2, com 50% de andamento e término em 03/11/2026.</t>
+  </si>
+  <si>
+    <t>Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3).</t>
+  </si>
+  <si>
     <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
 Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
 O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
@@ -779,7 +831,7 @@
   </si>
   <si>
     <t>Projeto apresenta significativo atraso e não há previsão para o término.
-Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure.
+Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure impactando cronograma.
 - Treinamento - TBD;
 - Homologação - TBD;
 - GMUD - TBD.
@@ -802,13 +854,13 @@
 --    Treinamento - TBD
 --    Homologação - TBD
 --    GMUD - TBD
---    Denilson/Gianini (GP Prodesp) acionará Ricardo Aragão (superintendente da BU) para destravar a migração de configuração OCR e Azure para Produção e seguir com cronograma de entrega.
+--    Aguardando a migração de configuração OCR e Azure para Produção e Best seguir com cronograma de entrega.
 Agente Q&amp;A da Wiki ("Isa") - wave 2 - Microsoft - 06/11/2026
 Agente Revisor de Conteúdo da wiki - wave 3:
 --    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
   </si>
   <si>
-    <t>O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e dar continuidade ao cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
+    <t>O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e Best seguir replanejar as atividades no cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
   </si>
   <si>
     <t>OCR e Azure: tinha bloqueio de configurações e migração para produção até 23/10 -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção. Esta aprovação foi realizada em 23/10.</t>
@@ -885,30 +937,31 @@
   <si>
     <t>Entrega V3.1: Correção de 10 itens prioritários:
 - Homologação Detran: 11/11.
-Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): aguardando aprovação das lojas.
-Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo)
+Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): Loja Android foi aprovado, pendente aprovação da loja da App Store.
+Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo) - 30/10
 Mapa de lesões V4 - em desenvolvimento: 
 - Homologação em 30/10.
 Módulo CST (V4):
-- Homologação Detran: 15/11;
-- Estimativa Be Solution e viabilidade técnica: 23/10.</t>
-  </si>
-  <si>
-    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App nas lojas e cadastro de usuários.</t>
+- Homologação Detran: TBD;
+- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
+  </si>
+  <si>
+    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App na loja Android e cadastro de usuários em andamento.</t>
   </si>
   <si>
     <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço;
 Entrega V3.1: Correção de 10 itens prioritários:
 - Homologação Detran: 11/11.
-Aprovação do APP pela lojas Android (Google Play) e iOS (App Store)
+Aprovação do APP pela loja iOS (App Store)
 Mapa de lesões V4 em desenvolvimento:
 - Homologação: 30/10.
 Módulo CST (V4):
-- Homologação Detran: 15/11.
-- Estimativa Be Solution e viabilidade técnica: 23/10.</t>
-  </si>
-  <si>
-    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)</t>
+- Homologação Detran: TBD;
+- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
+  </si>
+  <si>
+    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)
+Atraso no Módulo CST (V4) para estimativa Be Solution e viabilidade técnica devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
   </si>
   <si>
     <t>Possível revisão de escopo - impacto no cronograma</t>
@@ -947,6 +1000,10 @@
 Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
   </si>
   <si>
+    <t>Nenhuma realização relevante registrada no período.
+Não houve necessidade de agenda do projeto.</t>
+  </si>
+  <si>
     <t>Etapa 3 - Concluída em 07/08/2026;
 Etapa 4 definida pela DFT.</t>
   </si>
@@ -1169,59 +1226,12 @@
   <si>
     <t>Cancelado</t>
   </si>
-  <si>
-    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
-  </si>
-  <si>
-    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
-  </si>
-  <si>
-    <t>Portaria DETRAN-SP nº 49, de 22 de Janeiro de 2025</t>
-  </si>
-  <si>
-    <t>Acompanhamento da implantação do MVP2, com avanço de 50% com previsão de término para 03/11/2026.</t>
-  </si>
-  <si>
-    <t>Monitoramento da implantação MVP-1 extendida até 30/10/26, sem impacto no prazo final, com 90% de andamento.
-Monitoramento da implantação MVP-2, com 50% de andamento e término em 03/11/2026.</t>
-  </si>
-  <si>
-    <t>Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3).</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Ajustando história de usuário.
-Novo app: Área realizou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
-Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
-Emplacar veículo 0Km: Detalhado cronograma de execução</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
-Novo app: Realizar ajustes no app, até 29/10/26.
-Autorização de Transporte Escolar: Detalhar cronograma de desenvolvimento.
-Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
-Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
-  </si>
-  <si>
-    <t>Analistas estudando a teoria de Indicadores para aplicarem no projeto, conforme orientação AME e APC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validação e feedback das jornadas to-be feitas. </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1747,28 +1757,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
-    <col min="3" max="3" width="32.453125" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="40.54296875" customWidth="1"/>
-    <col min="9" max="9" width="25.54296875" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.54296875" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="16" width="17" customWidth="1"/>
-    <col min="17" max="22" width="40.54296875" customWidth="1"/>
-    <col min="23" max="23" width="50.54296875" customWidth="1"/>
-    <col min="24" max="24" width="120.54296875" customWidth="1"/>
+    <col min="17" max="22" width="40.5703125" customWidth="1"/>
+    <col min="23" max="23" width="50.5703125" customWidth="1"/>
+    <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1842,7 +1852,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="409.5" hidden="1">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1886,7 +1896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="246.6" hidden="1">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1930,7 +1940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="217.5">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1956,17 +1966,17 @@
         <v>43</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>276</v>
+        <v>45</v>
       </c>
       <c r="K4" s="30">
         <v>0.75</v>
       </c>
       <c r="L4" s="27">
         <f ca="1">(TODAY()-M4)/(N4-M4)</f>
-        <v>0.94233128834355828</v>
+        <v>0.94355828220858895</v>
       </c>
       <c r="M4" s="10">
         <v>45555</v>
@@ -1982,34 +1992,34 @@
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>277</v>
+        <v>46</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>275</v>
+        <v>47</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="130.5" hidden="1">
       <c r="A5" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>28</v>
@@ -2035,25 +2045,25 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="275.25">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -2062,13 +2072,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K6" s="28">
         <v>0.15</v>
@@ -2086,39 +2096,39 @@
         <v>46461</v>
       </c>
       <c r="P6" s="8">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="261" hidden="1">
       <c r="A7" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2147,25 +2157,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="409.5" hidden="1">
       <c r="A8" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2191,25 +2201,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A9" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>28</v>
@@ -2235,42 +2245,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="121.5">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K10" s="30">
         <v>0.79</v>
@@ -2289,37 +2299,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="29.1" hidden="1">
       <c r="A11" s="16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2345,41 +2355,43 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="183">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>271</v>
+        <v>103</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="J12" s="14"/>
+      <c r="J12" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="K12" s="28">
         <v>0.53</v>
       </c>
@@ -2397,34 +2409,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="409.5" hidden="1">
       <c r="A13" s="16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2455,27 +2467,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="130.5" hidden="1">
       <c r="A14" s="16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2501,23 +2513,23 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="130.5" hidden="1">
       <c r="A15" s="16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>28</v>
@@ -2543,22 +2555,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="137.25">
       <c r="A16" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2567,16 +2579,16 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K16" s="28">
         <v>0.81</v>
@@ -2597,41 +2609,41 @@
         <v>46321</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>269</v>
+        <v>138</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" ht="45.75">
       <c r="A17" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2640,13 +2652,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K17" s="28">
         <v>0.9</v>
@@ -2667,34 +2679,34 @@
         <v>46317</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>278</v>
+        <v>147</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>279</v>
+        <v>149</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" ht="409.5" hidden="1">
       <c r="A18" s="16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2723,25 +2735,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A19" s="16" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2767,25 +2779,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" ht="87" hidden="1">
       <c r="A20" s="16" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>28</v>
@@ -2811,25 +2823,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" ht="101.45" hidden="1">
       <c r="A21" s="16" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2855,27 +2867,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="174" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" ht="183">
       <c r="A22" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2884,13 +2896,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>272</v>
+        <v>175</v>
       </c>
       <c r="K22" s="28">
         <v>0.95</v>
@@ -2911,50 +2923,50 @@
         <v>46321</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" ht="275.25">
       <c r="A23" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="K23" s="28">
         <v>0.5</v>
@@ -2970,44 +2982,44 @@
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="8">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
       <c r="A24" s="16" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3033,25 +3045,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" ht="57.95" hidden="1">
       <c r="A25" s="16" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>28</v>
@@ -3077,40 +3089,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" ht="275.25">
       <c r="A26" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="K26" s="28">
         <v>0.99</v>
@@ -3128,59 +3140,59 @@
         <v>46356</v>
       </c>
       <c r="P26" s="8">
-        <v>46317</v>
+        <v>46323</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="R26" s="14" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="145" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" ht="152.25">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="K27" s="30">
         <v>0.92</v>
@@ -3201,39 +3213,39 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" ht="87" hidden="1">
       <c r="A28" s="16" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F28" s="19" t="s">
         <v>28</v>
@@ -3259,25 +3271,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" ht="101.45" hidden="1">
       <c r="A29" s="16" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3303,25 +3315,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" ht="57.95" hidden="1">
       <c r="A30" s="16" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3347,25 +3359,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" ht="57.95" hidden="1">
       <c r="A31" s="16" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3391,25 +3403,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" ht="87" hidden="1">
       <c r="A32" s="16" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3435,25 +3447,25 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" ht="130.5" hidden="1">
       <c r="A33" s="16" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3479,10 +3491,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3568,7 +3580,7 @@
           <x14:formula1>
             <xm:f>Listas!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>J9:J33 J2:J5 Q26:R26 G2:I33</xm:sqref>
+          <xm:sqref>J9:J33 J2:J5 G2:I33 Q26:R26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3579,12 +3591,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="7" width="10.54296875" customWidth="1"/>
+    <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="29.1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3592,50 +3604,50 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="29.1">
       <c r="A2" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="43.5">
       <c r="A3" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3644,58 +3656,58 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="29.1">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3706,9 +3718,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3732,17 +3744,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015CE13C5EA719F4EA619D9E66753C54C" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55cb74fdf57f27f2cc9cf17ec2a40dfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbf5d18f-a539-415a-b4b5-b13bf63fbc53" xmlns:ns3="3de8a3b1-ed4f-410f-8887-f682d26381a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb33ddc406ed8ee1ec2e32dedb674c94" ns2:_="" ns3:_="">
     <xsd:import namespace="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
@@ -3983,42 +3984,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
-    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6E36CCD-40C1-44B9-BCA9-46D8D52C8FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F58443B4-ED8D-41A7-8BF2-F4C86CAD2BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2676,7 +2676,7 @@
         <v>46373</v>
       </c>
       <c r="P17" s="8">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>147</v>

--- a/Painel-de-Projetos.xlsx
+++ b/Painel-de-Projetos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-assessoria.governanca/Shared Documents/General/PROJETOS/PROJETOS - RAP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akihiro.hayashi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F58443B4-ED8D-41A7-8BF2-F4C86CAD2BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF907DCE-012C-4E21-B811-E65365877877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="281">
   <si>
     <t>ID Projeto</t>
   </si>
@@ -191,43 +191,7 @@
     <t>Saudável</t>
   </si>
   <si>
-    <t>Live 1.0 - entregue
-Consulta de peças - entregue
-Live 2.0 em andamento sem impeditivos</t>
-  </si>
-  <si>
     <t>26/10/2026 a 29/10/2026</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Ajustando história de usuário.
-Novo app: Área realizou homologação e solicitou 25 ajustes, com entrega até 29/10/26;
-Live 2.0: Feito correções do Portal e integrado SISPL com mainframe.
-Emplacar veículo 0Km: Detalhado cronograma de execução</t>
-  </si>
-  <si>
-    <t>Gestão de procuração 2.0: Realizar ajustes nas história do usuário e desenvolver protótipo;
-Novo app: Realizar ajustes no app, até 29/10/26.
-Autorização de Transporte Escolar: Detalhar cronograma de desenvolvimento.
-Live 2.0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL.
-Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação.</t>
-  </si>
-  <si>
-    <t>Não houve report pelo GP do projeto:
-Primeira Habilitação;
-Renovação da CNH.
-Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala.
-Primeira Habilitação
-Renovação da CNH
-Live 1.0
-Live2.0
-Autorização de Transporte Escolar (ATE)
-Gestão de Procuração 2.0
-Emplacar Veículo 0Km
-Novo APP DETRAN-SP</t>
   </si>
   <si>
     <t xml:space="preserve">Otimizar a experiência e a satisfação do usuário com o atendimento
@@ -278,56 +242,6 @@
 Edital  publicado - provas 01/11/2026 (DAL)
 Material de treinamento em elaboração
 Concurso Público ocorre no domingo (01/11) conforme planejado</t>
-  </si>
-  <si>
-    <t>Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar - pendente validação da grade de formação dos 60 dias.</t>
-  </si>
-  <si>
-    <t>Publicação do Edital - Prova 01/11/2026.
-Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes.
-Concurso Público ocorre no domingo (01/11) conforme planejado.
-Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar.</t>
-  </si>
-  <si>
-    <t>Atualização do cronograma.
-Novo alinhamento com Tati e EPT para concluir as definições/validação de grade dos 60 dias.
-Definição dos locais na SEDE para realização do curso EAD para os ingressantes com Norma - depende da estratégia a ser definida para a formação em 60 dias com EPT e Tati.
-DCI finalizar a pesquisa dos docentes da DHC.
-DAC abrir SEI direcionado a DCI para solicitar pesquisa de seus docentes.</t>
-  </si>
-  <si>
-    <t>Atraso na revisão e validação do conteúdo da capacitação;
-Alterações normativas durante a produção do conteúdo da capacitação.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Promover a recepção dos novos agentes, garantindo que o processo de onboarding seja estruturado e acolhedor.
-A iniciativa contempla a apresentação institucional, incluindo áreas da empresa, benefícios e regras internas, além de reforçar a integração cultural por meio de atividades que transmitam valores, missão e visão da organização, serão ministrados treinamentos operacionais voltados às rotinas e processos específicos de cada função, com suporte de ferramentas digitais que centralizam informações, documentos e conteúdos de capacitação.
-Capacitação dos novos ingressantes para o exercício da função.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>NÃO ESCOPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: O Concurso Público em andamento é de responsabilidade única e exclusivamente da DAL. 
-A data da realização da prova, descrita  nesse projeto, é meramente informativa.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
@@ -430,9 +344,6 @@
     <t>FOCUS</t>
   </si>
   <si>
-    <t>Portaria DETRAN-SP Nº 2.889, DE 25 DE ABRIL DE 2024</t>
-  </si>
-  <si>
     <t>Isabella Monteiro</t>
   </si>
   <si>
@@ -440,32 +351,6 @@
   </si>
   <si>
     <t>Atenção</t>
-  </si>
-  <si>
-    <t>Mudança de estratégia: 
-Decisão de entrar na licitação da PRF para aquisição das câmeras corporais;
-Dependência de licitação a ser realizada por outro órgão;
-Até o momento não temos resposta da PRF sobre a licitação.</t>
-  </si>
-  <si>
-    <t>Nenhuma realização relevante registrada no período.
-Não houve necessidade de agenda do projeto</t>
-  </si>
-  <si>
-    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
-Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação.
-Não houve resposta da PRF até o momento.
-Não houve necessidade de agenda do projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação.
-</t>
-  </si>
-  <si>
-    <t>Dependência da licitação da PRF.</t>
-  </si>
-  <si>
-    <t>Estudar e implementar solução de monitoramento audiovisual da atuação do Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP).</t>
   </si>
   <si>
     <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
@@ -512,36 +397,10 @@
     <t>AEPE</t>
   </si>
   <si>
-    <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura.
-Desenhos técnicos necessários para contratação disponibilizados desde julho/2026.
-</t>
-  </si>
-  <si>
     <t>Não houve necessidade de agenda do projeto</t>
   </si>
   <si>
-    <t>Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP;
-Desenvolvimento das definições de layout, fluxos, materialidade e aplicabilidade do conceito;
-Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026; Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade.
-Não houve necessidade de agenda do projeto.</t>
-  </si>
-  <si>
-    <t>Prosseguimento, pela área de Infraestrutura, dos procedimentos necessários para contratação e implantação da unidade, contemplando os projetos e serviços necessários à execução da obra.
-Paralelamente, as definições consolidadas no projeto-piloto deverão subsidiar a padronização e replicabilidade do Habilita SP, com as devidas adequações às características e necessidades de cada futura unidade.</t>
-  </si>
-  <si>
-    <t>Necessidade de acompanhamento do andamento da contratação pela Infraestrutura, considerando que os desenhos técnicos estão disponibilizados desde julho/2026.
-Por se tratar do projeto-piloto, eventuais ajustes identificados durante as etapas de projeto executivo e implantação deverão ser avaliados quanto ao seu impacto no padrão a ser replicado nas demais unidades do Habilita SP.</t>
-  </si>
-  <si>
     <t>Cronograma com estimativa do prazo final</t>
-  </si>
-  <si>
-    <t>Risco de impacto no cronograma de implantação, caso haja prolongamento das etapas de contratação dos projetos, obra e serviços.
-Considerando o caráter piloto da Estaiadinha, eventual atraso também poderá repercutir na validação prática das soluções e na consolidação do padrão para expansão do Habilita SP.</t>
-  </si>
-  <si>
-    <t>Desenvolver e implementar, no âmbito do Estado de São Paulo, as localidades e instalações de realização dos exames práticos de direção veicular, com fundamento no artigo 12, da Resolução CONTRAN nº 789, 18 de junho de 2020, promovendo a formação responsável de condutores e contribuindo para a segurança viária, por meio de processos íntegros e eficientes, atendimento de excelência e infraestrutura de alta qualidade.</t>
   </si>
   <si>
     <t>Adotar as melhores práticas de transparência ativa, de acesso à informação e de proteção de dados
@@ -626,31 +485,6 @@
     <t>Arturo Sangiovani</t>
   </si>
   <si>
-    <t>O projeto original contemplava os módulos ITSM, ITAM e ITOM.
-Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
-  </si>
-  <si>
-    <t>Entrega dos Catalogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026.</t>
-  </si>
-  <si>
-    <t>Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentens técnicos 3, adicionar função para ciação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB;</t>
-  </si>
-  <si>
-    <t>Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação; Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026;                                                                                                      </t>
-  </si>
-  <si>
-    <t>Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM.</t>
-  </si>
-  <si>
-    <t>Projeto pode ser interrompido por não assinar o contrato;</t>
-  </si>
-  <si>
-    <t>Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Empregar soluções tecnológicas inovadoras para alavancar os resultados
 Aperfeiçoar a estrutura organizacional e a qualificação do atendimento
 Otimizar a alocação e modernização dos equipamentos e da infraestrutura
@@ -670,21 +504,6 @@
   </si>
   <si>
     <t>AEGE</t>
-  </si>
-  <si>
-    <t>Mapeamento de todas as jornadas finalizado como planejado.</t>
-  </si>
-  <si>
-    <t>Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be.</t>
-  </si>
-  <si>
-    <t>Analistas estudando a teoria de Indicadores para aplicarem no projeto, conforme orientação AME e APC.</t>
-  </si>
-  <si>
-    <t>Realinhar formato de indicadores de cada melhoria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validação e feedback das jornadas to-be feitas. </t>
   </si>
   <si>
     <t>Mapeamento de Jornadas, para levantamento de dores e propostas de melhorias com foco no cidadão</t>
@@ -796,24 +615,6 @@
     <t>DVA</t>
   </si>
   <si>
-    <t>Em andamento sem impeditivo.</t>
-  </si>
-  <si>
-    <t>Acompanhamento da implantação do MVP2, com avanço de 50% com previsão de término para 03/11/2026.</t>
-  </si>
-  <si>
-    <t>Monitoramento da implantação MVP-1 extendida até 30/10/26, sem impacto no prazo final, com 90% de andamento.
-Monitoramento da implantação MVP-2, com 50% de andamento e término em 03/11/2026.</t>
-  </si>
-  <si>
-    <t>Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3).</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
-Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores.
-O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
 Promover a cultura de integridade e auditoria permanente, combatendo com agilidade os desvios e a corrupção
 Adotar as melhores práticas de transparência ativa, acesso à informação e proteção de dados
@@ -830,43 +631,12 @@
     <t>Artur Giannini</t>
   </si>
   <si>
-    <t>Projeto apresenta significativo atraso e não há previsão para o término.
-Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure impactando cronograma.
-- Treinamento - TBD;
-- Homologação - TBD;
-- GMUD - TBD.
-Agente Q&amp;A da Wiki ("Isa") - wave 2 - Integração com o portal - Best:
-- Desenvolvimento - 30/10;
-- GMUD - 06/11.
-Agente Revisor de Conteúdo da wiki - wave 3:
-- Entrega Microsoft e Integração com portal pela Best - sem previsão.</t>
-  </si>
-  <si>
     <t>Sistema de Atendimento: GMUD  apenas ECVs - 05/10/2026</t>
   </si>
   <si>
     <t>Base de Conhecimento - entregue 14/06/2026
 Sistema de Atendimento - entregue 14/06/2026 (homologação)
 Base de Conhecimento - correções - entregue 30/09/2026</t>
-  </si>
-  <si>
-    <t>Agente OCR de Documentos de Credenciamento - integração com o portal:
---    Treinamento - TBD
---    Homologação - TBD
---    GMUD - TBD
---    Aguardando a migração de configuração OCR e Azure para Produção e Best seguir com cronograma de entrega.
-Agente Q&amp;A da Wiki ("Isa") - wave 2 - Microsoft - 06/11/2026
-Agente Revisor de Conteúdo da wiki - wave 3:
---    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
-  </si>
-  <si>
-    <t>O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e Best seguir replanejar as atividades no cronograma da entrega do OCR e Agentes IA wave2 e wave 3.</t>
-  </si>
-  <si>
-    <t>OCR e Azure: tinha bloqueio de configurações e migração para produção até 23/10 -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção. Esta aprovação foi realizada em 23/10.</t>
-  </si>
-  <si>
-    <t>A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto.</t>
   </si>
   <si>
     <t xml:space="preserve">Base de Conhecimento
@@ -935,42 +705,7 @@
     <t>BeSolution</t>
   </si>
   <si>
-    <t>Entrega V3.1: Correção de 10 itens prioritários:
-- Homologação Detran: 11/11.
-Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): Loja Android foi aprovado, pendente aprovação da loja da App Store.
-Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo) - 30/10
-Mapa de lesões V4 - em desenvolvimento: 
-- Homologação em 30/10.
-Módulo CST (V4):
-- Homologação Detran: TBD;
-- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
-  </si>
-  <si>
-    <t>Correção de Bugs da V3, iniciada subida em Produção, com publicação do App na loja Android e cadastro de usuários em andamento.</t>
-  </si>
-  <si>
-    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço;
-Entrega V3.1: Correção de 10 itens prioritários:
-- Homologação Detran: 11/11.
-Aprovação do APP pela loja iOS (App Store)
-Mapa de lesões V4 em desenvolvimento:
-- Homologação: 30/10.
-Módulo CST (V4):
-- Homologação Detran: TBD;
-- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
-  </si>
-  <si>
-    <t>Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)
-Atraso no Módulo CST (V4) para estimativa Be Solution e viabilidade técnica devido novos pedidos do Detran. Nova data será planejada depois de 5 dias do recebimento dos novos requisitos.</t>
-  </si>
-  <si>
     <t>Possível revisão de escopo - impacto no cronograma</t>
-  </si>
-  <si>
-    <t>O RST (Registro de Sinistro de Trânsito) é um sistema digital inovador desenvolvido para modernizar o processo de registro e acompanhamento de acidentes de trânsito.
-O projeto tem como foco usabilidade, automação inteligente e integração com fontes oficiais, operando totalmente em nuvem e com arquitetura escalável, responsiva e segura.
-O sistema foi construído sobre bases técnicas e operacionais que garantem segurança, desempenho e conformidade.
-Foco em entregar App com módulo RST, sendo aplicativo único para todos órgãos de trânsito, com transcrição IA para agente de trânsito/GCM para reportar notificações e integração monta Infosiga.</t>
   </si>
   <si>
     <t xml:space="preserve">Fortalecer a atuação e a cooperação com os demais órgãos de trânsito e segurança pública
@@ -990,42 +725,10 @@
     <t>SIAUT</t>
   </si>
   <si>
-    <t>Portaria DETRAN-SP nº 4.830, de 30 de julho de 2024</t>
-  </si>
-  <si>
     <t>Cyntia Tiemi Nihy</t>
   </si>
   <si>
-    <t>Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
-Devido a férias do P.O. do projeto essa aprovação só ocorrerá após 29/10.</t>
-  </si>
-  <si>
-    <t>Nenhuma realização relevante registrada no período.
-Não houve necessidade de agenda do projeto.</t>
-  </si>
-  <si>
-    <t>Etapa 3 - Concluída em 07/08/2026;
-Etapa 4 definida pela DFT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Etapa 4 -aprovação da presidência;
-Etapa 4 - início - requisitos.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprovação  da etapa 4 - apenas após 29/10/2026, devido as férias do P.O. do projeto 
-</t>
-  </si>
-  <si>
     <t>Aprovação da Etapa 4</t>
-  </si>
-  <si>
-    <t>O Projeto SIAUT tem por objetivo operacionalizar a lavratura de autuações e a aplicação das respectivas penalidades administrativas oriunda as infrações administrativas conhecidas como "multas de balcão", de competência do DETRAN-SP, que serão implantadas através de 04 (quatro) ETAPAS.
-ETAPA1 (MULTAS ART. 165-D)
-ETAPA2 (MULTAS ARTS.233 e 257, § 8º - NIC)
-ETAPA3 (MULTAS ARTS. 162, 163 ou 164)
-ETAPA4 (MULTAS ARTS. 240, 241, 242 e 243)</t>
   </si>
   <si>
     <t>Implementar as melhores práticas para a excelência dos processos internos e serviços à sociedade
@@ -1226,12 +929,289 @@
   <si>
     <t>Cancelado</t>
   </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 5 561, de 20 de setembro de 2024</t>
+  </si>
+  <si>
+    <t>Live 1 0 - entregue
+Consulta de peças - entregue
+Live 2 0 em andamento sem impeditivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Planejar a implementação e gerir a equipe de fornecedores para desenvolvimento de produtos digitais, para o Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP), utilizando modelos de inteligência artificial generativa e linguagem de grande escala 
+Primeira Habilitação
+Renovação da CNH
+Live 1 0
+Live2 0
+Autorização de Transporte Escolar (ATE)
+Gestão de Procuração 2 0
+Emplacar Veículo 0Km
+Novo APP DETRAN-SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar - pendente validação da grade de formação dos 60 dias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publicação do Edital - Prova 01/11/2026 
+Análise da lista de docentes da DHC está sendo realizada pela DCI e realizado alinhamento com DTI sobre a disponibilidade de equipamentos e posições de trabalho para o treinamento dos ingressantes 
+Concurso Público ocorre no domingo (01/11) conforme planejado 
+Realizado alinhamento com a Tati junto EPT sobre a grade do curso de formação e uso dos 60 dias propostas pela EPT, do conteúdo que é obrigatório versus o que fica como complementar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atualização do cronograma 
+Novo alinhamento com Tati e EPT para concluir as definições/validação de grade dos 60 dias 
+Definição dos locais na SEDE para realização do curso EAD para os ingressantes com Norma - depende da estratégia a ser definida para a formação em 60 dias com EPT e Tati 
+DCI finalizar a pesquisa dos docentes da DHC 
+DAC abrir SEI direcionado a DCI para solicitar pesquisa de seus docentes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promover a recepção dos novos agentes, garantindo que o processo de onboarding seja estruturado e acolhedor 
+A iniciativa contempla a apresentação institucional, incluindo áreas da empresa, benefícios e regras internas, além de reforçar a integração cultural por meio de atividades que transmitam valores, missão e visão da organização, serão ministrados treinamentos operacionais voltados às rotinas e processos específicos de cada função, com suporte de ferramentas digitais que centralizam informações, documentos e conteúdos de capacitação 
+Capacitação dos novos ingressantes para o exercício da função 
+NÃO ESCOPO: O Concurso Público em andamento é de responsabilidade única e exclusivamente da DAL  
+A data da realização da prova, descrita  nesse projeto, é meramente informativa </t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP Nº 2 889, DE 25 DE ABRIL DE 2024</t>
+  </si>
+  <si>
+    <t>Nenhuma realização relevante registrada no período 
+Não houve necessidade de agenda do projeto</t>
+  </si>
+  <si>
+    <t>Decisão de entrar na licitação da PRF para aquisição das câmeras corporais
+Foi solicitado formalmente à PRF a inclusão das camêras para o DETRAN-SP na licitação 
+Não houve resposta da PRF até o momento 
+Não houve necessidade de agenda do projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguardando resposta da PRF sobre a licitação 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependência da licitação da PRF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudar e implementar solução de monitoramento audiovisual da atuação do Departamento Estadual de Trânsito do Estado de São Paulo (DETRAN-SP) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demora no processo de contratação pela área de infraestrutura 
+Desenhos técnicos necessários para contratação disponibilizados desde julho/2026 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosseguimento, pela área de Infraestrutura, dos procedimentos necessários para contratação e implantação da unidade, contemplando os projetos e serviços necessários à execução da obra 
+Paralelamente, as definições consolidadas no projeto-piloto deverão subsidiar a padronização e replicabilidade do Habilita SP, com as devidas adequações às características e necessidades de cada futura unidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necessidade de acompanhamento do andamento da contratação pela Infraestrutura, considerando que os desenhos técnicos estão disponibilizados desde julho/2026 
+Por se tratar do projeto-piloto, eventuais ajustes identificados durante as etapas de projeto executivo e implantação deverão ser avaliados quanto ao seu impacto no padrão a ser replicado nas demais unidades do Habilita SP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risco de impacto no cronograma de implantação, caso haja prolongamento das etapas de contratação dos projetos, obra e serviços 
+Considerando o caráter piloto da Estaiadinha, eventual atraso também poderá repercutir na validação prática das soluções e na consolidação do padrão para expansão do Habilita SP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolver e implementar, no âmbito do Estado de São Paulo, as localidades e instalações de realização dos exames práticos de direção veicular, com fundamento no artigo 12, da Resolução CONTRAN nº 789, 18 de junho de 2020, promovendo a formação responsável de condutores e contribuindo para a segurança viária, por meio de processos íntegros e eficientes, atendimento de excelência e infraestrutura de alta qualidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O projeto original contemplava os módulos ITSM, ITAM e ITOM 
+Atualmente os módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega dos Catalogos de Serviço das divisões DAFT, implantar melhorias urgentes, DETRAN-SP -28/09/20026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Módulos ITAM e ITOM estão "congelados" e os esforços estão concentrados apenas no ITSM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implantação e a operacionalização de um sistema integrado de gestão de ativos, de serviços e de operações de Tecnologia da Informação (TI) no âmbito do DETRAN-SP visando a otimização e o controle dos processos relacionados à gestão do ciclo de vida dos ativos de TI, à prestação de serviços de TI e à eficiência operacional dos processos de TI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapeamento de todas as jornadas finalizado como planejado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reavaliação do trabalho pela AME, com ajuste no foco da entrega e na resolução do To-be </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analistas estudando a teoria de Indicadores para aplicarem no projeto, conforme orientação AME e APC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realinhar formato de indicadores de cada melhoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validação e feedback das jornadas to-be feitas  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em andamento sem impeditivo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompanhamento da implantação do MVP2, com avanço de 50% com previsão de término para 03/11/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoramento da implantação MVP-1 extendida até 30/10/26, sem impacto no prazo final, com 90% de andamento 
+Monitoramento da implantação MVP-2, com 50% de andamento e término em 03/11/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implantar-Laudos de Vistoria de Segurança Veicular (MVP-3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento e implantação da jornada de pagamento digital das vistorias veiculares no Portal Detran-SP, com integração ao ambiente financeiro do Banco do Brasil e à Plataforma
+Estadual de Veículos, conforme as especificações técnicas e requisitos funcionais validados pela Diretoria de Veículos Automotores 
+O serviço tem por objetivo viabilizar o recolhimento eletrônico das taxas de vistoria por meio de PIX, dispensando login prévio, com rastreabilidade integral das transações, integração automática com os sistemas de vistoria e restituição automatizada de valores </t>
+  </si>
+  <si>
+    <t>Agente OCR de Documentos de Credenciamento - integração com o portal:
+--    Treinamento - TBD
+--    Homologação - TBD
+--    GMUD - TBD
+--    Aguardando a migração de configuração OCR e Azure para Produção e Best seguir com cronograma de entrega 
+Agente Q&amp;A da Wiki ("Isa") - wave 2 - Microsoft - 06/11/2026
+Agente Revisor de Conteúdo da wiki - wave 3:
+--    Entrega Microsoft e Integração com portal pela Best - sem previsão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O crédito a Microsoft foi aprovado pela Prodesp em 23/10, para custear recursos Azure em Produção e Best seguir replanejar as atividades no cronograma da entrega do OCR e Agentes IA wave2 e wave 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCR e Azure: tinha bloqueio de configurações e migração para produção até 23/10 -  Prodesp informou que recursos Azure geram custos e dependem de aprovações adicionais em ambiente de Produção  Esta aprovação foi realizada em 23/10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A falta de um cronograma definido pela MIcrosoft, e a necessidade de  integração com o portal a cargo da Best sinalizam atrasos significativos para esse projeto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção de Bugs da V3, iniciada subida em Produção, com publicação do App na loja Android e cadastro de usuários em andamento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço (previsão era 13/10, está atrasado)
+Atraso no Módulo CST (V4) para estimativa Be Solution e viabilidade técnica devido novos pedidos do Detran  Nova data será planejada depois de 5 dias do recebimento dos novos requisitos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O RST (Registro de Sinistro de Trânsito) é um sistema digital inovador desenvolvido para modernizar o processo de registro e acompanhamento de acidentes de trânsito 
+O projeto tem como foco usabilidade, automação inteligente e integração com fontes oficiais, operando totalmente em nuvem e com arquitetura escalável, responsiva e segura 
+O sistema foi construído sobre bases técnicas e operacionais que garantem segurança, desempenho e conformidade 
+Foco em entregar App com módulo RST, sendo aplicativo único para todos órgãos de trânsito, com transcrição IA para agente de trânsito/GCM para reportar notificações e integração monta Infosiga </t>
+  </si>
+  <si>
+    <t>Portaria DETRAN-SP nº 4 830, de 30 de julho de 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto paralizado aguardando aprovação da etapa 4 pela Presidência
+Devido a férias do P O  do projeto essa aprovação só ocorrerá após 29/10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma realização relevante registrada no período 
+Não houve necessidade de agenda do projeto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovação  da etapa 4 - apenas após 29/10/2026, devido as férias do P O  do projeto 
+</t>
+  </si>
+  <si>
+    <t>O Projeto SIAUT tem por objetivo operacionalizar a lavratura de autuações e a aplicação das respectivas penalidades administrativas oriunda as infrações administrativas conhecidas como "multas de balcão", de competência do DETRAN-SP, que serão implantadas através de 04 (quatro) ETAPAS 
+ETAPA1 (MULTAS ART  165-D)
+ETAPA2 (MULTAS ARTS 233 e 257, § 8º - NIC)
+ETAPA3 (MULTAS ARTS  162, 163 ou 164)
+ETAPA4 (MULTAS ARTS  240, 241, 242 e 243)</t>
+  </si>
+  <si>
+    <t>Gestão de procuração 2 0: Ajustando história de usuário 
+Novo app: Área realizou homologação e solicitou 25 ajustes, com entrega até 29/10/26 
+Live 2 0: Feito correções do Portal e integrado SISPL com mainframe 
+Emplacar veículo 0Km: Detalhado cronograma de execução</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestão de procuração 2 0: Realizar ajustes nas história do usuário e desenvolver protótipo 
+Novo app: Realizar ajustes no app, até 29/10/26 
+Autorização de Transporte Escolar: Detalhar cronograma de desenvolvimento 
+Live 2 0: Homologar o desenvolvimento do portal, Executar QA-SISPL Sem socket e Construir o Socket-MF no SISPL 
+Emplacar veículo 0Km: Desenvolver estrutura técnica e modelo de dados da aplicação </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não houve report pelo GP do projeto:
+Primeira Habilitação 
+Renovação da CNH 
+Autorização de Transporte Escolar: Chaintec não forneceu cronograma de desenvolvimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atraso na revisão e validação do conteúdo da capacitação 
+Alterações normativas durante a produção do conteúdo da capacitação </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mudança de estratégia: 
+Decisão de entrar na licitação da PRF para aquisição das câmeras corporais 
+Dependência de licitação a ser realizada por outro órgão 
+Até o momento não temos resposta da PRF sobre a licitação </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidação da Estaiadinha como projeto-piloto e referência técnica do Habilita SP 
+Desenvolvimento das definições de layout, fluxos, materialidade e aplicabilidade do conceito 
+Conclusão e encaminhamento dos desenhos técnicos à Infraestrutura em julho/2026  Processo encaminhado para continuidade das etapas necessárias à contratação de projetos, obra e serviços para implantação da unidade 
+Não houve necessidade de agenda do projeto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega do catálogo da Divisão de Auditoria Forense Digital, interrompida a construção do Catálogo da Divisão de Segurança da Informação, atender as solicitações de melhorias urgentes, conceder acesso aos assistentens técnicos 3, adicionar função para ciação de rótulo no VTB, adicionar log na atividade de troca de grupo e atalho para página VTB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retomar desenvolvimento do catálogo da Divisão de Segurança da Informação  Iniciar homologação do catálogo da Divisão de Auditoria Forense Digital e finalizar o desenvolvimento do catálogo da Divisão de Monitoramento e Resposta a Incidentes Cibernéticos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato prestes a vencer em 21/11/2026                                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto pode ser interrompido por não assinar o contrato </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto apresenta significativo atraso e não há previsão para o término 
+Agente OCR - Integração com portal - Best: tem bloqueio de liberação de recursos do Azure impactando cronograma 
+- Treinamento - TBD 
+- Homologação - TBD 
+- GMUD - TBD 
+Agente Q&amp;A da Wiki ("Isa") - wave 2 - Integração com o portal - Best:
+- Desenvolvimento - 30/10 
+- GMUD - 06/11 
+Agente Revisor de Conteúdo da wiki - wave 3:
+- Entrega Microsoft e Integração com portal pela Best - sem previsão </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega V3 1: Correção de 10 itens prioritários:
+- Homologação Detran: 11/11 
+Publicação do app RST nas lojas Android (Google Play) e iOS (App Store): Loja Android foi aprovado, pendente aprovação da loja da App Store 
+Cadastro dos primeiros usuários de Produção em andamento: Estimativa de 90 usuários em campo (prova em campo) - 30/10
+Mapa de lesões V4 - em desenvolvimento: 
+- Homologação em 30/10 
+Módulo CST (V4):
+- Homologação Detran: TBD 
+- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran  Nova data será planejada depois de 5 dias do recebimento dos novos requisitos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detran retornar o parecer sobre as documentações Anexos_C e Ordem_de_Serviço 
+Entrega V3 1: Correção de 10 itens prioritários:
+- Homologação Detran: 11/11 
+Aprovação do APP pela loja iOS (App Store)
+Mapa de lesões V4 em desenvolvimento:
+- Homologação: 30/10 
+Módulo CST (V4):
+- Homologação Detran: TBD 
+- Estimativa Be Solution e viabilidade técnica: em atraso, devido novos pedidos do Detran  Nova data será planejada depois de 5 dias do recebimento dos novos requisitos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etapa 3 - Concluída em 07/08/2026 
+Etapa 4 definida pela DFT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Etapa 4 -aprovação da presidência 
+Etapa 4 - início - requisitos 
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,14 +1236,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1359,7 +1331,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1757,7 +1729,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="25" style="29" customWidth="1"/>
@@ -1778,7 +1750,7 @@
     <col min="24" max="24" width="120.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.95" customHeight="1">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1852,7 +1824,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="409.5" hidden="1">
+    <row r="2" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
@@ -1896,7 +1868,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="246.6" hidden="1">
+    <row r="3" spans="1:24" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
@@ -1940,7 +1912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="217.5">
+    <row r="4" spans="1:24" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1948,7 +1920,7 @@
         <v>38</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>40</v>
@@ -1963,13 +1935,13 @@
         <v>42</v>
       </c>
       <c r="H4" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>44</v>
-      </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="K4" s="30">
         <v>0.75</v>
@@ -1992,34 +1964,34 @@
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="3" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>47</v>
+        <v>268</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="130.5" hidden="1">
+    <row r="5" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>28</v>
@@ -2045,25 +2017,25 @@
       <c r="U5" s="22"/>
       <c r="V5" s="22"/>
       <c r="W5" s="23" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="275.25">
+    <row r="6" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -2072,13 +2044,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="K6" s="28">
         <v>0.15</v>
@@ -2099,36 +2071,36 @@
         <v>45958</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="6"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
-        <v>63</v>
+        <v>269</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>64</v>
+        <v>228</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="261" hidden="1">
+    <row r="7" spans="1:24" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>34</v>
@@ -2157,25 +2129,25 @@
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
       <c r="W7" s="23" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="409.5" hidden="1">
+    <row r="8" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>28</v>
@@ -2201,25 +2173,25 @@
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
       <c r="W8" s="23" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="9" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>28</v>
@@ -2245,42 +2217,42 @@
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="23" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="121.5">
+    <row r="10" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="K10" s="30">
         <v>0.79</v>
@@ -2299,37 +2271,37 @@
         <v>46304</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>91</v>
+        <v>232</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>92</v>
+        <v>233</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="29.1" hidden="1">
+    <row r="11" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>28</v>
@@ -2355,42 +2327,42 @@
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
       <c r="W11" s="23" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="183">
+    <row r="12" spans="1:24" ht="195" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K12" s="28">
         <v>0.53</v>
@@ -2409,34 +2381,34 @@
         <v>46304</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>110</v>
+        <v>237</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="3" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="409.5" hidden="1">
+    <row r="13" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="19"/>
@@ -2467,27 +2439,27 @@
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
       <c r="W13" s="23" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="130.5" hidden="1">
+    <row r="14" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>28</v>
@@ -2513,23 +2485,23 @@
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
       <c r="W14" s="23" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="130.5" hidden="1">
+    <row r="15" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>28</v>
@@ -2555,22 +2527,22 @@
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
       <c r="W15" s="23" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="X15" s="23" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="137.25">
+    <row r="16" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="7" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
@@ -2579,16 +2551,16 @@
         <v>41</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="K16" s="28">
         <v>0.81</v>
@@ -2609,41 +2581,41 @@
         <v>46321</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>136</v>
+        <v>274</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="3" t="s">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>138</v>
+        <v>275</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="45.75">
+    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="7" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>41</v>
@@ -2652,13 +2624,13 @@
         <v>42</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>145</v>
+        <v>244</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="K17" s="28">
         <v>0.9</v>
@@ -2679,34 +2651,34 @@
         <v>46324</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>147</v>
+        <v>246</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>148</v>
+        <v>247</v>
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="6"/>
       <c r="U17" s="3" t="s">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="409.5" hidden="1">
+    <row r="18" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="19" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>34</v>
@@ -2735,25 +2707,25 @@
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
       <c r="W18" s="23" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="19" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>28</v>
@@ -2779,25 +2751,25 @@
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
       <c r="W19" s="23" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="87" hidden="1">
+    <row r="20" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>28</v>
@@ -2823,25 +2795,25 @@
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
       <c r="W20" s="23" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="101.45" hidden="1">
+    <row r="21" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>28</v>
@@ -2867,27 +2839,27 @@
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="183">
+    <row r="22" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>41</v>
@@ -2896,13 +2868,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="K22" s="28">
         <v>0.95</v>
@@ -2923,50 +2895,50 @@
         <v>46321</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="6"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="275.25">
+    <row r="23" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="7" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="K23" s="28">
         <v>0.5</v>
@@ -2985,41 +2957,41 @@
         <v>46324</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="72.599999999999994" hidden="1">
+    <row r="24" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>28</v>
@@ -3045,25 +3017,25 @@
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
       <c r="W24" s="23" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="X24" s="23" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="57.95" hidden="1">
+    <row r="25" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>28</v>
@@ -3089,40 +3061,40 @@
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
       <c r="W25" s="23" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="X25" s="23" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="275.25">
+    <row r="26" spans="1:24" ht="300" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="7" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="K26" s="28">
         <v>0.99</v>
@@ -3143,56 +3115,56 @@
         <v>46323</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="R26" s="14" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="152.25">
+    <row r="27" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>217</v>
+        <v>262</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="K27" s="30">
         <v>0.92</v>
@@ -3213,39 +3185,39 @@
         <v>46303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="87" hidden="1">
+    <row r="28" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F28" s="19" t="s">
         <v>28</v>
@@ -3271,25 +3243,25 @@
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
       <c r="W28" s="23" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="101.45" hidden="1">
+    <row r="29" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>28</v>
@@ -3315,25 +3287,25 @@
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
       <c r="W29" s="23" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="57.95" hidden="1">
+    <row r="30" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>28</v>
@@ -3359,25 +3331,25 @@
       <c r="U30" s="22"/>
       <c r="V30" s="22"/>
       <c r="W30" s="23" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="X30" s="23" t="s">
-        <v>239</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="57.95" hidden="1">
+    <row r="31" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="19" t="s">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>28</v>
@@ -3403,25 +3375,25 @@
       <c r="U31" s="22"/>
       <c r="V31" s="22"/>
       <c r="W31" s="23" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="X31" s="23" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="87" hidden="1">
+    <row r="32" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>28</v>
@@ -3447,25 +3419,25 @@
       <c r="U32" s="22"/>
       <c r="V32" s="22"/>
       <c r="W32" s="23" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="130.5" hidden="1">
+    <row r="33" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="19" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>28</v>
@@ -3491,10 +3463,10 @@
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
       <c r="W33" s="23" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3591,12 +3563,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29.1">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3604,50 +3576,50 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>258</v>
+        <v>200</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29.1">
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>41</v>
@@ -3656,58 +3628,58 @@
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29.1">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -3718,9 +3690,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3735,12 +3707,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3985,26 +3959,50 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbf5d18f-a539-415a-b4b5-b13bf63fbc53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de8a3b1-ed4f-410f-8887-f682d26381a0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128BA07-FD07-4BF6-A5A5-C36F2194B10D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbf5d18f-a539-415a-b4b5-b13bf63fbc53"/>
+    <ds:schemaRef ds:uri="3de8a3b1-ed4f-410f-8887-f682d26381a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098CA860-76E1-4F5F-B46F-7BF705BE868D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB5EC8F-6DDA-4EEB-ACA6-454A491FFD4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
